--- a/RTM_AI_generated.xlsx
+++ b/RTM_AI_generated.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="600" firstSheet="0" activeTab="2" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="600" firstSheet="0" activeTab="2" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DR-FL" sheetId="1" state="visible" r:id="rId1"/>
@@ -197,7 +197,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -254,21 +254,27 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -283,25 +289,31 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -652,44 +664,44 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="30" t="inlineStr">
+      <c r="A1" s="32" t="inlineStr">
         <is>
           <t>Feature List分解表格</t>
         </is>
       </c>
-      <c r="B1" s="21" t="n"/>
-      <c r="C1" s="21" t="n"/>
-      <c r="D1" s="21" t="n"/>
-      <c r="E1" s="22" t="n"/>
-    </row>
-    <row r="2" ht="21" customHeight="1" s="25">
-      <c r="A2" s="30" t="inlineStr">
+      <c r="B1" s="22" t="n"/>
+      <c r="C1" s="22" t="n"/>
+      <c r="D1" s="22" t="n"/>
+      <c r="E1" s="23" t="n"/>
+    </row>
+    <row r="2" ht="21" customHeight="1" s="28">
+      <c r="A2" s="32" t="inlineStr">
         <is>
           <t>DR编号</t>
         </is>
       </c>
-      <c r="B2" s="30" t="inlineStr">
+      <c r="B2" s="32" t="inlineStr">
         <is>
           <t>Feature类别</t>
         </is>
       </c>
-      <c r="C2" s="30" t="inlineStr">
+      <c r="C2" s="32" t="inlineStr">
         <is>
           <t>FL编号</t>
         </is>
       </c>
-      <c r="D2" s="30" t="inlineStr">
+      <c r="D2" s="32" t="inlineStr">
         <is>
           <t>Feature描述</t>
         </is>
       </c>
-      <c r="E2" s="30" t="inlineStr">
+      <c r="E2" s="32" t="inlineStr">
         <is>
           <t>TP编号</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="27" customHeight="1" s="25">
+    <row r="3" ht="27" customHeight="1" s="28">
       <c r="A3" s="12" t="inlineStr">
         <is>
           <t>DR.APLC.001</t>
@@ -716,7 +728,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="27" customHeight="1" s="25">
+    <row r="4" ht="27" customHeight="1" s="28">
       <c r="A4" s="14" t="inlineStr">
         <is>
           <t>DR.APLC.001</t>
@@ -743,7 +755,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="27" customHeight="1" s="25">
+    <row r="5" ht="27" customHeight="1" s="28">
       <c r="A5" s="14" t="inlineStr">
         <is>
           <t>DR.APLC.001</t>
@@ -770,7 +782,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="27" customHeight="1" s="25">
+    <row r="6" ht="27" customHeight="1" s="28">
       <c r="A6" s="14" t="inlineStr">
         <is>
           <t>DR.APLC.001</t>
@@ -797,7 +809,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="27" customHeight="1" s="25">
+    <row r="7" ht="27" customHeight="1" s="28">
       <c r="A7" s="14" t="inlineStr">
         <is>
           <t>DR.APLC.001</t>
@@ -824,7 +836,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="27" customHeight="1" s="25">
+    <row r="8" ht="27" customHeight="1" s="28">
       <c r="A8" s="14" t="inlineStr">
         <is>
           <t>DR.APLC.001</t>
@@ -851,7 +863,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="27" customHeight="1" s="25">
+    <row r="9" ht="27" customHeight="1" s="28">
       <c r="A9" s="14" t="inlineStr">
         <is>
           <t>DR.APLC.001</t>
@@ -878,7 +890,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="27" customHeight="1" s="25">
+    <row r="10" ht="27" customHeight="1" s="28">
       <c r="A10" s="14" t="inlineStr">
         <is>
           <t>DR.APLC.001</t>
@@ -905,7 +917,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="27" customHeight="1" s="25">
+    <row r="11" ht="27" customHeight="1" s="28">
       <c r="A11" s="14" t="inlineStr">
         <is>
           <t>DR.APLC.001</t>
@@ -932,7 +944,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="27" customHeight="1" s="25">
+    <row r="12" ht="27" customHeight="1" s="28">
       <c r="A12" s="14" t="inlineStr">
         <is>
           <t>DR.APLC.001</t>
@@ -959,7 +971,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="27" customHeight="1" s="25">
+    <row r="13" ht="27" customHeight="1" s="28">
       <c r="A13" s="14" t="inlineStr">
         <is>
           <t>DR.APLC.001</t>
@@ -986,7 +998,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="27" customHeight="1" s="25">
+    <row r="14" ht="27" customHeight="1" s="28">
       <c r="A14" s="14" t="inlineStr">
         <is>
           <t>DR.APLC.001</t>
@@ -1013,7 +1025,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="27" customHeight="1" s="25">
+    <row r="15" ht="27" customHeight="1" s="28">
       <c r="A15" s="14" t="inlineStr">
         <is>
           <t>DR.APLC.001</t>
@@ -1040,7 +1052,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="27" customHeight="1" s="25">
+    <row r="16" ht="27" customHeight="1" s="28">
       <c r="A16" s="14" t="inlineStr">
         <is>
           <t>DR.APLC.001</t>
@@ -1067,7 +1079,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="27" customHeight="1" s="25">
+    <row r="17" ht="27" customHeight="1" s="28">
       <c r="A17" s="14" t="inlineStr">
         <is>
           <t>DR.APLC.001</t>
@@ -1094,7 +1106,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="40.5" customHeight="1" s="25">
+    <row r="18" ht="40.5" customHeight="1" s="28">
       <c r="A18" s="14" t="inlineStr">
         <is>
           <t>DR.APLC.001</t>
@@ -1122,18 +1134,18 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="28" t="n"/>
-      <c r="B19" s="28" t="n"/>
-      <c r="C19" s="28" t="n"/>
-      <c r="D19" s="28" t="n"/>
-      <c r="E19" s="28" t="n"/>
+      <c r="A19" s="30" t="n"/>
+      <c r="B19" s="30" t="n"/>
+      <c r="C19" s="30" t="n"/>
+      <c r="D19" s="30" t="n"/>
+      <c r="E19" s="30" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="28" t="n"/>
-      <c r="B20" s="28" t="n"/>
-      <c r="C20" s="28" t="n"/>
-      <c r="D20" s="28" t="n"/>
-      <c r="E20" s="28" t="n"/>
+      <c r="A20" s="30" t="n"/>
+      <c r="B20" s="30" t="n"/>
+      <c r="C20" s="30" t="n"/>
+      <c r="D20" s="30" t="n"/>
+      <c r="E20" s="30" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="14" t="n"/>
@@ -1143,70 +1155,70 @@
       <c r="E21" s="14" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="31" t="inlineStr">
+      <c r="A22" s="33" t="inlineStr">
         <is>
           <t>填写说明</t>
         </is>
       </c>
-      <c r="B22" s="21" t="n"/>
-      <c r="C22" s="21" t="n"/>
-      <c r="D22" s="21" t="n"/>
-      <c r="E22" s="22" t="n"/>
-    </row>
-    <row r="23" ht="27.95" customHeight="1" s="25">
+      <c r="B22" s="22" t="n"/>
+      <c r="C22" s="22" t="n"/>
+      <c r="D22" s="22" t="n"/>
+      <c r="E22" s="23" t="n"/>
+    </row>
+    <row r="23" ht="27.95" customHeight="1" s="28">
       <c r="A23" s="12" t="inlineStr">
         <is>
           <t>DR编号</t>
         </is>
       </c>
-      <c r="B23" s="29" t="inlineStr">
+      <c r="B23" s="31" t="inlineStr">
         <is>
           <t>应包含’ OR-DR’ sheet中的全部DR；DR-FL可以一对多，也可以多对一； DR编号可以不是顺序的</t>
         </is>
       </c>
-      <c r="C23" s="21" t="n"/>
-      <c r="D23" s="21" t="n"/>
-      <c r="E23" s="22" t="n"/>
-    </row>
-    <row r="24" ht="60" customHeight="1" s="25">
+      <c r="C23" s="22" t="n"/>
+      <c r="D23" s="22" t="n"/>
+      <c r="E23" s="23" t="n"/>
+    </row>
+    <row r="24" ht="60" customHeight="1" s="28">
       <c r="A24" s="12" t="inlineStr">
         <is>
           <t>Feature类别</t>
         </is>
       </c>
-      <c r="B24" s="27" t="inlineStr">
+      <c r="B24" s="29" t="inlineStr">
         <is>
           <t>Feature类别包括但不限于：  
 CLK, Reset, Register, 数据接口，控制接口，配置接口，工作模式，中断，异常，低功耗，性能，DFX, memory map  
 可以重复（例如不同行的Feature类别是相同的）</t>
         </is>
       </c>
-      <c r="C24" s="21" t="n"/>
-      <c r="D24" s="21" t="n"/>
-      <c r="E24" s="22" t="n"/>
-    </row>
-    <row r="25" ht="42.95" customHeight="1" s="25">
+      <c r="C24" s="22" t="n"/>
+      <c r="D24" s="22" t="n"/>
+      <c r="E24" s="23" t="n"/>
+    </row>
+    <row r="25" ht="42.95" customHeight="1" s="28">
       <c r="A25" s="12" t="inlineStr">
         <is>
           <t>FL编号</t>
         </is>
       </c>
-      <c r="B25" s="29" t="inlineStr">
+      <c r="B25" s="31" t="inlineStr">
         <is>
           <t>FL_xxx_yyy：其中xxx是Feature类别的编号，yyy是二级feature的编号；</t>
         </is>
       </c>
-      <c r="C25" s="21" t="n"/>
-      <c r="D25" s="21" t="n"/>
-      <c r="E25" s="22" t="n"/>
-    </row>
-    <row r="26" ht="66.95" customHeight="1" s="25">
+      <c r="C25" s="22" t="n"/>
+      <c r="D25" s="22" t="n"/>
+      <c r="E25" s="23" t="n"/>
+    </row>
+    <row r="26" ht="66.95" customHeight="1" s="28">
       <c r="A26" s="12" t="inlineStr">
         <is>
           <t>Feature描述</t>
         </is>
       </c>
-      <c r="B26" s="27" t="inlineStr">
+      <c r="B26" s="29" t="inlineStr">
         <is>
           <t>1. 不要照抄DR的内容，需进行细化  
 2. 要清晰明确，不能有模棱两可的内容  
@@ -1214,24 +1226,24 @@
 4. 和Design SPEC的配合关系：Feature描述特性，SPEC描述实现方案</t>
         </is>
       </c>
-      <c r="C26" s="21" t="n"/>
-      <c r="D26" s="21" t="n"/>
-      <c r="E26" s="22" t="n"/>
-    </row>
-    <row r="27" ht="29.1" customHeight="1" s="25">
+      <c r="C26" s="22" t="n"/>
+      <c r="D26" s="22" t="n"/>
+      <c r="E26" s="23" t="n"/>
+    </row>
+    <row r="27" ht="29.1" customHeight="1" s="28">
       <c r="A27" s="12" t="inlineStr">
         <is>
           <t>TP编号</t>
         </is>
       </c>
-      <c r="B27" s="29" t="inlineStr">
+      <c r="B27" s="31" t="inlineStr">
         <is>
           <t>由DV owner填完FL-TP sheet后反标过来</t>
         </is>
       </c>
-      <c r="C27" s="21" t="n"/>
-      <c r="D27" s="21" t="n"/>
-      <c r="E27" s="22" t="n"/>
+      <c r="C27" s="22" t="n"/>
+      <c r="D27" s="22" t="n"/>
+      <c r="E27" s="23" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="0" t="n"/>
@@ -1382,70 +1394,70 @@
   <dimension ref="A1:F28"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col width="12.375" customWidth="1" style="25" min="1" max="1"/>
-    <col width="13.5" customWidth="1" style="25" min="2" max="2"/>
-    <col width="12.625" customWidth="1" style="25" min="3" max="3"/>
-    <col width="98.375" customWidth="1" style="25" min="4" max="4"/>
-    <col width="13.875" customWidth="1" style="25" min="5" max="5"/>
-    <col width="15.75" customWidth="1" style="25" min="6" max="6"/>
+    <col width="12.375" customWidth="1" style="28" min="1" max="1"/>
+    <col width="13.5" customWidth="1" style="28" min="2" max="2"/>
+    <col width="12.625" customWidth="1" style="28" min="3" max="3"/>
+    <col width="98.375" customWidth="1" style="28" min="4" max="4"/>
+    <col width="13.875" customWidth="1" style="28" min="5" max="5"/>
+    <col width="15.75" customWidth="1" style="28" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26.1" customHeight="1" s="25">
-      <c r="A1" s="30" t="inlineStr">
+    <row r="1" ht="26.1" customHeight="1" s="28">
+      <c r="A1" s="32" t="inlineStr">
         <is>
           <t>TestPoint分解表格</t>
         </is>
       </c>
-      <c r="B1" s="21" t="n"/>
-      <c r="C1" s="21" t="n"/>
-      <c r="D1" s="21" t="n"/>
-      <c r="E1" s="21" t="n"/>
-      <c r="F1" s="22" t="n"/>
-    </row>
-    <row r="2" ht="29.1" customHeight="1" s="25">
-      <c r="A2" s="23" t="inlineStr">
+      <c r="B1" s="22" t="n"/>
+      <c r="C1" s="22" t="n"/>
+      <c r="D1" s="22" t="n"/>
+      <c r="E1" s="22" t="n"/>
+      <c r="F1" s="23" t="n"/>
+    </row>
+    <row r="2" ht="29.1" customHeight="1" s="28">
+      <c r="A2" s="24" t="inlineStr">
         <is>
           <t>Feature编号</t>
         </is>
       </c>
-      <c r="B2" s="23" t="inlineStr">
+      <c r="B2" s="24" t="inlineStr">
         <is>
           <t>TP类别</t>
         </is>
       </c>
-      <c r="C2" s="23" t="inlineStr">
+      <c r="C2" s="24" t="inlineStr">
         <is>
           <t>TP编号</t>
         </is>
       </c>
-      <c r="D2" s="23" t="inlineStr">
+      <c r="D2" s="24" t="inlineStr">
         <is>
           <t>TP描述</t>
         </is>
       </c>
-      <c r="E2" s="23" t="inlineStr">
+      <c r="E2" s="24" t="inlineStr">
         <is>
           <t>checker编号</t>
         </is>
       </c>
-      <c r="F2" s="23" t="inlineStr">
+      <c r="F2" s="24" t="inlineStr">
         <is>
           <t>Testcase编号</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="40.5" customHeight="1" s="25">
-      <c r="A3" s="32" t="inlineStr">
+    <row r="3" ht="40.5" customHeight="1" s="28">
+      <c r="A3" s="21" t="inlineStr">
         <is>
           <t>FL_001_001</t>
         </is>
       </c>
-      <c r="B3" s="32" t="inlineStr">
+      <c r="B3" s="21" t="inlineStr">
         <is>
           <t>时钟</t>
         </is>
       </c>
-      <c r="C3" s="32" t="inlineStr">
+      <c r="C3" s="21" t="inlineStr">
         <is>
           <t>TP_001</t>
         </is>
@@ -1457,29 +1469,29 @@
 期望：所有命令在100MHz频率下正确执行，协议采样、状态机控制和AHB-Lite主接口同域工作正常。</t>
         </is>
       </c>
-      <c r="E3" s="32" t="inlineStr">
+      <c r="E3" s="21" t="inlineStr">
         <is>
           <t>CHK_001</t>
         </is>
       </c>
-      <c r="F3" s="32" t="inlineStr">
+      <c r="F3" s="21" t="inlineStr">
         <is>
           <t>TC_001</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="54" customHeight="1" s="25">
-      <c r="A4" s="32" t="inlineStr">
+    <row r="4" ht="54" customHeight="1" s="28">
+      <c r="A4" s="21" t="inlineStr">
         <is>
           <t>FL_002_001</t>
         </is>
       </c>
-      <c r="B4" s="32" t="inlineStr">
+      <c r="B4" s="21" t="inlineStr">
         <is>
           <t>复位</t>
         </is>
       </c>
-      <c r="C4" s="32" t="inlineStr">
+      <c r="C4" s="21" t="inlineStr">
         <is>
           <t>TP_002</t>
         </is>
@@ -1491,29 +1503,29 @@
 期望：复位后状态机处于IDLE，CTRL寄存器默认值正确，STATUS/LAST_ERR清零，无残留状态。</t>
         </is>
       </c>
-      <c r="E4" s="32" t="inlineStr">
+      <c r="E4" s="21" t="inlineStr">
         <is>
           <t>CHK_002</t>
         </is>
       </c>
-      <c r="F4" s="32" t="inlineStr">
+      <c r="F4" s="21" t="inlineStr">
         <is>
           <t>TC_002</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="54" customHeight="1" s="25">
-      <c r="A5" s="32" t="inlineStr">
+    <row r="5" ht="54" customHeight="1" s="28">
+      <c r="A5" s="21" t="inlineStr">
         <is>
           <t>FL_003_001</t>
         </is>
       </c>
-      <c r="B5" s="32" t="inlineStr">
+      <c r="B5" s="21" t="inlineStr">
         <is>
           <t>寄存器</t>
         </is>
       </c>
-      <c r="C5" s="32" t="inlineStr">
+      <c r="C5" s="21" t="inlineStr">
         <is>
           <t>TP_003</t>
         </is>
@@ -1525,29 +1537,29 @@
 期望：CSR读写正确，VERSION返回预期值，CTRL配置生效，STATUS/LAST_ERR反映正确状态。</t>
         </is>
       </c>
-      <c r="E5" s="32" t="inlineStr">
+      <c r="E5" s="21" t="inlineStr">
         <is>
           <t>CHK_003</t>
         </is>
       </c>
-      <c r="F5" s="32" t="inlineStr">
+      <c r="F5" s="21" t="inlineStr">
         <is>
           <t>TC_003</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="54" customHeight="1" s="25">
-      <c r="A6" s="32" t="inlineStr">
+    <row r="6" ht="54" customHeight="1" s="28">
+      <c r="A6" s="21" t="inlineStr">
         <is>
           <t>FL_004_001</t>
         </is>
       </c>
-      <c r="B6" s="32" t="inlineStr">
+      <c r="B6" s="21" t="inlineStr">
         <is>
           <t>工作模式</t>
         </is>
       </c>
-      <c r="C6" s="32" t="inlineStr">
+      <c r="C6" s="21" t="inlineStr">
         <is>
           <t>TP_004</t>
         </is>
@@ -1559,29 +1571,29 @@
 期望：模块正确执行功能命令，协议采用半双工模式，CSR访问与AHB-Lite单次读写正常。</t>
         </is>
       </c>
-      <c r="E6" s="32" t="inlineStr">
+      <c r="E6" s="21" t="inlineStr">
         <is>
           <t>CHK_004</t>
         </is>
       </c>
-      <c r="F6" s="32" t="inlineStr">
+      <c r="F6" s="21" t="inlineStr">
         <is>
           <t>TC_004</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="54" customHeight="1" s="25">
-      <c r="A7" s="32" t="inlineStr">
+    <row r="7" ht="54" customHeight="1" s="28">
+      <c r="A7" s="21" t="inlineStr">
         <is>
           <t>FL_004_002</t>
         </is>
       </c>
-      <c r="B7" s="32" t="inlineStr">
+      <c r="B7" s="21" t="inlineStr">
         <is>
           <t>工作模式</t>
         </is>
       </c>
-      <c r="C7" s="32" t="inlineStr">
+      <c r="C7" s="21" t="inlineStr">
         <is>
           <t>TP_005</t>
         </is>
@@ -1593,29 +1605,29 @@
 期望：1-bit和4-bit模式正常工作，非法配置返回错误码，Burst和AXI功能确认不可用。</t>
         </is>
       </c>
-      <c r="E7" s="32" t="inlineStr">
-        <is>
-          <t>CHK_005</t>
-        </is>
-      </c>
-      <c r="F7" s="32" t="inlineStr">
-        <is>
-          <t>TC_005</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="54" customHeight="1" s="25">
-      <c r="A8" s="32" t="inlineStr">
+      <c r="E7" s="21" t="inlineStr">
+        <is>
+          <t>CHK_004</t>
+        </is>
+      </c>
+      <c r="F7" s="21" t="inlineStr">
+        <is>
+          <t>TC_004</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="54" customHeight="1" s="28">
+      <c r="A8" s="21" t="inlineStr">
         <is>
           <t>FL_005_001</t>
         </is>
       </c>
-      <c r="B8" s="32" t="inlineStr">
+      <c r="B8" s="21" t="inlineStr">
         <is>
           <t>数据接口</t>
         </is>
       </c>
-      <c r="C8" s="32" t="inlineStr">
+      <c r="C8" s="21" t="inlineStr">
         <is>
           <t>TP_006</t>
         </is>
@@ -1627,29 +1639,29 @@
 期望：数据接口按lane模式正确传输，帧边界清晰，MSB first顺序正确。</t>
         </is>
       </c>
-      <c r="E8" s="32" t="inlineStr">
-        <is>
-          <t>CHK_006</t>
-        </is>
-      </c>
-      <c r="F8" s="32" t="inlineStr">
-        <is>
-          <t>TC_006</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="54" customHeight="1" s="25">
-      <c r="A9" s="32" t="inlineStr">
+      <c r="E8" s="21" t="inlineStr">
+        <is>
+          <t>CHK_005</t>
+        </is>
+      </c>
+      <c r="F8" s="21" t="inlineStr">
+        <is>
+          <t>TC_005</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="54" customHeight="1" s="28">
+      <c r="A9" s="21" t="inlineStr">
         <is>
           <t>FL_005_002</t>
         </is>
       </c>
-      <c r="B9" s="32" t="inlineStr">
+      <c r="B9" s="21" t="inlineStr">
         <is>
           <t>数据接口</t>
         </is>
       </c>
-      <c r="C9" s="32" t="inlineStr">
+      <c r="C9" s="21" t="inlineStr">
         <is>
           <t>TP_007</t>
         </is>
@@ -1661,29 +1673,29 @@
 期望：请求/响应阶段正确分离，turnaround固定1周期，协议字段MSB first传输，四种帧格式正确处理。</t>
         </is>
       </c>
-      <c r="E9" s="32" t="inlineStr">
-        <is>
-          <t>CHK_007</t>
-        </is>
-      </c>
-      <c r="F9" s="32" t="inlineStr">
-        <is>
-          <t>TC_007</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="54" customHeight="1" s="25">
-      <c r="A10" s="32" t="inlineStr">
+      <c r="E9" s="21" t="inlineStr">
+        <is>
+          <t>CHK_005</t>
+        </is>
+      </c>
+      <c r="F9" s="21" t="inlineStr">
+        <is>
+          <t>TC_006</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="54" customHeight="1" s="28">
+      <c r="A10" s="21" t="inlineStr">
         <is>
           <t>FL_006_001</t>
         </is>
       </c>
-      <c r="B10" s="32" t="inlineStr">
+      <c r="B10" s="21" t="inlineStr">
         <is>
           <t>控制接口</t>
         </is>
       </c>
-      <c r="C10" s="32" t="inlineStr">
+      <c r="C10" s="21" t="inlineStr">
         <is>
           <t>TP_008</t>
         </is>
@@ -1695,29 +1707,29 @@
 期望：四种opcode正确译码并执行，非法opcode返回STS_BAD_OPCODE(0x01)，前端正确确定期望帧长。</t>
         </is>
       </c>
-      <c r="E10" s="32" t="inlineStr">
-        <is>
-          <t>CHK_008</t>
-        </is>
-      </c>
-      <c r="F10" s="32" t="inlineStr">
-        <is>
-          <t>TC_008</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="67.5" customHeight="1" s="25">
-      <c r="A11" s="32" t="inlineStr">
+      <c r="E10" s="21" t="inlineStr">
+        <is>
+          <t>CHK_006</t>
+        </is>
+      </c>
+      <c r="F10" s="21" t="inlineStr">
+        <is>
+          <t>TC_007</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="67.5" customHeight="1" s="28">
+      <c r="A11" s="21" t="inlineStr">
         <is>
           <t>FL_007_001</t>
         </is>
       </c>
-      <c r="B11" s="32" t="inlineStr">
+      <c r="B11" s="21" t="inlineStr">
         <is>
           <t>配置接口</t>
         </is>
       </c>
-      <c r="C11" s="32" t="inlineStr">
+      <c r="C11" s="21" t="inlineStr">
         <is>
           <t>TP_009</t>
         </is>
@@ -1729,29 +1741,29 @@
 期望：CTRL配置正确生效，使能/禁用状态切换正确，软复位功能正常。</t>
         </is>
       </c>
-      <c r="E11" s="32" t="inlineStr">
-        <is>
-          <t>CHK_009</t>
-        </is>
-      </c>
-      <c r="F11" s="32" t="inlineStr">
-        <is>
-          <t>TC_009</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="54" customHeight="1" s="25">
-      <c r="A12" s="32" t="inlineStr">
+      <c r="E11" s="21" t="inlineStr">
+        <is>
+          <t>CHK_007</t>
+        </is>
+      </c>
+      <c r="F11" s="21" t="inlineStr">
+        <is>
+          <t>TC_008</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="54" customHeight="1" s="28">
+      <c r="A12" s="21" t="inlineStr">
         <is>
           <t>FL_008_001</t>
         </is>
       </c>
-      <c r="B12" s="32" t="inlineStr">
+      <c r="B12" s="21" t="inlineStr">
         <is>
           <t>中断</t>
         </is>
       </c>
-      <c r="C12" s="32" t="inlineStr">
+      <c r="C12" s="21" t="inlineStr">
         <is>
           <t>TP_010</t>
         </is>
@@ -1763,29 +1775,29 @@
 期望：所有错误与完成状态通过STATUS/LAST_ERR查询获取，MVP版本无中断输出，ATE轮询方式正确获取状态。</t>
         </is>
       </c>
-      <c r="E12" s="32" t="inlineStr">
-        <is>
-          <t>CHK_010</t>
-        </is>
-      </c>
-      <c r="F12" s="32" t="inlineStr">
-        <is>
-          <t>TC_010</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="81" customHeight="1" s="25">
-      <c r="A13" s="32" t="inlineStr">
+      <c r="E12" s="21" t="inlineStr">
+        <is>
+          <t>CHK_008</t>
+        </is>
+      </c>
+      <c r="F12" s="21" t="inlineStr">
+        <is>
+          <t>TC_009</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="81" customHeight="1" s="28">
+      <c r="A13" s="21" t="inlineStr">
         <is>
           <t>FL_009_001</t>
         </is>
       </c>
-      <c r="B13" s="32" t="inlineStr">
+      <c r="B13" s="21" t="inlineStr">
         <is>
           <t>异常</t>
         </is>
       </c>
-      <c r="C13" s="32" t="inlineStr">
+      <c r="C13" s="21" t="inlineStr">
         <is>
           <t>TP_011</t>
         </is>
@@ -1797,29 +1809,29 @@
 期望：各类错误正确检测，在发起AHB访问前完成前置错误收敛，返回确定性状态码，LAST_ERR更新正确。</t>
         </is>
       </c>
-      <c r="E13" s="32" t="inlineStr">
-        <is>
-          <t>CHK_011</t>
-        </is>
-      </c>
-      <c r="F13" s="32" t="inlineStr">
-        <is>
-          <t>TC_011</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="54" customHeight="1" s="25">
-      <c r="A14" s="32" t="inlineStr">
+      <c r="E13" s="21" t="inlineStr">
+        <is>
+          <t>CHK_009</t>
+        </is>
+      </c>
+      <c r="F13" s="21" t="inlineStr">
+        <is>
+          <t>TC_010</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="54" customHeight="1" s="28">
+      <c r="A14" s="21" t="inlineStr">
         <is>
           <t>FL_010_001</t>
         </is>
       </c>
-      <c r="B14" s="32" t="inlineStr">
+      <c r="B14" s="21" t="inlineStr">
         <is>
           <t>低功耗</t>
         </is>
       </c>
-      <c r="C14" s="32" t="inlineStr">
+      <c r="C14" s="21" t="inlineStr">
         <is>
           <t>TP_012</t>
         </is>
@@ -1831,29 +1843,29 @@
 期望：空闲态无效翻转最小化，低功耗设计目标满足，功耗测试通过。</t>
         </is>
       </c>
-      <c r="E14" s="32" t="inlineStr">
-        <is>
-          <t>CHK_012</t>
-        </is>
-      </c>
-      <c r="F14" s="32" t="inlineStr">
-        <is>
-          <t>TC_012</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="67.5" customHeight="1" s="25">
-      <c r="A15" s="32" t="inlineStr">
+      <c r="E14" s="21" t="inlineStr">
+        <is>
+          <t>CHK_010</t>
+        </is>
+      </c>
+      <c r="F14" s="21" t="inlineStr">
+        <is>
+          <t>TC_011</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="67.5" customHeight="1" s="28">
+      <c r="A15" s="21" t="inlineStr">
         <is>
           <t>FL_011_001</t>
         </is>
       </c>
-      <c r="B15" s="32" t="inlineStr">
+      <c r="B15" s="21" t="inlineStr">
         <is>
           <t>性能</t>
         </is>
       </c>
-      <c r="C15" s="32" t="inlineStr">
+      <c r="C15" s="21" t="inlineStr">
         <is>
           <t>TP_013</t>
         </is>
@@ -1865,29 +1877,29 @@
 期望：目标频率100MHz稳定工作，延时符合预期(约23~24 cycles)，吞吐率达标，AHB访问约束满足。</t>
         </is>
       </c>
-      <c r="E15" s="32" t="inlineStr">
-        <is>
-          <t>CHK_013</t>
-        </is>
-      </c>
-      <c r="F15" s="32" t="inlineStr">
-        <is>
-          <t>TC_013</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="54" customHeight="1" s="25">
-      <c r="A16" s="32" t="inlineStr">
+      <c r="E15" s="21" t="inlineStr">
+        <is>
+          <t>CHK_011</t>
+        </is>
+      </c>
+      <c r="F15" s="21" t="inlineStr">
+        <is>
+          <t>TC_012</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="54" customHeight="1" s="28">
+      <c r="A16" s="21" t="inlineStr">
         <is>
           <t>FL_012_001</t>
         </is>
       </c>
-      <c r="B16" s="32" t="inlineStr">
+      <c r="B16" s="21" t="inlineStr">
         <is>
           <t>DFX</t>
         </is>
       </c>
-      <c r="C16" s="32" t="inlineStr">
+      <c r="C16" s="21" t="inlineStr">
         <is>
           <t>TP_014</t>
         </is>
@@ -1899,29 +1911,29 @@
 期望：所有调试可观测点可采集，便于联调、波形定位和故障复现。</t>
         </is>
       </c>
-      <c r="E16" s="32" t="inlineStr">
-        <is>
-          <t>CHK_014</t>
-        </is>
-      </c>
-      <c r="F16" s="32" t="inlineStr">
-        <is>
-          <t>TC_014</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="67.5" customHeight="1" s="25">
-      <c r="A17" s="32" t="inlineStr">
+      <c r="E16" s="21" t="inlineStr">
+        <is>
+          <t>CHK_012</t>
+        </is>
+      </c>
+      <c r="F16" s="21" t="inlineStr">
+        <is>
+          <t>TC_013</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="67.5" customHeight="1" s="28">
+      <c r="A17" s="21" t="inlineStr">
         <is>
           <t>FL_013_001</t>
         </is>
       </c>
-      <c r="B17" s="32" t="inlineStr">
+      <c r="B17" s="21" t="inlineStr">
         <is>
           <t>Memory map</t>
         </is>
       </c>
-      <c r="C17" s="32" t="inlineStr">
+      <c r="C17" s="21" t="inlineStr">
         <is>
           <t>TP_015</t>
         </is>
@@ -1933,29 +1945,29 @@
 期望：CSR通过协议命令访问正常，AHB Master访问正确，地址空间约束满足。</t>
         </is>
       </c>
-      <c r="E17" s="32" t="inlineStr">
-        <is>
-          <t>CHK_015</t>
-        </is>
-      </c>
-      <c r="F17" s="32" t="inlineStr">
-        <is>
-          <t>TC_015</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="67.5" customHeight="1" s="25">
-      <c r="A18" s="32" t="inlineStr">
+      <c r="E17" s="21" t="inlineStr">
+        <is>
+          <t>CHK_013</t>
+        </is>
+      </c>
+      <c r="F17" s="21" t="inlineStr">
+        <is>
+          <t>TC_014</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="67.5" customHeight="1" s="28">
+      <c r="A18" s="21" t="inlineStr">
         <is>
           <t>FL_014_001</t>
         </is>
       </c>
-      <c r="B18" s="32" t="inlineStr">
+      <c r="B18" s="21" t="inlineStr">
         <is>
           <t>总线接口</t>
         </is>
       </c>
-      <c r="C18" s="32" t="inlineStr">
+      <c r="C18" s="21" t="inlineStr">
         <is>
           <t>TP_016</t>
         </is>
@@ -1967,57 +1979,60 @@
 期望：AHB-Lite Master接口符合规范，单次读写事务正确，信号时序满足AHB协议要求。</t>
         </is>
       </c>
-      <c r="E18" s="32" t="inlineStr">
-        <is>
-          <t>CHK_016</t>
-        </is>
-      </c>
-      <c r="F18" s="32" t="inlineStr">
-        <is>
-          <t>TC_016</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="24" customHeight="1" s="25">
-      <c r="A19" s="32" t="n"/>
-      <c r="B19" s="32" t="n"/>
-      <c r="C19" s="32" t="n"/>
+      <c r="E18" s="21" t="inlineStr">
+        <is>
+          <t>CHK_014</t>
+        </is>
+      </c>
+      <c r="F18" s="21" t="inlineStr">
+        <is>
+          <t>TC_015</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="24" customHeight="1" s="28">
+      <c r="A19" s="21" t="n"/>
+      <c r="B19" s="21" t="n"/>
+      <c r="C19" s="21" t="n"/>
       <c r="D19" s="4" t="n"/>
-      <c r="E19" s="32" t="n"/>
-      <c r="F19" s="32" t="n"/>
-    </row>
+      <c r="E19" s="21" t="n"/>
+      <c r="F19" s="21" t="n"/>
+    </row>
+    <row r="20"/>
+    <row r="21"/>
+    <row r="22"/>
     <row r="23">
-      <c r="A23" s="24" t="inlineStr">
+      <c r="A23" s="27" t="inlineStr">
         <is>
           <t>填写说明</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="54.95" customHeight="1" s="25">
-      <c r="A24" s="32" t="inlineStr">
+    <row r="24" ht="54.95" customHeight="1" s="28">
+      <c r="A24" s="21" t="inlineStr">
         <is>
           <t>Feature编号</t>
         </is>
       </c>
-      <c r="B24" s="27" t="inlineStr">
+      <c r="B24" s="29" t="inlineStr">
         <is>
           <t>1. 应包含’ DR-FL’ sheet中的全部feature;
 2. Feature-TP可以一对多，也可以多对一！
 3. Feature编号可以不是顺序的</t>
         </is>
       </c>
-      <c r="C24" s="21" t="n"/>
-      <c r="D24" s="21" t="n"/>
-      <c r="E24" s="21" t="n"/>
-      <c r="F24" s="22" t="n"/>
-    </row>
-    <row r="25" ht="71.09999999999999" customHeight="1" s="25">
-      <c r="A25" s="32" t="inlineStr">
+      <c r="C24" s="22" t="n"/>
+      <c r="D24" s="22" t="n"/>
+      <c r="E24" s="22" t="n"/>
+      <c r="F24" s="23" t="n"/>
+    </row>
+    <row r="25" ht="71.09999999999999" customHeight="1" s="28">
+      <c r="A25" s="21" t="inlineStr">
         <is>
           <t>TP类别</t>
         </is>
       </c>
-      <c r="B25" s="27" t="inlineStr">
+      <c r="B25" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">1.TestPoint类别包括但不限于：
 CLK，Reset，Register，数据接口，控制接口，配置接口，工作模式，中断，异常，低功耗，性能，DFX、设备兼容性
@@ -2026,59 +2041,59 @@
 </t>
         </is>
       </c>
-      <c r="C25" s="21" t="n"/>
-      <c r="D25" s="21" t="n"/>
-      <c r="E25" s="21" t="n"/>
-      <c r="F25" s="22" t="n"/>
-    </row>
-    <row r="26" ht="45.95" customHeight="1" s="25">
-      <c r="A26" s="32" t="inlineStr">
+      <c r="C25" s="22" t="n"/>
+      <c r="D25" s="22" t="n"/>
+      <c r="E25" s="22" t="n"/>
+      <c r="F25" s="23" t="n"/>
+    </row>
+    <row r="26" ht="45.95" customHeight="1" s="28">
+      <c r="A26" s="21" t="inlineStr">
         <is>
           <t>TP编号</t>
         </is>
       </c>
-      <c r="B26" s="27" t="inlineStr">
+      <c r="B26" s="29" t="inlineStr">
         <is>
           <t>1. 所有FL编号必须要有对应的TP编号。如无，要重点解释说明  
 2. 允许TP编号没有对应的FL编号，即允许TP比FL多（例如’设备兼容性’这类TP）</t>
         </is>
       </c>
-      <c r="C26" s="21" t="n"/>
-      <c r="D26" s="21" t="n"/>
-      <c r="E26" s="21" t="n"/>
-      <c r="F26" s="22" t="n"/>
-    </row>
-    <row r="27" ht="38.1" customHeight="1" s="25">
-      <c r="A27" s="32" t="inlineStr">
+      <c r="C26" s="22" t="n"/>
+      <c r="D26" s="22" t="n"/>
+      <c r="E26" s="22" t="n"/>
+      <c r="F26" s="23" t="n"/>
+    </row>
+    <row r="27" ht="38.1" customHeight="1" s="28">
+      <c r="A27" s="21" t="inlineStr">
         <is>
           <t>Testcase编号</t>
         </is>
       </c>
-      <c r="B27" s="29" t="inlineStr">
+      <c r="B27" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve"> 如果多个Testcase都可以cover同一个TP，写一个即可</t>
         </is>
       </c>
-      <c r="C27" s="21" t="n"/>
-      <c r="D27" s="21" t="n"/>
-      <c r="E27" s="21" t="n"/>
-      <c r="F27" s="22" t="n"/>
-    </row>
-    <row r="28" ht="41.1" customHeight="1" s="25">
-      <c r="A28" s="32" t="inlineStr">
+      <c r="C27" s="22" t="n"/>
+      <c r="D27" s="22" t="n"/>
+      <c r="E27" s="22" t="n"/>
+      <c r="F27" s="23" t="n"/>
+    </row>
+    <row r="28" ht="41.1" customHeight="1" s="28">
+      <c r="A28" s="21" t="inlineStr">
         <is>
           <t>Checker编号</t>
         </is>
       </c>
-      <c r="B28" s="29" t="inlineStr">
+      <c r="B28" s="31" t="inlineStr">
         <is>
           <t>可以重复</t>
         </is>
       </c>
-      <c r="C28" s="21" t="n"/>
-      <c r="D28" s="21" t="n"/>
-      <c r="E28" s="21" t="n"/>
-      <c r="F28" s="22" t="n"/>
+      <c r="C28" s="22" t="n"/>
+      <c r="D28" s="22" t="n"/>
+      <c r="E28" s="22" t="n"/>
+      <c r="F28" s="23" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -2100,476 +2115,473 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D40"/>
+  <dimension ref="A1:M21"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col width="18.875" customWidth="1" style="25" min="1" max="1"/>
-    <col width="19.25" customWidth="1" style="25" min="2" max="2"/>
-    <col width="50.25" customWidth="1" style="25" min="3" max="3"/>
-    <col width="35.125" customWidth="1" style="25" min="4" max="4"/>
+    <col width="12" customWidth="1" style="28" min="1" max="1"/>
+    <col width="25" customWidth="1" style="28" min="2" max="2"/>
+    <col width="80" customWidth="1" style="28" min="3" max="3"/>
+    <col width="15" customWidth="1" style="28" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="30" t="inlineStr">
+      <c r="A1" s="32" t="inlineStr">
         <is>
           <t>Checker List</t>
         </is>
       </c>
-      <c r="B1" s="21" t="n"/>
-      <c r="C1" s="21" t="n"/>
-      <c r="D1" s="22" t="n"/>
+      <c r="B1" s="22" t="n"/>
+      <c r="C1" s="22" t="n"/>
+      <c r="D1" s="23" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="23" t="inlineStr">
+      <c r="A2" s="24" t="inlineStr">
         <is>
           <t>CHK编号</t>
         </is>
       </c>
-      <c r="B2" s="23" t="inlineStr">
+      <c r="B2" s="24" t="inlineStr">
         <is>
           <t>CHK Name</t>
         </is>
       </c>
-      <c r="C2" s="23" t="inlineStr">
+      <c r="C2" s="24" t="inlineStr">
         <is>
           <t>CHK描述</t>
         </is>
       </c>
-      <c r="D2" s="23" t="inlineStr">
+      <c r="D2" s="24" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="32" t="inlineStr">
+      <c r="A3" s="21" t="inlineStr">
         <is>
           <t>CHK_001</t>
         </is>
       </c>
-      <c r="B3" s="32" t="inlineStr">
-        <is>
-          <t>freq_checker</t>
-        </is>
-      </c>
-      <c r="C3" s="6" t="inlineStr">
-        <is>
-          <t>检查频率值是否正确：连续采集clk_i上升沿和下降沿并计算实际频率/周期，判断是否处于100MHz目标频率的允许误差范围内（±3%）；检查时钟稳定性：通过连续采样周期，对比相邻两个周期的频率偏差是否在3%内。</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="n"/>
+      <c r="B3" s="21" t="inlineStr">
+        <is>
+          <t>clk_freq_checker</t>
+        </is>
+      </c>
+      <c r="C3" s="36" t="inlineStr">
+        <is>
+          <t>检查clk_i时钟频率和稳定性：
+1.频率检查：连续采集clk_i上升沿和下降沿，计算实际频率/周期，判断是否处于目标频率100MHz的允许误差范围内（±1%）；
+2.稳定性检查：通过连续采样周期，对比相邻两个周期的频率偏差是否在3%内；
+3.时钟域同步：验证协议采样、状态机控制和AHB-Lite主接口均在clk_i上升沿同步工作。</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>覆盖TP_001</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="32" t="inlineStr">
+      <c r="A4" s="21" t="inlineStr">
         <is>
           <t>CHK_002</t>
         </is>
       </c>
       <c r="B4" s="18" t="inlineStr">
         <is>
-          <t>rst_checker</t>
-        </is>
-      </c>
-      <c r="C4" s="17" t="inlineStr">
-        <is>
-          <t>检查复位connectivity：是否正确连接至模块并生效；包含主要复位信号：rst_ni负责模块的全局复位，复位后状态机回到IDLE，CTRL.EN=0，LANE_MODE=01(1-bit默认值)，清空协议/响应上下文和错误状态。</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="n"/>
+          <t>reset_checker</t>
+        </is>
+      </c>
+      <c r="C4" s="37" t="inlineStr">
+        <is>
+          <t>检查rst_ni复位行为正确性：
+1.复位有效检查：rst_ni为低时，状态机应处于IDLE状态；
+2.复位释放检查：rst_ni释放后，验证内部同步释放机制；
+3.默认值检查：复位后CTRL.EN=0，CTRL.LANE_MODE=00(1-bit模式)；
+4.状态清零检查：复位后STATUS寄存器和LAST_ERR寄存器清零，协议上下文和错误状态已清空。</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>覆盖TP_002</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="32" t="inlineStr">
+      <c r="A5" s="21" t="inlineStr">
         <is>
           <t>CHK_003</t>
         </is>
       </c>
-      <c r="B5" s="32" t="inlineStr">
-        <is>
-          <t>regs_checker</t>
-        </is>
-      </c>
-      <c r="C5" s="6" t="inlineStr">
-        <is>
-          <t>九步法检测寄存器：包含默认值、读写属性、异常地址读写检查等；具体检查VERSION(只读)、CTRL(读写)、STATUS(只读)、LAST_ERR(只读)寄存器的访问属性和默认值。</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="n"/>
+      <c r="B5" s="21" t="inlineStr">
+        <is>
+          <t>csr_reg_checker</t>
+        </is>
+      </c>
+      <c r="C5" s="36" t="inlineStr">
+        <is>
+          <t>检查CSR寄存器读写正确性：
+1.VERSION寄存器：读取值应返回预期版本号；
+2.CTRL寄存器：EN、LANE_MODE、SOFT_RST字段读写正确，写入配置后读取值与写入一致；
+3.STATUS寄存器：busy位和sticky位反映正确状态；
+4.LAST_ERR寄存器：正确记录最近发生的错误码。</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>覆盖TP_003</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="32" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>CHK_004</t>
         </is>
       </c>
-      <c r="B6" s="32" t="inlineStr">
-        <is>
-          <t>status_checker</t>
-        </is>
-      </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>监测模块状态：STATUS.BUSY、STATUS.DONE、STATUS.ERR信号的复位初始状态、模式切换及正常输出的指示值是否正确；检查test_mode_i=1且CTRL.EN=1时模块处于测试使能状态，允许执行功能命令。</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="n"/>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>work_mode_checker</t>
+        </is>
+      </c>
+      <c r="C6" s="38" t="inlineStr">
+        <is>
+          <t>检查工作模式和lane模式配置正确性：
+1.使能检查：test_mode_i=1且CTRL.EN=1时，模块允许执行功能命令；
+2.lane模式检查：LANE_MODE=00时使用1-bit模式(pdi_i[0]/pdo_o[0])，LANE_MODE=01时使用4-bit模式(pdi_i[3:0]/pdo_o[3:0])；
+3.半双工检查：请求阶段由主机驱动pdi_i，响应阶段由模块驱动pdo_o，pdo_oe_o正确指示方向切换；
+4.不支持功能检查：验证Burst和AXI后端功能确认不可用。</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>覆盖TP_004, TP_005</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="12" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>CHK_005</t>
         </is>
       </c>
-      <c r="B7" s="12" t="inlineStr">
-        <is>
-          <t>protocol_checker</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>检查外部接口协议时序：1.帧边界检测：pcs_n_i定义帧起始和结束；2.数据传输时序：pdi_i[3:0]/pdo_o[3:0]在clk_i上升沿采样；3.方向控制：pdo_oe_o正确切换输入输出方向；4.协议字段：opcode、addr、data按MSB first传输；5.Lane模式：1-bit模式使用pdi_i[0]/pdo_o[0]，4-bit模式按高nibble优先发送。</t>
-        </is>
-      </c>
-      <c r="D7" s="14" t="n"/>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>data_interface_checker</t>
+        </is>
+      </c>
+      <c r="C7" s="38" t="inlineStr">
+        <is>
+          <t>检查数据接口时序和格式正确性：
+1.帧边界检查：pcs_n_i=1表示空闲，pcs_n_i拉低开启事务，pcs_n_i拉高结束事务；
+2.数据顺序检查：协议字段按MSB first传输；
+3.lane模式检查：1-bit模式使用bit0，4-bit模式按高nibble优先发送；
+4.turnaround检查：请求阶段与响应阶段之间固定插入1个clk_i周期的turnaround；
+5.方向控制检查：响应期间pdo_oe_o=1，非响应期间pdo_oe_o=0。</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>覆盖TP_006, TP_007</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="12" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>CHK_006</t>
         </is>
       </c>
-      <c r="B8" s="12" t="inlineStr">
-        <is>
-          <t>spi_protocol_checker</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>检查类SPI协议时序：1.帧边界检测：pcs_n_i拉低定义帧起始，拉高定义帧结束；2.数据传输时序：pdi_i[3:0]在clk_i上升沿采样作为输入数据，pdo_o[3:0]在clk_i上升沿更新作为输出数据；3.方向控制：pdo_oe_o在响应阶段为1(输出使能)，请求阶段为0；4.协议字段：opcode(8bit)、addr(32bit)、data(32bit)按MSB first传输。</t>
-        </is>
-      </c>
-      <c r="D8" s="14" t="n"/>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>opcode_checker</t>
+        </is>
+      </c>
+      <c r="C8" s="38" t="inlineStr">
+        <is>
+          <t>检查opcode译码正确性：
+1.合法opcode检查：0x10译码为WR_CSR，0x11译码为RD_CSR，0x20译码为AHB_WR32，0x21译码为AHB_RD32；
+2.帧长确定检查：前端收满8bit opcode后正确确定期望帧长；
+3.非法opcode检查：非法opcode(如0x00/0xFF)应返回STS_BAD_OPCODE(0x01)。</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>覆盖TP_008</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="12" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>CHK_007</t>
         </is>
       </c>
-      <c r="B9" s="12" t="inlineStr">
-        <is>
-          <t>timing_checker</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>检查turnaround时序：请求阶段结束后，固定1个clk_i周期turnaround，然后进入响应阶段；pdo_oe_o在turnaround周期后拉高，进入TX阶段输出status+rdata。</t>
-        </is>
-      </c>
-      <c r="D9" s="14" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="12" t="inlineStr">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>ctrl_config_checker</t>
+        </is>
+      </c>
+      <c r="C9" s="38" t="inlineStr">
+        <is>
+          <t>检查CTRL寄存器配置生效正确性：
+1.EN字段检查：CTRL.EN=1使能模块功能，CTRL.EN=0禁用模块；
+2.LANE_MODE字段检查：仅允许00=1-bit、01=4-bit，其他值应返回错误；
+3.SOFT_RST字段检查：SOFT_RST写1触发协议上下文清零并恢复默认lane模式(1-bit)；
+4.配置生效时序检查：配置在下一个事务生效。</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>覆盖TP_009</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="24" customHeight="1" s="28">
+      <c r="A10" t="inlineStr">
         <is>
           <t>CHK_008</t>
         </is>
       </c>
-      <c r="B10" s="12" t="inlineStr">
-        <is>
-          <t>opcode_checker</t>
-        </is>
-      </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>检查opcode译码正确性：1.正确译码：8'h10译码为WR_CSR命令，8'h11译码为RD_CSR命令，8'h20译码为AHB_WR32命令，8'h21译码为AHB_RD32命令；2.非法opcode检测：除0x10/0x11/0x20/0x21外的opcode值视为BAD_OPCODE，期望状态码0x01。</t>
-        </is>
-      </c>
-      <c r="D10" s="14" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="12" t="inlineStr">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>status_polling_checker</t>
+        </is>
+      </c>
+      <c r="C10" s="38" t="inlineStr">
+        <is>
+          <t>检查状态查询机制正确性：
+1.STATUS寄存器检查：busy位反映模块执行状态，sticky位记录历史错误；
+2.LAST_ERR寄存器检查：正确记录最近错误码(0x00~0x08)；
+3.无中断检查：MVP版本无独立中断输出，所有状态通过轮询获取。</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>覆盖TP_010</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="69.95" customHeight="1" s="28">
+      <c r="A11" t="inlineStr">
         <is>
           <t>CHK_009</t>
         </is>
       </c>
-      <c r="B11" s="12" t="inlineStr">
-        <is>
-          <t>ctrl_config_checker</t>
-        </is>
-      </c>
-      <c r="C11" s="6" t="inlineStr">
-        <is>
-          <t>检查CTRL寄存器配置正确性：1.CTRL.EN=1时模块使能，CTRL.EN=0时模块禁用(命令返回DISABLED错误码0x04)；2.CTRL.LANE_MODE=00(1-bit模式)或01(4-bit模式)，非法值(10/11)返回错误；3.CTRL.SOFT_RST写1触发软复位，协议上下文清零并恢复默认lane模式。</t>
-        </is>
-      </c>
-      <c r="D11" s="14" t="n"/>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>exception_checker</t>
+        </is>
+      </c>
+      <c r="C11" s="38" t="inlineStr">
+        <is>
+          <t>检查异常检测和状态码返回正确性：
+1.BAD_OPCODE(0x01)：非法opcode检测；
+2.BAD_REG(0x02)：非法CSR地址检测；
+3.ALIGN_ERR(0x03)：非4Byte对齐地址检测；
+4.DISABLED(0x04)：CTRL.EN=0时发送命令检测；
+5.NOT_IN_TEST(0x05)：test_mode_i=0时发送命令检测；
+6.FRAME_ERR(0x06)：pcs_n_i提前拉高帧错误检测；
+7.AHB_ERR(0x07)：hresp_i=1错误检测；
+8.TIMEOUT(0x08)：AHB超时检测；
+9.错误收敛检查：在发起AHB访问前完成前置错误收敛。</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>覆盖TP_011</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="12" t="inlineStr">
+      <c r="A12" t="inlineStr">
         <is>
           <t>CHK_010</t>
         </is>
       </c>
-      <c r="B12" s="12" t="inlineStr">
-        <is>
-          <t>status_query_checker</t>
-        </is>
-      </c>
-      <c r="C12" s="6" t="inlineStr">
-        <is>
-          <t>监测模块状态：STATUS寄存器提供busy/done/err状态，LAST_ERR寄存器提供最近错误码；检查STATUS.BUSY在命令执行期间为1，完成后为0；检查LAST_ERR在错误发生时更新为对应错误码。</t>
-        </is>
-      </c>
-      <c r="D12" s="14" t="n"/>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>low_power_checker</t>
+        </is>
+      </c>
+      <c r="C12" s="38" t="inlineStr">
+        <is>
+          <t>检查低功耗设计正确性：
+1.空闲态检查：pcs_n_i=1时，接收移位寄存器不更新；
+2.非发送态检查：非发送阶段，发送移位寄存器不翻转；
+3.超时计数器检查：timeout counter仅在AHB等待态工作；
+4.测试模式检查：test_mode_i=0时，AHB输出保持IDLE值。</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>覆盖TP_012</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="12" t="inlineStr">
+      <c r="A13" t="inlineStr">
         <is>
           <t>CHK_011</t>
         </is>
       </c>
-      <c r="B13" s="12" t="inlineStr">
-        <is>
-          <t>error_checker</t>
-        </is>
-      </c>
-      <c r="C13" s="6" t="inlineStr">
-        <is>
-          <t>检查协议错误的检测：1.BAD_OPCODE(0x01)：非法opcode检测；2.BAD_REG(0x02)：非法CSR地址检测；3.ALIGN_ERR(0x03)：地址非4Byte对齐检测；4.DISABLED(0x04)：模块未使能检测；5.NOT_IN_TEST(0x05)：非测试模式检测；6.FRAME_ERR(0x06)：帧错误检测(pcs_n_i提前拉高)；7.AHB_ERR(0x07)：AHB总线错误(hresp_i=1)检测；8.TIMEOUT(0x08)：超时检测。所有错误应在发起AHB访问前完成收敛。</t>
-        </is>
-      </c>
-      <c r="D13" s="14" t="n"/>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>performance_checker</t>
+        </is>
+      </c>
+      <c r="C13" s="38" t="inlineStr">
+        <is>
+          <t>检查性能指标达标：
+1.频率检查：clk_i=100MHz稳定工作；
+2.延时检查：4-bit模式下AHB_RD32最小端到端延时约23~24 cycles；
+3.吞吐率检查：1-bit模式线速12.5MB/s，4-bit模式线速50MB/s；
+4.AHB约束检查：AHB接口32bit字访问，地址4Byte对齐。</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>覆盖TP_013</t>
+        </is>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="12" t="inlineStr">
+      <c r="A14" t="inlineStr">
         <is>
           <t>CHK_012</t>
         </is>
       </c>
-      <c r="B14" s="12" t="inlineStr">
-        <is>
-          <t>lowpower_checker</t>
-        </is>
-      </c>
-      <c r="C14" s="6" t="inlineStr">
-        <is>
-          <t>检查空闲态低功耗行为：1.空闲态(test_mode_i=0或无有效任务)接收/发送移位寄存器不翻转；2.超时计数器仅在RX/TX/WAIT_AHB状态工作；3.test_mode_i=0时AHB输出保持IDLE(htrans_o=IDLE)；4.仅在关键状态翻转关键寄存器。</t>
-        </is>
-      </c>
-      <c r="D14" s="14" t="n"/>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>dfx_observer_checker</t>
+        </is>
+      </c>
+      <c r="C14" s="38" t="inlineStr">
+        <is>
+          <t>检查DFX可观测点可访问：
+1.状态机状态可观测；
+2.opcode、addr、wdata、rdata、status_code可观测；
+3.rx/tx计数可观测；
+4.pcs_n_i、pdi_i、pdo_o、pdo_oe_o信号可观测。</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>覆盖TP_014</t>
+        </is>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="12" t="inlineStr">
+      <c r="A15" t="inlineStr">
         <is>
           <t>CHK_013</t>
         </is>
       </c>
-      <c r="B15" s="12" t="inlineStr">
-        <is>
-          <t>throughput_checker</t>
-        </is>
-      </c>
-      <c r="C15" s="6" t="inlineStr">
-        <is>
-          <t>检查性能指标：1.clk_i频率稳定在100MHz±3%；2.1-bit模式原始链路线速12.5MB/s；3.4-bit模式原始链路线速50MB/s；4.AHB接口固定32bit字访问，地址4Byte对齐；5.端到端延时约23~24 cycles。</t>
-        </is>
-      </c>
-      <c r="D15" s="14" t="n"/>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>memory_map_checker</t>
+        </is>
+      </c>
+      <c r="C15" s="38" t="inlineStr">
+        <is>
+          <t>检查memory map正确性：
+1.CSR访问检查：模块内部CSR(VERSION/CTRL/STATUS/LAST_ERR)通过WR_CSR/RD_CSR协议命令访问；
+2.CSR隔离检查：模块自身CSR不进入SoC AHB memory map；
+3.AHB Master检查：对外AHB-Lite Master访问采用32bit地址空间和word访问粒度。</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>覆盖TP_015</t>
+        </is>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" s="12" t="inlineStr">
+      <c r="A16" t="inlineStr">
         <is>
           <t>CHK_014</t>
         </is>
       </c>
-      <c r="B16" s="12" t="inlineStr">
-        <is>
-          <t>dfx_checker</t>
-        </is>
-      </c>
-      <c r="C16" s="6" t="inlineStr">
-        <is>
-          <t>检查调试可观测点可访问性：状态机状态、opcode、addr、wdata、rdata、status_code、rx/tx计数等内部调试信号可采集；便于联调、波形定位和故障复现。</t>
-        </is>
-      </c>
-      <c r="D16" s="14" t="n"/>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ahb_interface_checker</t>
+        </is>
+      </c>
+      <c r="C16" s="38" t="inlineStr">
+        <is>
+          <t>检查AHB-Lite Master接口正确性：
+1.htrans_o检查：仅输出IDLE(2'b00)和NONSEQ(2'b10)；
+2.hsize_o检查：固定为WORD(3'b010)；
+3.hburst_o检查：固定为SINGLE(3'b000)；
+4.hwrite_o检查：写命令为高，读命令为低；
+5.haddr_o检查：地址4Byte对齐；
+6.hwdata_o/hrdata_i检查：32bit数据正确传输；
+7.hready_i/hresp_i检查：正确处理响应信号。</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>覆盖TP_016</t>
+        </is>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" s="12" t="inlineStr">
-        <is>
-          <t>CHK_015</t>
-        </is>
-      </c>
-      <c r="B17" s="12" t="inlineStr">
-        <is>
-          <t>memory_map_checker</t>
-        </is>
-      </c>
-      <c r="C17" s="36" t="inlineStr">
-        <is>
-          <t>检查memory map约束：1.模块CSR(VERSION/CTRL/STATUS/LAST_ERR)仅通过WR_CSR/RD_CSR协议命令访问，不映射到SoC AHB地址空间；2.AHB Master访问采用32bit地址空间和word访问粒度；3.AHB地址需4Byte对齐。</t>
-        </is>
-      </c>
-      <c r="D17" s="14" t="n"/>
+      <c r="A17" s="27" t="inlineStr">
+        <is>
+          <t>填写要求</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="12" t="inlineStr">
         <is>
-          <t>CHK_016</t>
-        </is>
-      </c>
-      <c r="B18" s="12" t="inlineStr">
-        <is>
-          <t>ahb_protocol_checker</t>
-        </is>
-      </c>
-      <c r="C18" s="36" t="inlineStr">
-        <is>
-          <t>检查AHB-Lite Master协议符合性：1.htrans_o仅输出IDLE(2'b00)或NONSEQ(2'b10)，不输出SEQ(2'b01)或BUSY(2'b11)；2.hsize_o固定为WORD(3'b010，32-bit)；3.hburst_o固定为SINGLE(3'b000)；4.haddr_o/hwrite_o/hwdata_o输出正确；5.hrdata_i/hready_i/hresp_i输入正确处理。</t>
-        </is>
-      </c>
-      <c r="D18" s="14" t="n"/>
+          <t>CHK Name</t>
+        </is>
+      </c>
+      <c r="B18" s="39" t="inlineStr">
+        <is>
+          <t>如果是SVA checker，需填写SVA property名字</t>
+        </is>
+      </c>
+      <c r="C18" s="22" t="n"/>
+      <c r="D18" s="23" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="12" t="n"/>
-      <c r="B19" s="12" t="n"/>
-      <c r="C19" s="36" t="n"/>
-      <c r="D19" s="14" t="n"/>
+      <c r="A19" s="12" t="inlineStr">
+        <is>
+          <t>CHK描述</t>
+        </is>
+      </c>
+      <c r="B19" s="40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1、需要定性+定量描述，需具体到check的信号、取值 
+2、和DV SPEC中Checker方案描述的区别 — RTM中描述check的内容，DV SPEC中描述checker的实现方案(例如是通过SVA实现还是scoreboard实时数据比对，还是文件对比)
+</t>
+        </is>
+      </c>
+      <c r="C19" s="22" t="n"/>
+      <c r="D19" s="23" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="12" t="n"/>
       <c r="B20" s="12" t="n"/>
-      <c r="C20" s="36" t="n"/>
-      <c r="D20" s="14" t="n"/>
+      <c r="C20" s="22" t="n"/>
+      <c r="D20" s="23" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="12" t="n"/>
       <c r="B21" s="12" t="n"/>
-      <c r="C21" s="36" t="n"/>
-      <c r="D21" s="14" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="12" t="n"/>
-      <c r="B22" s="12" t="n"/>
-      <c r="C22" s="36" t="n"/>
-      <c r="D22" s="14" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="12" t="n"/>
-      <c r="B23" s="12" t="n"/>
-      <c r="C23" s="36" t="n"/>
-      <c r="D23" s="14" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="12" t="n"/>
-      <c r="B24" s="12" t="n"/>
-      <c r="C24" s="36" t="n"/>
-      <c r="D24" s="14" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="12" t="n"/>
-      <c r="B25" s="12" t="n"/>
-      <c r="C25" s="6" t="n"/>
-      <c r="D25" s="14" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="12" t="n"/>
-      <c r="B26" s="12" t="n"/>
-      <c r="C26" s="6" t="n"/>
-      <c r="D26" s="14" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="32" t="n"/>
-      <c r="B27" s="32" t="n"/>
-      <c r="C27" s="6" t="n"/>
-      <c r="D27" s="4" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="32" t="n"/>
-      <c r="B28" s="32" t="n"/>
-      <c r="C28" s="6" t="n"/>
-      <c r="D28" s="4" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="32" t="n"/>
-      <c r="B29" s="32" t="n"/>
-      <c r="C29" s="6" t="n"/>
-      <c r="D29" s="4" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="32" t="n"/>
-      <c r="B30" s="32" t="n"/>
-      <c r="C30" s="6" t="n"/>
-      <c r="D30" s="4" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="32" t="n"/>
-      <c r="B31" s="32" t="n"/>
-      <c r="C31" s="6" t="n"/>
-      <c r="D31" s="4" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="32" t="n"/>
-      <c r="B32" s="32" t="n"/>
-      <c r="C32" s="6" t="n"/>
-      <c r="D32" s="4" t="n"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="24" t="inlineStr">
-        <is>
-          <t>填写要求</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="24" customHeight="1" s="25">
-      <c r="A37" s="32" t="inlineStr">
-        <is>
-          <t>CHK Name</t>
-        </is>
-      </c>
-      <c r="B37" s="37" t="inlineStr">
-        <is>
-          <t>如果是SVA checker，需填写SVA property名字</t>
-        </is>
-      </c>
-      <c r="C37" s="21" t="n"/>
-      <c r="D37" s="22" t="n"/>
-    </row>
-    <row r="38" ht="69.95" customHeight="1" s="25">
-      <c r="A38" s="32" t="inlineStr">
-        <is>
-          <t>CHK描述</t>
-        </is>
-      </c>
-      <c r="B38" s="38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1、需要定性+定量描述，需具体到check的信号、取值 
-2、和DV SPEC中Checker方案描述的区别 — RTM中描述check的内容，DV SPEC中描述checker的实现方案(例如是通过SVA实现还是scoreboard实时数据比对，还是文件对比)
-</t>
-        </is>
-      </c>
-      <c r="C38" s="21" t="n"/>
-      <c r="D38" s="22" t="n"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="32" t="n"/>
-      <c r="B39" s="12" t="n"/>
-      <c r="C39" s="21" t="n"/>
-      <c r="D39" s="22" t="n"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="32" t="n"/>
-      <c r="B40" s="12" t="n"/>
-      <c r="C40" s="21" t="n"/>
-      <c r="D40" s="22" t="n"/>
+      <c r="C21" s="22" t="n"/>
+      <c r="D21" s="23" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="6">
     <mergeCell ref="A1:D1"/>
-    <mergeCell ref="B37:D37"/>
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="B39:D39"/>
-    <mergeCell ref="B38:D38"/>
-    <mergeCell ref="A36:D36"/>
+    <mergeCell ref="I17"/>
+    <mergeCell ref="J17"/>
+    <mergeCell ref="K17"/>
+    <mergeCell ref="M17"/>
+    <mergeCell ref="L17"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2581,42 +2593,42 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D42"/>
+  <dimension ref="A1:D17"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col width="13.75" customWidth="1" style="25" min="1" max="1"/>
-    <col width="20" customWidth="1" style="25" min="2" max="2"/>
-    <col width="53.5" customWidth="1" style="25" min="3" max="3"/>
-    <col width="14.25" customWidth="1" style="25" min="4" max="4"/>
+    <col width="12" customWidth="1" style="28" min="1" max="1"/>
+    <col width="25" customWidth="1" style="28" min="2" max="2"/>
+    <col width="80" customWidth="1" style="28" min="3" max="3"/>
+    <col width="15" customWidth="1" style="28" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="30" t="inlineStr">
+      <c r="A1" s="32" t="inlineStr">
         <is>
           <t>Test Case List</t>
         </is>
       </c>
-      <c r="B1" s="21" t="n"/>
-      <c r="C1" s="21" t="n"/>
-      <c r="D1" s="22" t="n"/>
+      <c r="B1" s="22" t="n"/>
+      <c r="C1" s="22" t="n"/>
+      <c r="D1" s="23" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="23" t="inlineStr">
+      <c r="A2" s="24" t="inlineStr">
         <is>
           <t>TC编号</t>
         </is>
       </c>
-      <c r="B2" s="23" t="inlineStr">
+      <c r="B2" s="24" t="inlineStr">
         <is>
           <t>TC Name</t>
         </is>
       </c>
-      <c r="C2" s="23" t="inlineStr">
+      <c r="C2" s="24" t="inlineStr">
         <is>
           <t>TC 描述</t>
         </is>
       </c>
-      <c r="D2" s="23" t="inlineStr">
+      <c r="D2" s="24" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
@@ -2630,27 +2642,32 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>test_tbus_clk_normal</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
+          <t>clk_domain_sync_test</t>
+        </is>
+      </c>
+      <c r="C3" s="41" t="inlineStr">
         <is>
           <t>配置条件：
 1.配置clk_i时钟频率为100MHz；
-2.配置test_mode_i=1，通过WR_CSR(0x10)设置CTRL.EN=1使能模块；
-3.配置LANE_MODE=00(1-bit模式)或01(4-bit模式)。
+2.配置test_mode_i=1，通过WR_CSR(0x10)设置CTRL.EN=1；
+3.分别配置LANE_MODE=00(1-bit)和LANE_MODE=01(4-bit)。
 输入激励：
-1.连续发送AHB_RD32(0x21)和AHB_WR32(0x20)命令，覆盖1-bit和4-bit两种lane模式；
-2.验证协议采样、状态机控制和AHB-Lite主接口同域工作。
+1.在1-bit模式下，连续发送AHB_RD32(0x21)和AHB_WR32(0x20)命令各100次；
+2.在4-bit模式下，重复上述测试；
+3.随机插入idle周期，验证时钟稳定性。
 期望结果：
 1.所有命令在100MHz频率下正确执行；
-2.clk_i时钟域同步性正常，无时序违例；
-3.协议采样正确，状态机跳转正常，AHB-Lite主接口工作正常。
+2.协议采样、状态机控制和AHB-Lite主接口同域工作正常；
+3.无时序违例，无数据丢失。
 coverage check点：
-对lane模式配置(1-bit/4-bit)收集功能覆盖率</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="n"/>
+直接用例覆盖，不收功能覆盖率。</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>覆盖TP_001</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -2660,29 +2677,34 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>test_tbus_rst</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
+          <t>reset_behavior_test</t>
+        </is>
+      </c>
+      <c r="C4" s="41" t="inlineStr">
         <is>
           <t>配置条件：
-1.配置test_mode_i=1，模块进入测试模式；
-2.初始状态rst_ni为低，模块处于复位状态。
+1.初始状态rst_ni为低，模块处于复位状态；
+2.时钟clk_i稳定运行。
 输入激励：
-1.释放rst_ni，验证复位后状态机回到IDLE；
-2.通过RD_CSR(0x11)读取CTRL寄存器，检查CTRL.EN=0，LANE_MODE=01默认值；
-3.读取STATUS/LAST_ERR寄存器验证清零；
-4.验证协议上下文和错误状态已清空。
+1.释放rst_ni，等待同步释放完成；
+2.通过RD_CSR(0x11)读取CTRL寄存器，验证EN=0、LANE_MODE=00；
+3.通过RD_CSR读取STATUS和LAST_ERR寄存器，验证清零；
+4.验证状态机处于IDLE状态；
+5.反复复位释放10次，验证复位行为一致性。
 期望结果：
-1.复位后状态机处于IDLE状态；
-2.CTRL.EN=0，LANE_MODE=01(1-bit模式)；
-3.STATUS/LAST_ERR寄存器值为0x00000000；
-4.无残留协议上下文和错误状态。
+1.复位后状态机处于IDLE；
+2.CTRL.EN=0，CTRL.LANE_MODE=00(1-bit)；
+3.STATUS=0x00，LAST_ERR=0x00；
+4.协议上下文和错误状态已清空，无残留状态。
 coverage check点：
-直接用例覆盖，不收功能覆盖率</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="n"/>
+直接用例覆盖，不收功能覆盖率。</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>覆盖TP_002</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -2692,30 +2714,34 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>test_tbus_reg</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
+          <t>csr_access_test</t>
+        </is>
+      </c>
+      <c r="C5" s="41" t="inlineStr">
         <is>
           <t>配置条件：
-1.配置test_mode_i=1，通过WR_CSR(0x10)设置CTRL.EN=1使能模块；
-2.模块进入使能工作状态。
+1.配置test_mode_i=1；
+2.通过WR_CSR(0x10)设置CTRL.EN=1使能模块。
 输入激励：
-1.通过RD_CSR(0x11)读取VERSION寄存器验证版本号；
-2.通过WR_CSR(0x10)/RD_CSR(0x11)访问CTRL寄存器配置EN、LANE_MODE、SOFT_RST字段；
-3.读取STATUS检查busy状态；
-4.读取LAST_ERR检查错误状态；
-5.九步法寄存器测试激励。
+1.通过RD_CSR(0x11)读取VERSION寄存器，验证版本号；
+2.通过WR_CSR写入CTRL.EN=1，LANE_MODE=01，验证配置生效；
+3.通过RD_CSR读取CTRL寄存器，验证写入正确；
+4.写入CTRL.SOFT_RST=1触发软复位，验证恢复默认值；
+5.随机读写STATUS和LAST_ERR寄存器，验证sticky位行为。
 期望结果：
-1.CSR读写正确，VERSION返回预期值(如0x00010000)；
-2.CTRL.EN、CTRL.LANE_MODE、CTRL.SOFT_RST配置生效；
-3.STATUS/LAST_ERR反映正确状态；
-4.寄存器读写属性符合规范。
+1.VERSION寄存器返回预期版本号；
+2.CTRL配置正确写入和读取；
+3.SOFT_RST触发后恢复默认lane模式；
+4.STATUS/LAST_ERR反映正确状态。
 coverage check点：
-对CSR地址和数据位宽收集功能覆盖率</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="n"/>
+直接用例覆盖，不收功能覆盖率。</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>覆盖TP_003</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2725,29 +2751,35 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>test_tbus_test_mode</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
+          <t>work_mode_test</t>
+        </is>
+      </c>
+      <c r="C6" s="41" t="inlineStr">
         <is>
           <t>配置条件：
 1.配置test_mode_i=1，通过WR_CSR(0x10)设置CTRL.EN=1；
-2.模块进入ATE测试模式。
+2.分别配置LANE_MODE=00(1-bit)和LANE_MODE=01(4-bit)。
 输入激励：
-1.发送WR_CSR(0x10)命令配置LANE_MODE字段；
-2.发送AHB_WR32(0x20)命令进行单次写操作；
-3.发送AHB_RD32(0x21)命令进行单次读操作；
-4.验证半双工请求/响应模式工作正常。
+1.在test_mode_i=1时，发送WR_CSR配置lane模式，发送AHB_WR32/AHB_RD32命令；
+2.在test_mode_i=0时，发送功能命令，验证返回NOT_IN_TEST错误(0x05)；
+3.在CTRL.EN=0时，发送功能命令，验证返回DISABLED错误(0x04)；
+4.尝试配置非法LANE_MODE值(02/03)，验证错误处理；
+5.验证半双工请求/响应模式：请求阶段pdo_oe_o=0，响应阶段pdo_oe_o=1。
 期望结果：
-1.模块正确执行功能命令；
-2.协议采用半双工模式：请求阶段输入、turnaround 1周期、响应阶段输出；
-3.CSR访问与AHB-Lite单次读写正常；
-4.STATUS寄存器反映正确的busy/done状态。
+1.test_mode_i=1且CTRL.EN=1时，命令正确执行；
+2.test_mode_i=0时，返回STS_NOT_IN_TEST(0x05)；
+3.CTRL.EN=0时，返回STS_DISABLED(0x04)；
+4.非法LANE_MODE值返回错误；
+5.Burst和AXI功能确认不可用。
 coverage check点：
-对命令类型(WR_CSR/RD_CSR/AHB_WR32/AHB_RD32)收集功能覆盖率</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="n"/>
+直接用例覆盖，不收功能覆盖率。</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>覆盖TP_004, TP_005</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="16" t="inlineStr">
@@ -2757,530 +2789,408 @@
       </c>
       <c r="B7" s="16" t="inlineStr">
         <is>
-          <t>test_tbus_lane_mode</t>
-        </is>
-      </c>
-      <c r="C7" s="35" t="inlineStr">
+          <t>data_interface_test</t>
+        </is>
+      </c>
+      <c r="C7" s="42" t="inlineStr">
         <is>
           <t>配置条件：
 1.配置test_mode_i=1，CTRL.EN=1；
-2.模块进入使能工作状态。
+2.分别配置LANE_MODE=00(1-bit)和LANE_MODE=01(4-bit)。
 输入激励：
-1.配置CTRL.LANE_MODE=00，验证1-bit模式数据传输；
-2.配置CTRL.LANE_MODE=01，验证4-bit模式数据传输(高nibble优先)；
-3.尝试配置非法LANE_MODE值(10/11)，验证错误处理；
-4.验证不支持Burst和AXI后端功能。
+1.在1-bit模式下发送WR_CSR(0x10)命令，验证pdi_i[0]/pdo_o[0]数据传输；
+2.在4-bit模式下发送相同命令，验证pdi_i[3:0]/pdo_o[3:0]按高nibble优先发送；
+3.验证pcs_n_i帧边界：拉低开启事务，拉高结束事务；
+4.验证MSB first传输顺序。
 期望结果：
-1.1-bit模式正常工作，pdi_i[0]/pdo_o[0]正确传输；
-2.4-bit模式正常工作，pdi_i[3:0]/pdo_o[3:0]按高nibble优先发送；
-3.非法LANE_MODE配置返回错误码；
-4.Burst和AXI功能确认不可用。
+1.1-bit模式正确使用bit0传输；
+2.4-bit模式按高nibble优先发送；
+3.pcs_n_i正确标记帧边界；
+4.数据按MSB first顺序传输。
 coverage check点：
-对LANE_MODE配置值(00/01/10/11)收集功能覆盖率</t>
-        </is>
-      </c>
-      <c r="D7" s="14" t="n"/>
+直接用例覆盖，不收功能覆盖率。</t>
+        </is>
+      </c>
+      <c r="D7" s="14" t="inlineStr">
+        <is>
+          <t>覆盖TP_006</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="16" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>TC_006</t>
         </is>
       </c>
-      <c r="B8" s="16" t="inlineStr">
-        <is>
-          <t>test_tbus_data_interface</t>
-        </is>
-      </c>
-      <c r="C8" s="35" t="inlineStr">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>protocol_timing_test</t>
+        </is>
+      </c>
+      <c r="C8" s="38" t="inlineStr">
         <is>
           <t>配置条件：
 1.配置test_mode_i=1，CTRL.EN=1；
-2.配置LANE_MODE=00(1-bit模式)。
+2.配置LANE_MODE=01(4-bit模式)。
 输入激励：
-1.在1-bit模式下发送WR_CSR(0x10)命令，验证pdi_i[0]/pdo_o[0]数据传输；
-2.配置LANE_MODE=01(4-bit模式)；
-3.在4-bit模式下发送AHB_WR32(0x20)命令，验证pdi_i[3:0]/pdo_o[3:0]按高nibble优先发送；
-4.验证pcs_n_i帧边界正确：拉低开始帧，拉高结束帧。
+1.发送WR_CSR(0x10)命令，记录请求阶段结束时刻；
+2.验证turnaround周期为1个clk_i周期；
+3.检查pdo_oe_o在turnaround后置1；
+4.依次发送四种命令：WR_CSR(0x10)、RD_CSR(0x11)、AHB_WR32(0x20)、AHB_RD32(0x21)；
+5.测量每种命令的端到端延时。
 期望结果：
-1.数据接口按lane模式正确传输；
-2.帧边界清晰：pcs_n_i定义请求阶段和响应阶段；
-3.MSB first顺序正确；
-4.pdo_oe_o在turnaround后拉高，响应阶段输出使能。
+1.请求阶段与响应阶段正确分离；
+2.turnaround固定1周期；
+3.pdo_oe_o在响应阶段置1；
+4.协议字段MSB first传输；
+5.四种帧格式正确处理。
 coverage check点：
-对lane模式(1-bit/4-bit)和数据包类型收集功能覆盖率</t>
-        </is>
-      </c>
-      <c r="D8" s="14" t="n"/>
+直接用例覆盖，不收功能覆盖率。</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>覆盖TP_007</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="16" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>TC_007</t>
         </is>
       </c>
-      <c r="B9" s="16" t="inlineStr">
-        <is>
-          <t>test_tbus_protocol_timing</t>
-        </is>
-      </c>
-      <c r="C9" s="35" t="inlineStr">
-        <is>
-          <t>配置条件：
-1.配置test_mode_i=1，CTRL.EN=1；
-2.配置LANE_MODE=00或01。
-输入激励：
-1.发送WR_CSR(0x10)命令验证请求阶段；
-2.监测turnaround周期(1个clk_i)；
-3.检查响应阶段pdo_oe_o输出使能；
-4.验证四种命令帧格式：WR_CSR(0x10)、RD_CSR(0x11)、AHB_WR32(0x20)、AHB_RD32(0x21)。
-期望结果：
-1.请求/响应阶段正确分离；
-2.turnaround固定1个clk_i周期；
-3.协议字段MSB first传输；
-4.四种帧格式正确处理。
-coverage check点：
-对四种opcode(0x10/0x11/0x20/0x21)收集功能覆盖率</t>
-        </is>
-      </c>
-      <c r="D9" s="14" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="16" t="inlineStr">
-        <is>
-          <t>TC_008</t>
-        </is>
-      </c>
-      <c r="B10" s="16" t="inlineStr">
-        <is>
-          <t>test_tbus_opcode</t>
-        </is>
-      </c>
-      <c r="C10" s="35" t="inlineStr">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>opcode_test</t>
+        </is>
+      </c>
+      <c r="C9" s="38" t="inlineStr">
         <is>
           <t>配置条件：
 1.配置test_mode_i=1，CTRL.EN=1；
 2.AHB总线空闲。
 输入激励：
-1.发送opcode=8'h10执行WR_CSR命令；
-2.发送opcode=8'h11执行RD_CSR命令；
-3.发送opcode=8'h20执行AHB_WR32命令；
-4.发送opcode=8'h21执行AHB_RD32命令；
-5.发送非法opcode(8'h00/8'hFF)验证错误处理。
+1.发送opcode=0x10(WR_CSR)，验证CSR写功能；
+2.发送opcode=0x11(RD_CSR)，验证CSR读功能；
+3.发送opcode=0x20(AHB_WR32)，验证AHB单次写功能；
+4.发送opcode=0x21(AHB_RD32)，验证AHB单次读功能；
+5.发送非法opcode(0x00/0xFF/0x30/0x0F等)，验证错误返回；
+6.随机生成100个非法opcode，验证全部返回STS_BAD_OPCODE(0x01)。
 期望结果：
-1.四种opcode正确译码并执行；
+1.四种合法opcode正确译码并执行；
 2.非法opcode返回STS_BAD_OPCODE(0x01)；
-3.前端正确确定期望帧长；
-4.LAST_ERR寄存器更新为对应错误码。
+3.前端收满8bit后正确确定期望帧长。
 coverage check点：
-对opcode值(0x10/0x11/0x20/0x21/非法值)收集功能覆盖率</t>
-        </is>
-      </c>
-      <c r="D10" s="14" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="16" t="inlineStr">
-        <is>
-          <t>TC_009</t>
-        </is>
-      </c>
-      <c r="B11" s="16" t="inlineStr">
-        <is>
-          <t>test_tbus_ctrl_config</t>
-        </is>
-      </c>
-      <c r="C11" s="35" t="inlineStr">
+直接用例覆盖，不收功能覆盖率。</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>覆盖TP_008</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>TC_008</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>ctrl_config_test</t>
+        </is>
+      </c>
+      <c r="C10" s="38" t="inlineStr">
         <is>
           <t>配置条件：
 1.配置test_mode_i=1；
-2.模块初始禁用状态(CTRL.EN=0)。
+2.模块初始状态禁用(CTRL.EN=0)。
 输入激励：
-1.通过WR_CSR(0x10)写CTRL.EN=1使能模块，验证功能命令可执行；
-2.写CTRL.EN=0禁用模块，发送命令验证返回DISABLED错误(0x04)；
-3.配置CTRL.LANE_MODE=00验证1-bit模式；
-4.配置CTRL.LANE_MODE=01验证4-bit模式；
-5.写CTRL.SOFT_RST=1触发软复位，验证协议上下文清零并恢复默认lane模式。
+1.写CTRL.EN=1使能模块，发送功能命令验证可执行；
+2.写CTRL.EN=0禁用模块，发送命令验证返回DISABLED(0x04)；
+3.配置LANE_MODE=00验证1-bit模式工作；
+4.配置LANE_MODE=01验证4-bit模式工作；
+5.尝试配置LANE_MODE=10/11，验证非法配置处理；
+6.写CTRL.SOFT_RST=1触发软复位，验证协议上下文清零；
+7.软复位后验证恢复默认lane模式(1-bit)。
 期望结果：
-1.CTRL.EN配置正确生效；
-2.使能/禁用状态切换正确；
-3.LANE_MODE配置生效；
-4.软复位功能正常，协议上下文清零。
+1.EN使能/禁用状态切换正确；
+2.LANE_MODE=00/01配置生效；
+3.非法LANE_MODE返回错误；
+4.SOFT_RST触发协议上下文清零；
+5.恢复默认1-bit模式。
 coverage check点：
-对CTRL.EN、CTRL.LANE_MODE、CTRL.SOFT_RST配置值收集功能覆盖率</t>
-        </is>
-      </c>
-      <c r="D11" s="14" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="16" t="inlineStr">
-        <is>
-          <t>TC_010</t>
-        </is>
-      </c>
-      <c r="B12" s="16" t="inlineStr">
-        <is>
-          <t>test_tbus_status_query</t>
-        </is>
-      </c>
-      <c r="C12" s="35" t="inlineStr">
+直接用例覆盖，不收功能覆盖率。</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>覆盖TP_009</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>TC_009</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>status_polling_test</t>
+        </is>
+      </c>
+      <c r="C11" s="38" t="inlineStr">
         <is>
           <t>配置条件：
 1.配置test_mode_i=1，CTRL.EN=1；
-2.模块进入使能工作状态。
+2.准备触发各类错误条件。
 输入激励：
-1.触发各类错误条件(非法opcode、帧错误、AHB错误等)；
-2.通过RD_CSR(0x11)读取STATUS寄存器检查sticky位；
-3.读取LAST_ERR寄存器获取最近错误码；
-4.验证无独立中断输出。
+1.触发非法opcode错误，通过RD_CSR读取STATUS寄存器sticky位；
+2.读取LAST_ERR寄存器验证错误码更新；
+3.依次触发各类错误(BAD_REG/ALIGN_ERR/DISABLED/NOT_IN_TEST/FRAME_ERR/AHB_ERR/TIMEOUT)；
+4.验证无独立中断输出信号；
+5.模拟ATE轮询方式获取状态。
 期望结果：
-1.所有错误与完成状态通过STATUS/LAST_ERR查询获取；
-2.MVP版本无中断输出；
-3.ATE轮询方式正确获取状态；
-4.STATUS.BUSY在命令执行期间为1，完成后为0。
+1.STATUS寄存器sticky位正确记录历史错误；
+2.LAST_ERR正确记录最近错误码；
+3.MVP版本无中断输出；
+4.轮询方式正确获取状态。
 coverage check点：
-对STATUS和LAST_ERR寄存器值收集功能覆盖率</t>
-        </is>
-      </c>
-      <c r="D12" s="14" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="16" t="inlineStr">
-        <is>
-          <t>TC_011</t>
-        </is>
-      </c>
-      <c r="B13" s="16" t="inlineStr">
-        <is>
-          <t>test_tbus_error_detect</t>
-        </is>
-      </c>
-      <c r="C13" s="35" t="inlineStr">
+直接用例覆盖，不收功能覆盖率。</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>覆盖TP_010</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>TC_010</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>exception_test</t>
+        </is>
+      </c>
+      <c r="C12" s="38" t="inlineStr">
         <is>
           <t>配置条件：
 1.配置test_mode_i=1，CTRL.EN=1；
-2.AHB总线正常。
+2.AHB总线正常响应。
 输入激励：
-1.发送非法opcode(8'h00/8'hFF)验证BAD_OPCODE错误(0x01)；
-2.访问非法CSR地址验证BAD_REG错误(0x02)；
-3.发送非4Byte对齐地址验证ALIGN_ERR错误(0x03)；
-4.配置CTRL.EN=0后发送命令验证DISABLED错误(0x04)；
-5.配置test_mode_i=0后发送命令验证NOT_IN_TEST错误(0x05)；
-6.提前拉高pcs_n_i验证FRAME_ERR错误(0x06)；
-7.触发hresp_i=1验证AHB_ERR错误(0x07)；
-8.模拟AHB超时验证TIMEOUT错误(0x08)。
+1.发送非法opcode(0x00/0xFF)验证BAD_OPCODE(0x01)；
+2.访问非法CSR地址(如0xFC)验证BAD_REG(0x02)；
+3.发送非4Byte对齐地址(如0x01)验证ALIGN_ERR(0x03)；
+4.设置CTRL.EN=0后发送命令验证DISABLED(0x04)；
+5.设置test_mode_i=0后发送命令验证NOT_IN_TEST(0x05)；
+6.在请求阶段提前拉高pcs_n_i验证FRAME_ERR(0x06)；
+7.配置hresp_i=1模拟AHB错误验证AHB_ERR(0x07)；
+8.模拟hready_i长时间为0验证TIMEOUT(0x08)；
+9.验证所有错误在发起AHB访问前完成收敛。
 期望结果：
-1.各类错误正确检测；
-2.在发起AHB访问前完成前置错误收敛；
-3.返回确定性状态码；
-4.LAST_ERR寄存器更新正确。
+1.各类错误正确检测并返回对应状态码；
+2.LAST_ERR更新正确；
+3.错误在AHB访问前收敛，不发起错误AHB访问。
 coverage check点：
-对错误类型(0x01~0x08)收集功能覆盖率</t>
-        </is>
-      </c>
-      <c r="D13" s="14" t="n"/>
+直接用例覆盖，不收功能覆盖率。</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>覆盖TP_011</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>TC_011</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>low_power_test</t>
+        </is>
+      </c>
+      <c r="C13" s="38" t="inlineStr">
+        <is>
+          <t>配置条件：
+1.模块初始处于空闲态(test_mode_i=0或pcs_n_i=1)。
+输入激励：
+1.保持pcs_n_i=1，观察接收移位寄存器是否翻转；
+2.模拟AHB等待态，观察超时计数器是否工作；
+3.设置test_mode_i=0，验证AHB输出保持IDLE；
+4.切换到工作态，验证关键寄存器翻转；
+5.测量空闲态和工作态的翻转活动差异。
+期望结果：
+1.pcs_n_i=1时接收移位寄存器不翻转；
+2.超时计数器仅在AHB等待态工作；
+3.test_mode_i=0时AHB输出IDLE；
+4.空闲态翻转最小化，低功耗目标满足。
+coverage check点：
+直接用例覆盖，不收功能覆盖率。</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>覆盖TP_012</t>
+        </is>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="16" t="inlineStr">
+      <c r="A14" t="inlineStr">
         <is>
           <t>TC_012</t>
         </is>
       </c>
-      <c r="B14" s="16" t="inlineStr">
-        <is>
-          <t>test_tbus_lowpower</t>
-        </is>
-      </c>
-      <c r="C14" s="35" t="inlineStr">
-        <is>
-          <t>配置条件：
-1.模块处于空闲态(test_mode_i=0或无有效任务)。
-输入激励：
-1.保持pcs_n_i=1验证接收/发送移位寄存器不翻转；
-2.模拟AHB等待态验证超时计数器仅在此状态工作；
-3.test_mode_i=0时验证AHB输出保持IDLE；
-4.切换到工作态验证关键寄存器翻转。
-期望结果：
-1.空闲态无效翻转最小化；
-2.低功耗设计目标满足；
-3.AHB接口在空闲态保持IDLE；
-4.功耗测试通过。
-coverage check点：
-直接用例覆盖，不收功能覆盖率</t>
-        </is>
-      </c>
-      <c r="D14" s="14" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="16" t="inlineStr">
-        <is>
-          <t>TC_013</t>
-        </is>
-      </c>
-      <c r="B15" s="16" t="inlineStr">
-        <is>
-          <t>test_tbus_performance</t>
-        </is>
-      </c>
-      <c r="C15" s="35" t="inlineStr">
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>performance_test</t>
+        </is>
+      </c>
+      <c r="C14" s="38" t="inlineStr">
         <is>
           <t>配置条件：
 1.配置clk_i=100MHz；
-2.AHB总线响应正常。
+2.AHB总线hready_i=1正常响应。
 输入激励：
-1.在1-bit模式下连续执行AHB_RD32/AHB_WR32命令，计算端到端延时和吞吐率；
-2.在4-bit模式下执行相同测试；
-3.验证原始链路线速：1-bit模式12.5MB/s，4-bit模式50MB/s；
-4.验证AHB接口32bit字访问和4Byte对齐约束。
+1.在1-bit模式下连续执行AHB_RD32/AHB_WR32命令各100次，计算端到端延时；
+2.在4-bit模式下执行相同测试，测量延时；
+3.计算吞吐率：1-bit模式和4-bit模式；
+4.发送非4Byte对齐地址，验证AHB访问约束；
+5.测量状态机各阶段延时分布。
 期望结果：
-1.目标频率100MHz稳定工作；
-2.延时符合预期(约23~24 cycles)；
-3.吞吐率达标；
-4.AHB访问约束满足。
+1.100MHz稳定工作；
+2.4-bit模式AHB_RD32最小延时约23~24 cycles；
+3.1-bit模式线速≈12.5MB/s，4-bit模式≈50MB/s；
+4.AHB访问32bit字粒度，4Byte对齐约束满足。
 coverage check点：
-对性能指标(频率、延时、吞吐率)收集功能覆盖率</t>
-        </is>
-      </c>
-      <c r="D15" s="14" t="n"/>
+直接用例覆盖，不收功能覆盖率。</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>覆盖TP_013</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>TC_013</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>dfx_test</t>
+        </is>
+      </c>
+      <c r="C15" s="38" t="inlineStr">
+        <is>
+          <t>配置条件：
+1.仿真环境，配置test_mode_i=1，CTRL.EN=1。
+输入激励：
+1.执行多种命令序列(包含所有四种opcode)；
+2.采集状态机状态信号；
+3.采集opcode、addr、wdata、rdata、status_code；
+4.采集rx/tx计数；
+5.采集pcs_n_i、pdi_i、pdo_o、pdo_oe_o；
+6.触发各类错误，观察调试可观测点。
+期望结果：
+1.状态机状态可观测；
+2.所有内部调试信号可采集；
+3.便于联调、波形定位和故障复现。
+coverage check点：
+直接用例覆盖，不收功能覆盖率。</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>覆盖TP_014</t>
+        </is>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" s="16" t="inlineStr">
+      <c r="A16" t="inlineStr">
         <is>
           <t>TC_014</t>
         </is>
       </c>
-      <c r="B16" s="16" t="inlineStr">
-        <is>
-          <t>test_tbus_dfx</t>
-        </is>
-      </c>
-      <c r="C16" s="35" t="inlineStr">
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>memory_map_test</t>
+        </is>
+      </c>
+      <c r="C16" s="38" t="inlineStr">
         <is>
           <t>配置条件：
-1.仿真环境，test_mode_i=1，CTRL.EN=1；
-2.模块进入使能工作状态。
+1.配置test_mode_i=1，CTRL.EN=1。
 输入激励：
-1.执行多种命令序列(WR_CSR/RD_CSR/AHB_WR32/AHB_RD32)；
-2.采集状态机状态、opcode、addr、wdata、rdata、status_code；
-3.采集rx/tx计数、pcs_n_i、pdi_i、pdo_o、pdo_oe_o；
-4.验证内部调试可观测点可访问。
+1.通过WR_CSR/RD_CSR访问VERSION寄存器，验证CSR路径；
+2.通过WR_CSR/RD_CSR访问CTRL、STATUS、LAST_ERR寄存器；
+3.发送AHB_WR32/AHB_RD32命令访问SoC内部memory-mapped地址；
+4.验证模块自身CSR不通过AHB地址空间访问；
+5.验证AHB Master使用32bit地址空间和word访问粒度。
 期望结果：
-1.所有调试可观测点可采集；
-2.便于联调、波形定位和故障复现；
-3.状态机跳转清晰可追踪。
+1.CSR通过协议命令正确访问；
+2.模块CSR不进入SoC AHB memory map；
+3.AHB Master访问正确，地址空间约束满足。
 coverage check点：
-直接用例覆盖，不收功能覆盖率</t>
-        </is>
-      </c>
-      <c r="D16" s="14" t="n"/>
+直接用例覆盖，不收功能覆盖率。</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>覆盖TP_015</t>
+        </is>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" s="16" t="inlineStr">
+      <c r="A17" t="inlineStr">
         <is>
           <t>TC_015</t>
         </is>
       </c>
-      <c r="B17" s="16" t="inlineStr">
-        <is>
-          <t>test_tbus_memory_map</t>
-        </is>
-      </c>
-      <c r="C17" s="35" t="inlineStr">
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>ahb_interface_test</t>
+        </is>
+      </c>
+      <c r="C17" s="38" t="inlineStr">
         <is>
           <t>配置条件：
 1.配置test_mode_i=1，CTRL.EN=1；
-2.模块进入使能工作状态。
+2.AHB总线hready_i=1，hresp_i=0正常响应。
 输入激励：
-1.通过WR_CSR(0x10)/RD_CSR(0x11)访问模块内部CSR寄存器(VERSION/CTRL/STATUS/LAST_ERR)；
-2.发送AHB_WR32(0x20)/AHB_RD32(0x21)命令访问SoC内部memory-mapped地址；
-3.验证模块自身CSR不进入SoC AHB memory map；
-4.验证AHB Master访问采用32bit地址空间和word访问粒度。
+1.发送AHB_WR32(0x20)命令，验证haddr_o/hwrite_o/htrans_o/hsize_o/hburst_o/hwdata_o输出；
+2.发送AHB_RD32(0x21)命令，验证hrdata_i输入正确接收；
+3.验证htrans_o仅输出IDLE(2'b00)和NONSEQ(2'b10)；
+4.验证hsize_o固定为WORD(3'b010)；
+5.验证hburst_o固定为SINGLE(3'b000)；
+6.模拟hready_i=0等待态，验证模块行为；
+7.模拟hresp_i=1错误响应，验证错误处理。
 期望结果：
-1.CSR通过协议命令访问正常；
-2.AHB Master访问正确；
-3.地址空间约束满足；
-4.4Byte对齐约束满足。
+1.AHB信号输出符合AHB-Lite协议规范；
+2.htrans_o仅IDLE/NONSEQ；
+3.hsize_o=WORD，hburst_o=SINGLE；
+4.hready_i等待和hresp_i错误正确处理。
 coverage check点：
-对CSR地址和AHB地址收集功能覆盖率</t>
-        </is>
-      </c>
-      <c r="D17" s="14" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="16" t="inlineStr">
-        <is>
-          <t>TC_016</t>
-        </is>
-      </c>
-      <c r="B18" s="16" t="inlineStr">
-        <is>
-          <t>test_tbus_ahb_master</t>
-        </is>
-      </c>
-      <c r="C18" s="35" t="inlineStr">
-        <is>
-          <t>配置条件：
-1.配置test_mode_i=1，CTRL.EN=1；
-2.AHB总线空闲。
-输入激励：
-1.发送AHB_WR32(0x20)命令，验证haddr_o/hwrite_o/htrans_o/hsize_o/hburst_o/hwdata_o输出正确；
-2.发送AHB_RD32(0x21)命令，验证hrdata_i/hready_i/hresp_i输入正确处理；
-3.验证htrans_o仅输出IDLE/NONSEQ；
-4.验证hsize_o固定为WORD(32-bit)；
-5.验证hburst_o固定为SINGLE。
-期望结果：
-1.AHB-Lite Master接口符合规范；
-2.单次读写事务正确；
-3.信号时序满足AHB协议要求；
-4.hresp_i=1时正确处理AHB错误。
-coverage check点：
-对AHB事务类型(读/写)和响应类型收集功能覆盖率</t>
-        </is>
-      </c>
-      <c r="D18" s="14" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="16" t="n"/>
-      <c r="B19" s="16" t="n"/>
-      <c r="C19" s="35" t="n"/>
-      <c r="D19" s="14" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="16" t="n"/>
-      <c r="B20" s="16" t="n"/>
-      <c r="C20" s="35" t="n"/>
-      <c r="D20" s="14" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="16" t="n"/>
-      <c r="B21" s="16" t="n"/>
-      <c r="C21" s="35" t="n"/>
-      <c r="D21" s="14" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="16" t="n"/>
-      <c r="B22" s="16" t="n"/>
-      <c r="C22" s="35" t="n"/>
-      <c r="D22" s="14" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="16" t="n"/>
-      <c r="B23" s="16" t="n"/>
-      <c r="C23" s="35" t="n"/>
-      <c r="D23" s="14" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="16" t="n"/>
-      <c r="B24" s="16" t="n"/>
-      <c r="C24" s="35" t="n"/>
-      <c r="D24" s="14" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="16" t="n"/>
-      <c r="B25" s="16" t="n"/>
-      <c r="C25" s="3" t="n"/>
-      <c r="D25" s="14" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="16" t="n"/>
-      <c r="B26" s="16" t="n"/>
-      <c r="C26" s="3" t="n"/>
-      <c r="D26" s="14" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="16" t="n"/>
-      <c r="B27" s="16" t="n"/>
-      <c r="C27" s="3" t="n"/>
-      <c r="D27" s="14" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="16" t="n"/>
-      <c r="B28" s="16" t="n"/>
-      <c r="C28" s="3" t="n"/>
-      <c r="D28" s="14" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="16" t="n"/>
-      <c r="B29" s="16" t="n"/>
-      <c r="C29" s="3" t="n"/>
-      <c r="D29" s="14" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="16" t="n"/>
-      <c r="B30" s="16" t="n"/>
-      <c r="C30" s="3" t="n"/>
-      <c r="D30" s="14" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="16" t="n"/>
-      <c r="B31" s="16" t="n"/>
-      <c r="C31" s="3" t="n"/>
-      <c r="D31" s="14" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="16" t="n"/>
-      <c r="B32" s="16" t="n"/>
-      <c r="C32" s="3" t="n"/>
-      <c r="D32" s="14" t="n"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="16" t="n"/>
-      <c r="B33" s="16" t="n"/>
-      <c r="C33" s="3" t="n"/>
-      <c r="D33" s="14" t="n"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="16" t="n"/>
-      <c r="B34" s="16" t="n"/>
-      <c r="C34" s="3" t="n"/>
-      <c r="D34" s="14" t="n"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="16" t="n"/>
-      <c r="B35" s="16" t="n"/>
-      <c r="C35" s="3" t="n"/>
-      <c r="D35" s="14" t="n"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="16" t="n"/>
-      <c r="B36" s="16" t="n"/>
-      <c r="C36" s="3" t="n"/>
-      <c r="D36" s="14" t="n"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="4" t="n"/>
-      <c r="B37" s="4" t="n"/>
-      <c r="C37" s="3" t="n"/>
-      <c r="D37" s="4" t="n"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="4" t="n"/>
-      <c r="B38" s="4" t="n"/>
-      <c r="C38" s="3" t="n"/>
-      <c r="D38" s="4" t="n"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="4" t="n"/>
-      <c r="B39" s="4" t="n"/>
-      <c r="C39" s="3" t="n"/>
-      <c r="D39" s="4" t="n"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="4" t="n"/>
-      <c r="B40" s="4" t="n"/>
-      <c r="C40" s="3" t="n"/>
-      <c r="D40" s="4" t="n"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="4" t="n"/>
-      <c r="B41" s="4" t="n"/>
-      <c r="C41" s="3" t="n"/>
-      <c r="D41" s="4" t="n"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="4" t="n"/>
-      <c r="B42" s="4" t="n"/>
-      <c r="C42" s="3" t="n"/>
-      <c r="D42" s="4" t="n"/>
+直接用例覆盖，不收功能覆盖率。</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>覆盖TP_016</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/RTM_AI_generated.xlsx
+++ b/RTM_AI_generated.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="600" firstSheet="0" activeTab="2" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowHeight="17655" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DR-FL" sheetId="1" state="visible" r:id="rId1"/>
@@ -12,14 +12,14 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DV Testcase List" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="0" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="23">
     <font>
       <name val="宋体"/>
       <charset val="134"/>
@@ -30,7 +30,6 @@
     <font>
       <name val="宋体"/>
       <charset val="134"/>
-      <family val="3"/>
       <color theme="1"/>
       <sz val="8"/>
       <scheme val="minor"/>
@@ -38,7 +37,6 @@
     <font>
       <name val="宋体"/>
       <charset val="134"/>
-      <family val="3"/>
       <color theme="1"/>
       <sz val="6"/>
       <scheme val="minor"/>
@@ -46,7 +44,6 @@
     <font>
       <name val="宋体"/>
       <charset val="134"/>
-      <family val="3"/>
       <b val="1"/>
       <color theme="0"/>
       <sz val="11"/>
@@ -54,29 +51,150 @@
     </font>
     <font>
       <name val="宋体"/>
-      <charset val="134"/>
-      <family val="3"/>
-      <sz val="9"/>
+      <charset val="0"/>
+      <color rgb="FF0000FF"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF800080"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FFFF0000"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
       <name val="宋体"/>
       <charset val="134"/>
-      <family val="3"/>
-      <color theme="1"/>
-      <sz val="8"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="18"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <i val="1"/>
+      <color rgb="FF7F7F7F"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
       <name val="宋体"/>
       <charset val="134"/>
-      <family val="3"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="15"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="13"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF3F3F76"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FF3F3F3F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF006100"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF9C0006"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF9C6500"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color theme="0"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="35">
     <fill>
       <patternFill/>
     </fill>
@@ -85,7 +203,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.5999938962981048"/>
+        <fgColor theme="5" tint="0.6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -95,8 +213,194 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="8">
+  <borders count="25">
     <border>
       <left/>
       <right/>
@@ -111,6 +415,19 @@
       <right style="thin">
         <color auto="1"/>
       </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
       <top style="thin">
         <color auto="1"/>
       </top>
@@ -147,6 +464,24 @@
       <left style="thin">
         <color auto="1"/>
       </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right style="thin">
         <color auto="1"/>
       </right>
@@ -163,11 +498,107 @@
       <right style="thin">
         <color auto="1"/>
       </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
       <top style="thin">
-        <color auto="1"/>
+        <color rgb="FFB2B2B2"/>
       </top>
       <bottom style="thin">
-        <color auto="1"/>
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -191,13 +622,200 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="9" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="12" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="13" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="12" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="14" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="15" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="16" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -213,111 +831,176 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -643,7 +1326,6 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
@@ -656,569 +1338,569 @@
   <dimension ref="A1:E45"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col width="13.25" customWidth="1" style="4" min="1" max="1"/>
-    <col width="13.5" customWidth="1" style="4" min="2" max="2"/>
-    <col width="14.75" customWidth="1" style="4" min="3" max="3"/>
-    <col width="85.875" customWidth="1" style="4" min="4" max="4"/>
+    <col width="13.275" customWidth="1" style="4" min="1" max="1"/>
+    <col width="13.4416666666667" customWidth="1" style="4" min="2" max="2"/>
+    <col width="14.7583333333333" customWidth="1" style="4" min="3" max="3"/>
+    <col width="46.95" customWidth="1" style="4" min="4" max="4"/>
     <col width="15.625" customWidth="1" style="4" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="32" t="inlineStr">
+      <c r="A1" s="35" t="inlineStr">
         <is>
           <t>Feature List分解表格</t>
         </is>
       </c>
-      <c r="B1" s="22" t="n"/>
-      <c r="C1" s="22" t="n"/>
-      <c r="D1" s="22" t="n"/>
-      <c r="E1" s="23" t="n"/>
-    </row>
-    <row r="2" ht="21" customHeight="1" s="28">
-      <c r="A2" s="32" t="inlineStr">
+      <c r="B1" s="43" t="n"/>
+      <c r="C1" s="43" t="n"/>
+      <c r="D1" s="43" t="n"/>
+      <c r="E1" s="44" t="n"/>
+    </row>
+    <row r="2" ht="21" customHeight="1" s="31">
+      <c r="A2" s="35" t="inlineStr">
         <is>
           <t>DR编号</t>
         </is>
       </c>
-      <c r="B2" s="32" t="inlineStr">
+      <c r="B2" s="35" t="inlineStr">
         <is>
           <t>Feature类别</t>
         </is>
       </c>
-      <c r="C2" s="32" t="inlineStr">
+      <c r="C2" s="35" t="inlineStr">
         <is>
           <t>FL编号</t>
         </is>
       </c>
-      <c r="D2" s="32" t="inlineStr">
+      <c r="D2" s="35" t="inlineStr">
         <is>
           <t>Feature描述</t>
         </is>
       </c>
-      <c r="E2" s="32" t="inlineStr">
+      <c r="E2" s="35" t="inlineStr">
         <is>
           <t>TP编号</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="27" customHeight="1" s="28">
-      <c r="A3" s="12" t="inlineStr">
+    <row r="3">
+      <c r="A3" s="37" t="inlineStr">
         <is>
           <t>DR.APLC.001</t>
         </is>
       </c>
-      <c r="B3" s="13" t="inlineStr">
+      <c r="B3" s="38" t="inlineStr">
         <is>
           <t>时钟</t>
         </is>
       </c>
-      <c r="C3" s="12" t="inlineStr">
+      <c r="C3" s="37" t="inlineStr">
         <is>
           <t>FL_001_001</t>
         </is>
       </c>
-      <c r="D3" s="15" t="inlineStr">
+      <c r="D3" s="39" t="inlineStr">
         <is>
           <t>模块采用单时钟域clk_i实现，外部协议采样、状态机控制和AHB-Lite主接口同域工作；MVP目标频率100MHz。</t>
         </is>
       </c>
-      <c r="E3" s="14" t="inlineStr">
+      <c r="E3" s="39" t="inlineStr">
         <is>
           <t>TP_001</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="27" customHeight="1" s="28">
-      <c r="A4" s="14" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="39" t="inlineStr">
         <is>
           <t>DR.APLC.001</t>
         </is>
       </c>
-      <c r="B4" s="13" t="inlineStr">
+      <c r="B4" s="38" t="inlineStr">
         <is>
           <t>复位</t>
         </is>
       </c>
-      <c r="C4" s="12" t="inlineStr">
+      <c r="C4" s="37" t="inlineStr">
         <is>
           <t>FL_002_001</t>
         </is>
       </c>
-      <c r="D4" s="15" t="inlineStr">
+      <c r="D4" s="39" t="inlineStr">
         <is>
           <t>模块支持rst_ni低有效异步复位、内部同步释放；复位后状态机回到IDLE，CTRL.EN=0，LANE_MODE=1-bit，清空协议/响应上下文和错误状态。</t>
         </is>
       </c>
-      <c r="E4" s="14" t="inlineStr">
+      <c r="E4" s="39" t="inlineStr">
         <is>
           <t>TP_002</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="27" customHeight="1" s="28">
-      <c r="A5" s="14" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="39" t="inlineStr">
         <is>
           <t>DR.APLC.001</t>
         </is>
       </c>
-      <c r="B5" s="13" t="inlineStr">
+      <c r="B5" s="38" t="inlineStr">
         <is>
           <t>寄存器</t>
         </is>
       </c>
-      <c r="C5" s="12" t="inlineStr">
+      <c r="C5" s="37" t="inlineStr">
         <is>
           <t>FL_003_001</t>
         </is>
       </c>
-      <c r="D5" s="15" t="inlineStr">
+      <c r="D5" s="39" t="inlineStr">
         <is>
           <t>模块实现CSR寄存器VERSION、CTRL、STATUS、LAST_ERR；支持通过WR_CSR/RD_CSR访问，CTRL提供EN、LANE_MODE、SOFT_RST配置，STATUS/LAST_ERR提供busy和错误可观测性。</t>
         </is>
       </c>
-      <c r="E5" s="14" t="inlineStr">
+      <c r="E5" s="39" t="inlineStr">
         <is>
           <t>TP_003</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="27" customHeight="1" s="28">
-      <c r="A6" s="14" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="39" t="inlineStr">
         <is>
           <t>DR.APLC.001</t>
         </is>
       </c>
-      <c r="B6" s="12" t="inlineStr">
+      <c r="B6" s="37" t="inlineStr">
         <is>
           <t>工作模式</t>
         </is>
       </c>
-      <c r="C6" s="12" t="inlineStr">
+      <c r="C6" s="37" t="inlineStr">
         <is>
           <t>FL_004_001</t>
         </is>
       </c>
-      <c r="D6" s="15" t="inlineStr">
+      <c r="D6" s="39" t="inlineStr">
         <is>
           <t>模块工作于ATE测试模式，test_mode_i=1且CTRL.EN=1时允许执行功能命令；协议采用半双工请求/响应模式，支持CSR访问与AHB-Lite单次读写。</t>
         </is>
       </c>
-      <c r="E6" s="14" t="inlineStr">
+      <c r="E6" s="39" t="inlineStr">
         <is>
           <t>TP_004</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="27" customHeight="1" s="28">
-      <c r="A7" s="14" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="39" t="inlineStr">
         <is>
           <t>DR.APLC.001</t>
         </is>
       </c>
-      <c r="B7" s="12" t="inlineStr">
+      <c r="B7" s="37" t="inlineStr">
         <is>
           <t>工作模式</t>
         </is>
       </c>
-      <c r="C7" s="12" t="inlineStr">
+      <c r="C7" s="37" t="inlineStr">
         <is>
           <t>FL_004_002</t>
         </is>
       </c>
-      <c r="D7" s="15" t="inlineStr">
+      <c r="D7" s="39" t="inlineStr">
         <is>
           <t>MVP版本仅支持1-bit与4-bit lane模式、Single事务和AHB-Lite后端；原始需求中的8/16-bit、Burst、AXI后端在后续版本扩展，本版明确不支持。</t>
         </is>
       </c>
-      <c r="E7" s="14" t="inlineStr">
+      <c r="E7" s="39" t="inlineStr">
         <is>
           <t>TP_005</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="27" customHeight="1" s="28">
-      <c r="A8" s="14" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="39" t="inlineStr">
         <is>
           <t>DR.APLC.001</t>
         </is>
       </c>
-      <c r="B8" s="12" t="inlineStr">
+      <c r="B8" s="37" t="inlineStr">
         <is>
           <t>数据接口</t>
         </is>
       </c>
-      <c r="C8" s="12" t="inlineStr">
+      <c r="C8" s="37" t="inlineStr">
         <is>
           <t>FL_005_001</t>
         </is>
       </c>
-      <c r="D8" s="15" t="inlineStr">
+      <c r="D8" s="39" t="inlineStr">
         <is>
           <t>外部接口采用类SPI帧式协议，使用pcs_n_i定义帧边界，pdi_i[3:0]/pdo_o[3:0]承载数据，pdo_oe_o控制输出方向；1-bit模式使用bit0，4-bit模式按高nibble优先发送。</t>
         </is>
       </c>
-      <c r="E8" s="14" t="inlineStr">
+      <c r="E8" s="39" t="inlineStr">
         <is>
           <t>TP_006</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="27" customHeight="1" s="28">
-      <c r="A9" s="14" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="39" t="inlineStr">
         <is>
           <t>DR.APLC.001</t>
         </is>
       </c>
-      <c r="B9" s="12" t="inlineStr">
+      <c r="B9" s="37" t="inlineStr">
         <is>
           <t>数据接口</t>
         </is>
       </c>
-      <c r="C9" s="12" t="inlineStr">
+      <c r="C9" s="37" t="inlineStr">
         <is>
           <t>FL_005_002</t>
         </is>
       </c>
-      <c r="D9" s="15" t="inlineStr">
+      <c r="D9" s="39" t="inlineStr">
         <is>
           <t>请求阶段输入、响应阶段输出，中间固定1个clk_i turnaround周期；协议字段按MSB first传输，支持WR_CSR、RD_CSR、AHB_WR32、AHB_RD32四类固定帧格式。</t>
         </is>
       </c>
-      <c r="E9" s="14" t="inlineStr">
+      <c r="E9" s="39" t="inlineStr">
         <is>
           <t>TP_007</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="27" customHeight="1" s="28">
-      <c r="A10" s="14" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="39" t="inlineStr">
         <is>
           <t>DR.APLC.001</t>
         </is>
       </c>
-      <c r="B10" s="12" t="inlineStr">
+      <c r="B10" s="37" t="inlineStr">
         <is>
           <t>控制接口</t>
         </is>
       </c>
-      <c r="C10" s="12" t="inlineStr">
+      <c r="C10" s="37" t="inlineStr">
         <is>
           <t>FL_006_001</t>
         </is>
       </c>
-      <c r="D10" s="15" t="inlineStr">
+      <c r="D10" s="39" t="inlineStr">
         <is>
           <t>控制命令由opcode驱动：0x10 WR_CSR、0x11 RD_CSR、0x20 AHB_WR32、0x21 AHB_RD32；前端需先收满8bit opcode后确定期望帧长并发起任务。</t>
         </is>
       </c>
-      <c r="E10" s="14" t="inlineStr">
+      <c r="E10" s="39" t="inlineStr">
         <is>
           <t>TP_008</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="27" customHeight="1" s="28">
-      <c r="A11" s="14" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="39" t="inlineStr">
         <is>
           <t>DR.APLC.001</t>
         </is>
       </c>
-      <c r="B11" s="12" t="inlineStr">
+      <c r="B11" s="37" t="inlineStr">
         <is>
           <t>配置接口</t>
         </is>
       </c>
-      <c r="C11" s="12" t="inlineStr">
+      <c r="C11" s="37" t="inlineStr">
         <is>
           <t>FL_007_001</t>
         </is>
       </c>
-      <c r="D11" s="15" t="inlineStr">
+      <c r="D11" s="39" t="inlineStr">
         <is>
           <t>CTRL寄存器支持模块使能、lane模式配置及软复位；LANE_MODE仅允许00=1-bit、01=4-bit，SOFT_RST写1触发协议上下文清零并恢复默认lane模式。</t>
         </is>
       </c>
-      <c r="E11" s="14" t="inlineStr">
+      <c r="E11" s="39" t="inlineStr">
         <is>
           <t>TP_009</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="27" customHeight="1" s="28">
-      <c r="A12" s="14" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="39" t="inlineStr">
         <is>
           <t>DR.APLC.001</t>
         </is>
       </c>
-      <c r="B12" s="12" t="inlineStr">
+      <c r="B12" s="37" t="inlineStr">
         <is>
           <t>中断</t>
         </is>
       </c>
-      <c r="C12" s="12" t="inlineStr">
+      <c r="C12" s="37" t="inlineStr">
         <is>
           <t>FL_008_001</t>
         </is>
       </c>
-      <c r="D12" s="15" t="inlineStr">
+      <c r="D12" s="39" t="inlineStr">
         <is>
           <t>MVP版本不实现独立中断输出；所有错误与完成状态通过STATUS寄存器和LAST_ERR寄存器查询，由ATE主机采用轮询方式获取。</t>
         </is>
       </c>
-      <c r="E12" s="14" t="inlineStr">
+      <c r="E12" s="39" t="inlineStr">
         <is>
           <t>TP_010</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="27" customHeight="1" s="28">
-      <c r="A13" s="14" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="39" t="inlineStr">
         <is>
           <t>DR.APLC.001</t>
         </is>
       </c>
-      <c r="B13" s="12" t="inlineStr">
+      <c r="B13" s="37" t="inlineStr">
         <is>
           <t>异常</t>
         </is>
       </c>
-      <c r="C13" s="12" t="inlineStr">
+      <c r="C13" s="37" t="inlineStr">
         <is>
           <t>FL_009_001</t>
         </is>
       </c>
-      <c r="D13" s="15" t="inlineStr">
+      <c r="D13" s="39" t="inlineStr">
         <is>
           <t>模块需对BAD_OPCODE、BAD_REG、ALIGN_ERR、DISABLED、NOT_IN_TEST、FRAME_ERR、AHB_ERR、TIMEOUT进行检测并生成确定性状态码，且在发起AHB访问前完成前置错误收敛。</t>
         </is>
       </c>
-      <c r="E13" s="14" t="inlineStr">
+      <c r="E13" s="39" t="inlineStr">
         <is>
           <t>TP_011</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="27" customHeight="1" s="28">
-      <c r="A14" s="14" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="39" t="inlineStr">
         <is>
           <t>DR.APLC.001</t>
         </is>
       </c>
-      <c r="B14" s="12" t="inlineStr">
+      <c r="B14" s="37" t="inlineStr">
         <is>
           <t>低功耗</t>
         </is>
       </c>
-      <c r="C14" s="12" t="inlineStr">
+      <c r="C14" s="37" t="inlineStr">
         <is>
           <t>FL_010_001</t>
         </is>
       </c>
-      <c r="D14" s="15" t="inlineStr">
+      <c r="D14" s="39" t="inlineStr">
         <is>
           <t>空闲态下接收/发送移位寄存器和超时计数器不更新；test_mode_i=0或无有效任务时AHB输出保持IDLE，仅在RX/TX/WAIT_AHB相关状态翻转关键寄存器。</t>
         </is>
       </c>
-      <c r="E14" s="14" t="inlineStr">
+      <c r="E14" s="39" t="inlineStr">
         <is>
           <t>TP_012</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="27" customHeight="1" s="28">
-      <c r="A15" s="14" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="39" t="inlineStr">
         <is>
           <t>DR.APLC.001</t>
         </is>
       </c>
-      <c r="B15" s="12" t="inlineStr">
+      <c r="B15" s="37" t="inlineStr">
         <is>
           <t>性能</t>
         </is>
       </c>
-      <c r="C15" s="12" t="inlineStr">
+      <c r="C15" s="37" t="inlineStr">
         <is>
           <t>FL_011_001</t>
         </is>
       </c>
-      <c r="D15" s="15" t="inlineStr">
+      <c r="D15" s="39" t="inlineStr">
         <is>
           <t>MVP目标频率100MHz；原始链路线速在1-bit模式为12.5MB/s，在4-bit模式为50MB/s；AHB接口固定32bit字访问，地址需4Byte对齐。</t>
         </is>
       </c>
-      <c r="E15" s="14" t="inlineStr">
+      <c r="E15" s="39" t="inlineStr">
         <is>
           <t>TP_013</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="27" customHeight="1" s="28">
-      <c r="A16" s="14" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="39" t="inlineStr">
         <is>
           <t>DR.APLC.001</t>
         </is>
       </c>
-      <c r="B16" s="12" t="inlineStr">
+      <c r="B16" s="37" t="inlineStr">
         <is>
           <t>DFX</t>
         </is>
       </c>
-      <c r="C16" s="12" t="inlineStr">
+      <c r="C16" s="37" t="inlineStr">
         <is>
           <t>FL_012_001</t>
         </is>
       </c>
-      <c r="D16" s="15" t="inlineStr">
+      <c r="D16" s="39" t="inlineStr">
         <is>
           <t>模块需保留状态机状态、opcode、addr、wdata、rdata、status_code、rx/tx计数等内部调试可观测点，便于联调、波形定位和故障复现。</t>
         </is>
       </c>
-      <c r="E16" s="14" t="inlineStr">
+      <c r="E16" s="39" t="inlineStr">
         <is>
           <t>TP_014</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="27" customHeight="1" s="28">
-      <c r="A17" s="14" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="39" t="inlineStr">
         <is>
           <t>DR.APLC.001</t>
         </is>
       </c>
-      <c r="B17" s="12" t="inlineStr">
+      <c r="B17" s="37" t="inlineStr">
         <is>
           <t>Memory map</t>
         </is>
       </c>
-      <c r="C17" s="12" t="inlineStr">
+      <c r="C17" s="37" t="inlineStr">
         <is>
           <t>FL_013_001</t>
         </is>
       </c>
-      <c r="D17" s="15" t="inlineStr">
+      <c r="D17" s="39" t="inlineStr">
         <is>
           <t>模块自身CSR不进入SoC AHB memory map，通过协议命令访问；对外AHB-Lite Master访问采用32bit地址空间和word访问粒度，具体可达目标地址范围由SoC顶层统一约束。</t>
         </is>
       </c>
-      <c r="E17" s="14" t="inlineStr">
+      <c r="E17" s="39" t="inlineStr">
         <is>
           <t>TP_015</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="40.5" customHeight="1" s="28">
-      <c r="A18" s="14" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="39" t="inlineStr">
         <is>
           <t>DR.APLC.001</t>
         </is>
       </c>
-      <c r="B18" s="12" t="inlineStr">
+      <c r="B18" s="37" t="inlineStr">
         <is>
           <t>总线接口</t>
         </is>
       </c>
-      <c r="C18" s="12" t="inlineStr">
+      <c r="C18" s="37" t="inlineStr">
         <is>
           <t>FL_014_001</t>
         </is>
       </c>
-      <c r="D18" s="15" t="inlineStr">
+      <c r="D18" s="39" t="inlineStr">
         <is>
           <t>外部控制命令在芯片内部转换为AHB-Lite Master单次读写事务，输出haddr/hwrite/htrans/hsize/hburst/hwdata并接收hrdata/hready/hresp；后续版本可扩展至AXI或更高吞吐后端。</t>
         </is>
       </c>
-      <c r="E18" s="14" t="inlineStr">
+      <c r="E18" s="39" t="inlineStr">
         <is>
           <t>TP_016</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="30" t="n"/>
-      <c r="B19" s="30" t="n"/>
-      <c r="C19" s="30" t="n"/>
-      <c r="D19" s="30" t="n"/>
-      <c r="E19" s="30" t="n"/>
+      <c r="A19" s="36" t="n"/>
+      <c r="B19" s="36" t="n"/>
+      <c r="C19" s="36" t="n"/>
+      <c r="D19" s="36" t="n"/>
+      <c r="E19" s="36" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="30" t="n"/>
-      <c r="B20" s="30" t="n"/>
-      <c r="C20" s="30" t="n"/>
-      <c r="D20" s="30" t="n"/>
-      <c r="E20" s="30" t="n"/>
+      <c r="A20" s="36" t="n"/>
+      <c r="B20" s="36" t="n"/>
+      <c r="C20" s="36" t="n"/>
+      <c r="D20" s="36" t="n"/>
+      <c r="E20" s="36" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="14" t="n"/>
-      <c r="B21" s="14" t="n"/>
-      <c r="C21" s="14" t="n"/>
-      <c r="D21" s="14" t="n"/>
-      <c r="E21" s="14" t="n"/>
+      <c r="A21" s="39" t="n"/>
+      <c r="B21" s="39" t="n"/>
+      <c r="C21" s="39" t="n"/>
+      <c r="D21" s="39" t="n"/>
+      <c r="E21" s="39" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="33" t="inlineStr">
+      <c r="A22" s="40" t="inlineStr">
         <is>
           <t>填写说明</t>
         </is>
       </c>
-      <c r="B22" s="22" t="n"/>
-      <c r="C22" s="22" t="n"/>
-      <c r="D22" s="22" t="n"/>
-      <c r="E22" s="23" t="n"/>
-    </row>
-    <row r="23" ht="27.95" customHeight="1" s="28">
-      <c r="A23" s="12" t="inlineStr">
+      <c r="B22" s="43" t="n"/>
+      <c r="C22" s="43" t="n"/>
+      <c r="D22" s="43" t="n"/>
+      <c r="E22" s="44" t="n"/>
+    </row>
+    <row r="23" ht="28" customHeight="1" s="31">
+      <c r="A23" s="37" t="inlineStr">
         <is>
           <t>DR编号</t>
         </is>
       </c>
-      <c r="B23" s="31" t="inlineStr">
+      <c r="B23" s="41" t="inlineStr">
         <is>
           <t>应包含’ OR-DR’ sheet中的全部DR；DR-FL可以一对多，也可以多对一； DR编号可以不是顺序的</t>
         </is>
       </c>
-      <c r="C23" s="22" t="n"/>
-      <c r="D23" s="22" t="n"/>
-      <c r="E23" s="23" t="n"/>
-    </row>
-    <row r="24" ht="60" customHeight="1" s="28">
-      <c r="A24" s="12" t="inlineStr">
+      <c r="C23" s="43" t="n"/>
+      <c r="D23" s="43" t="n"/>
+      <c r="E23" s="44" t="n"/>
+    </row>
+    <row r="24" ht="60" customHeight="1" s="31">
+      <c r="A24" s="37" t="inlineStr">
         <is>
           <t>Feature类别</t>
         </is>
       </c>
-      <c r="B24" s="29" t="inlineStr">
+      <c r="B24" s="42" t="inlineStr">
         <is>
           <t>Feature类别包括但不限于：  
 CLK, Reset, Register, 数据接口，控制接口，配置接口，工作模式，中断，异常，低功耗，性能，DFX, memory map  
 可以重复（例如不同行的Feature类别是相同的）</t>
         </is>
       </c>
-      <c r="C24" s="22" t="n"/>
-      <c r="D24" s="22" t="n"/>
-      <c r="E24" s="23" t="n"/>
-    </row>
-    <row r="25" ht="42.95" customHeight="1" s="28">
-      <c r="A25" s="12" t="inlineStr">
+      <c r="C24" s="43" t="n"/>
+      <c r="D24" s="43" t="n"/>
+      <c r="E24" s="44" t="n"/>
+    </row>
+    <row r="25" ht="43" customHeight="1" s="31">
+      <c r="A25" s="37" t="inlineStr">
         <is>
           <t>FL编号</t>
         </is>
       </c>
-      <c r="B25" s="31" t="inlineStr">
+      <c r="B25" s="41" t="inlineStr">
         <is>
           <t>FL_xxx_yyy：其中xxx是Feature类别的编号，yyy是二级feature的编号；</t>
         </is>
       </c>
-      <c r="C25" s="22" t="n"/>
-      <c r="D25" s="22" t="n"/>
-      <c r="E25" s="23" t="n"/>
-    </row>
-    <row r="26" ht="66.95" customHeight="1" s="28">
-      <c r="A26" s="12" t="inlineStr">
+      <c r="C25" s="43" t="n"/>
+      <c r="D25" s="43" t="n"/>
+      <c r="E25" s="44" t="n"/>
+    </row>
+    <row r="26" ht="67" customHeight="1" s="31">
+      <c r="A26" s="37" t="inlineStr">
         <is>
           <t>Feature描述</t>
         </is>
       </c>
-      <c r="B26" s="29" t="inlineStr">
+      <c r="B26" s="42" t="inlineStr">
         <is>
           <t>1. 不要照抄DR的内容，需进行细化  
 2. 要清晰明确，不能有模棱两可的内容  
@@ -1226,150 +1908,150 @@
 4. 和Design SPEC的配合关系：Feature描述特性，SPEC描述实现方案</t>
         </is>
       </c>
-      <c r="C26" s="22" t="n"/>
-      <c r="D26" s="22" t="n"/>
-      <c r="E26" s="23" t="n"/>
-    </row>
-    <row r="27" ht="29.1" customHeight="1" s="28">
-      <c r="A27" s="12" t="inlineStr">
+      <c r="C26" s="43" t="n"/>
+      <c r="D26" s="43" t="n"/>
+      <c r="E26" s="44" t="n"/>
+    </row>
+    <row r="27" ht="29" customHeight="1" s="31">
+      <c r="A27" s="37" t="inlineStr">
         <is>
           <t>TP编号</t>
         </is>
       </c>
-      <c r="B27" s="31" t="inlineStr">
+      <c r="B27" s="41" t="inlineStr">
         <is>
           <t>由DV owner填完FL-TP sheet后反标过来</t>
         </is>
       </c>
-      <c r="C27" s="22" t="n"/>
-      <c r="D27" s="22" t="n"/>
-      <c r="E27" s="23" t="n"/>
+      <c r="C27" s="43" t="n"/>
+      <c r="D27" s="43" t="n"/>
+      <c r="E27" s="44" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="0" t="n"/>
-      <c r="B28" s="0" t="n"/>
-      <c r="C28" s="0" t="n"/>
-      <c r="D28" s="0" t="n"/>
-      <c r="E28" s="0" t="n"/>
+      <c r="A28" s="20" t="n"/>
+      <c r="B28" s="20" t="n"/>
+      <c r="C28" s="20" t="n"/>
+      <c r="D28" s="20" t="n"/>
+      <c r="E28" s="20" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="0" t="n"/>
-      <c r="B29" s="0" t="n"/>
-      <c r="C29" s="0" t="n"/>
-      <c r="D29" s="0" t="n"/>
-      <c r="E29" s="0" t="n"/>
+      <c r="A29" s="20" t="n"/>
+      <c r="B29" s="20" t="n"/>
+      <c r="C29" s="20" t="n"/>
+      <c r="D29" s="20" t="n"/>
+      <c r="E29" s="20" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="0" t="n"/>
-      <c r="B30" s="0" t="n"/>
-      <c r="C30" s="0" t="n"/>
-      <c r="D30" s="0" t="n"/>
-      <c r="E30" s="0" t="n"/>
+      <c r="A30" s="20" t="n"/>
+      <c r="B30" s="20" t="n"/>
+      <c r="C30" s="20" t="n"/>
+      <c r="D30" s="20" t="n"/>
+      <c r="E30" s="20" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="0" t="n"/>
-      <c r="B31" s="0" t="n"/>
-      <c r="C31" s="0" t="n"/>
-      <c r="D31" s="0" t="n"/>
-      <c r="E31" s="0" t="n"/>
+      <c r="A31" s="20" t="n"/>
+      <c r="B31" s="20" t="n"/>
+      <c r="C31" s="20" t="n"/>
+      <c r="D31" s="20" t="n"/>
+      <c r="E31" s="20" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="0" t="n"/>
-      <c r="B32" s="0" t="n"/>
-      <c r="C32" s="0" t="n"/>
-      <c r="D32" s="0" t="n"/>
-      <c r="E32" s="0" t="n"/>
+      <c r="A32" s="20" t="n"/>
+      <c r="B32" s="20" t="n"/>
+      <c r="C32" s="20" t="n"/>
+      <c r="D32" s="20" t="n"/>
+      <c r="E32" s="20" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="0" t="n"/>
-      <c r="B33" s="0" t="n"/>
-      <c r="C33" s="0" t="n"/>
-      <c r="D33" s="0" t="n"/>
-      <c r="E33" s="0" t="n"/>
+      <c r="A33" s="20" t="n"/>
+      <c r="B33" s="20" t="n"/>
+      <c r="C33" s="20" t="n"/>
+      <c r="D33" s="20" t="n"/>
+      <c r="E33" s="20" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="0" t="n"/>
-      <c r="B34" s="0" t="n"/>
-      <c r="C34" s="0" t="n"/>
-      <c r="D34" s="0" t="n"/>
-      <c r="E34" s="0" t="n"/>
+      <c r="A34" s="20" t="n"/>
+      <c r="B34" s="20" t="n"/>
+      <c r="C34" s="20" t="n"/>
+      <c r="D34" s="20" t="n"/>
+      <c r="E34" s="20" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="0" t="n"/>
-      <c r="B35" s="0" t="n"/>
-      <c r="C35" s="0" t="n"/>
-      <c r="D35" s="0" t="n"/>
-      <c r="E35" s="0" t="n"/>
+      <c r="A35" s="20" t="n"/>
+      <c r="B35" s="20" t="n"/>
+      <c r="C35" s="20" t="n"/>
+      <c r="D35" s="20" t="n"/>
+      <c r="E35" s="20" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="0" t="n"/>
-      <c r="B36" s="0" t="n"/>
-      <c r="C36" s="0" t="n"/>
-      <c r="D36" s="0" t="n"/>
-      <c r="E36" s="0" t="n"/>
+      <c r="A36" s="20" t="n"/>
+      <c r="B36" s="20" t="n"/>
+      <c r="C36" s="20" t="n"/>
+      <c r="D36" s="20" t="n"/>
+      <c r="E36" s="20" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="0" t="n"/>
-      <c r="B37" s="0" t="n"/>
-      <c r="C37" s="0" t="n"/>
-      <c r="D37" s="0" t="n"/>
-      <c r="E37" s="0" t="n"/>
+      <c r="A37" s="20" t="n"/>
+      <c r="B37" s="20" t="n"/>
+      <c r="C37" s="20" t="n"/>
+      <c r="D37" s="20" t="n"/>
+      <c r="E37" s="20" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="0" t="n"/>
-      <c r="B38" s="0" t="n"/>
-      <c r="C38" s="0" t="n"/>
-      <c r="D38" s="0" t="n"/>
-      <c r="E38" s="0" t="n"/>
+      <c r="A38" s="20" t="n"/>
+      <c r="B38" s="20" t="n"/>
+      <c r="C38" s="20" t="n"/>
+      <c r="D38" s="20" t="n"/>
+      <c r="E38" s="20" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="0" t="n"/>
-      <c r="B39" s="0" t="n"/>
-      <c r="C39" s="0" t="n"/>
-      <c r="D39" s="0" t="n"/>
-      <c r="E39" s="0" t="n"/>
+      <c r="A39" s="20" t="n"/>
+      <c r="B39" s="20" t="n"/>
+      <c r="C39" s="20" t="n"/>
+      <c r="D39" s="20" t="n"/>
+      <c r="E39" s="20" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="0" t="n"/>
-      <c r="B40" s="0" t="n"/>
-      <c r="C40" s="0" t="n"/>
-      <c r="D40" s="0" t="n"/>
-      <c r="E40" s="0" t="n"/>
+      <c r="A40" s="20" t="n"/>
+      <c r="B40" s="20" t="n"/>
+      <c r="C40" s="20" t="n"/>
+      <c r="D40" s="20" t="n"/>
+      <c r="E40" s="20" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="0" t="n"/>
-      <c r="B41" s="0" t="n"/>
-      <c r="C41" s="0" t="n"/>
-      <c r="D41" s="0" t="n"/>
-      <c r="E41" s="0" t="n"/>
+      <c r="A41" s="20" t="n"/>
+      <c r="B41" s="20" t="n"/>
+      <c r="C41" s="20" t="n"/>
+      <c r="D41" s="20" t="n"/>
+      <c r="E41" s="20" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="0" t="n"/>
-      <c r="B42" s="0" t="n"/>
-      <c r="C42" s="0" t="n"/>
-      <c r="D42" s="0" t="n"/>
-      <c r="E42" s="0" t="n"/>
+      <c r="A42" s="20" t="n"/>
+      <c r="B42" s="20" t="n"/>
+      <c r="C42" s="20" t="n"/>
+      <c r="D42" s="20" t="n"/>
+      <c r="E42" s="20" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="0" t="n"/>
-      <c r="B43" s="0" t="n"/>
-      <c r="C43" s="0" t="n"/>
-      <c r="D43" s="0" t="n"/>
-      <c r="E43" s="0" t="n"/>
+      <c r="A43" s="20" t="n"/>
+      <c r="B43" s="20" t="n"/>
+      <c r="C43" s="20" t="n"/>
+      <c r="D43" s="20" t="n"/>
+      <c r="E43" s="20" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" s="0" t="n"/>
-      <c r="B44" s="0" t="n"/>
-      <c r="C44" s="0" t="n"/>
-      <c r="D44" s="0" t="n"/>
-      <c r="E44" s="0" t="n"/>
+      <c r="A44" s="20" t="n"/>
+      <c r="B44" s="20" t="n"/>
+      <c r="C44" s="20" t="n"/>
+      <c r="D44" s="20" t="n"/>
+      <c r="E44" s="20" t="n"/>
     </row>
     <row r="45">
-      <c r="A45" s="8" t="n"/>
-      <c r="B45" s="8" t="n"/>
-      <c r="C45" s="8" t="n"/>
-      <c r="D45" s="8" t="n"/>
-      <c r="E45" s="8" t="n"/>
+      <c r="A45" s="28" t="n"/>
+      <c r="B45" s="28" t="n"/>
+      <c r="C45" s="28" t="n"/>
+      <c r="D45" s="28" t="n"/>
+      <c r="E45" s="28" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -1394,645 +2076,662 @@
   <dimension ref="A1:F28"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col width="12.375" customWidth="1" style="28" min="1" max="1"/>
-    <col width="13.5" customWidth="1" style="28" min="2" max="2"/>
-    <col width="12.625" customWidth="1" style="28" min="3" max="3"/>
-    <col width="98.375" customWidth="1" style="28" min="4" max="4"/>
-    <col width="13.875" customWidth="1" style="28" min="5" max="5"/>
-    <col width="15.75" customWidth="1" style="28" min="6" max="6"/>
+    <col width="12.4083333333333" customWidth="1" style="31" min="1" max="1"/>
+    <col width="13.4416666666667" customWidth="1" style="31" min="2" max="2"/>
+    <col width="12.575" customWidth="1" style="31" min="3" max="3"/>
+    <col width="68.7083333333333" customWidth="1" style="31" min="4" max="4"/>
+    <col width="13.8416666666667" customWidth="1" style="31" min="5" max="5"/>
+    <col width="15.7583333333333" customWidth="1" style="31" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26.1" customHeight="1" s="28">
-      <c r="A1" s="32" t="inlineStr">
+    <row r="1" ht="26" customHeight="1" s="31">
+      <c r="A1" s="5" t="inlineStr">
         <is>
           <t>TestPoint分解表格</t>
         </is>
       </c>
-      <c r="B1" s="22" t="n"/>
-      <c r="C1" s="22" t="n"/>
-      <c r="D1" s="22" t="n"/>
-      <c r="E1" s="22" t="n"/>
-      <c r="F1" s="23" t="n"/>
-    </row>
-    <row r="2" ht="29.1" customHeight="1" s="28">
-      <c r="A2" s="24" t="inlineStr">
+      <c r="B1" s="29" t="n"/>
+      <c r="C1" s="29" t="n"/>
+      <c r="D1" s="29" t="n"/>
+      <c r="E1" s="29" t="n"/>
+      <c r="F1" s="30" t="n"/>
+    </row>
+    <row r="2" ht="29" customHeight="1" s="31">
+      <c r="A2" s="5" t="inlineStr">
         <is>
           <t>Feature编号</t>
         </is>
       </c>
-      <c r="B2" s="24" t="inlineStr">
+      <c r="B2" s="5" t="inlineStr">
         <is>
           <t>TP类别</t>
         </is>
       </c>
-      <c r="C2" s="24" t="inlineStr">
+      <c r="C2" s="5" t="inlineStr">
         <is>
           <t>TP编号</t>
         </is>
       </c>
-      <c r="D2" s="24" t="inlineStr">
+      <c r="D2" s="5" t="inlineStr">
         <is>
           <t>TP描述</t>
         </is>
       </c>
-      <c r="E2" s="24" t="inlineStr">
+      <c r="E2" s="5" t="inlineStr">
         <is>
           <t>checker编号</t>
         </is>
       </c>
-      <c r="F2" s="24" t="inlineStr">
+      <c r="F2" s="5" t="inlineStr">
         <is>
           <t>Testcase编号</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="40.5" customHeight="1" s="28">
-      <c r="A3" s="21" t="inlineStr">
+    <row r="3" ht="49" customHeight="1" s="31">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>FL_001_001</t>
         </is>
       </c>
-      <c r="B3" s="21" t="inlineStr">
+      <c r="B3" s="6" t="inlineStr">
         <is>
           <t>时钟</t>
         </is>
       </c>
-      <c r="C3" s="21" t="inlineStr">
+      <c r="C3" s="6" t="inlineStr">
         <is>
           <t>TP_001</t>
         </is>
       </c>
-      <c r="D3" s="19" t="inlineStr">
+      <c r="D3" s="16" t="inlineStr">
         <is>
           <t>条件：配置clk_i时钟频率为100MHz，验证模块时钟域同步性。
 激励：连续发送AHB_RD32和AHB_WR32命令，覆盖1-bit和4-bit两种lane模式。
-期望：所有命令在100MHz频率下正确执行，协议采样、状态机控制和AHB-Lite主接口同域工作正常。</t>
-        </is>
-      </c>
-      <c r="E3" s="21" t="inlineStr">
+期望：所有命令在100MHz频率下正确执行，协议采样、状态机控制和AHB-Lite主接口同域工作正常，无时序违例。</t>
+        </is>
+      </c>
+      <c r="E3" s="6" t="inlineStr">
         <is>
           <t>CHK_001</t>
         </is>
       </c>
-      <c r="F3" s="21" t="inlineStr">
-        <is>
-          <t>TC_001</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="54" customHeight="1" s="28">
-      <c r="A4" s="21" t="inlineStr">
+      <c r="F3" s="6" t="inlineStr">
+        <is>
+          <t>DV_TC_001</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="82" customHeight="1" s="31">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>FL_002_001</t>
         </is>
       </c>
-      <c r="B4" s="21" t="inlineStr">
+      <c r="B4" s="6" t="inlineStr">
         <is>
           <t>复位</t>
         </is>
       </c>
-      <c r="C4" s="21" t="inlineStr">
+      <c r="C4" s="6" t="inlineStr">
         <is>
           <t>TP_002</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="D4" s="16" t="inlineStr">
         <is>
           <t>条件：初始状态rst_ni为低，模块处于复位状态。
 激励：1) 释放rst_ni，验证复位后状态机回到IDLE；2) 检查CTRL.EN=0，LANE_MODE=1-bit默认值；3) 验证协议上下文和错误状态已清空。
 期望：复位后状态机处于IDLE，CTRL寄存器默认值正确，STATUS/LAST_ERR清零，无残留状态。</t>
         </is>
       </c>
-      <c r="E4" s="21" t="inlineStr">
+      <c r="E4" s="6" t="inlineStr">
         <is>
           <t>CHK_002</t>
         </is>
       </c>
-      <c r="F4" s="21" t="inlineStr">
-        <is>
-          <t>TC_002</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="54" customHeight="1" s="28">
-      <c r="A5" s="21" t="inlineStr">
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>DV_TC_002</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="44" customHeight="1" s="31">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>FL_003_001</t>
         </is>
       </c>
-      <c r="B5" s="21" t="inlineStr">
+      <c r="B5" s="6" t="inlineStr">
         <is>
           <t>寄存器</t>
         </is>
       </c>
-      <c r="C5" s="21" t="inlineStr">
+      <c r="C5" s="6" t="inlineStr">
         <is>
           <t>TP_003</t>
         </is>
       </c>
-      <c r="D5" s="7" t="inlineStr">
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>条件：模块使能(test_mode_i=1, CTRL.EN=1)。
 激励：1) 通过RD_CSR读取VERSION寄存器验证版本号；2) 通过WR_CSR/RD_CSR访问CTRL寄存器配置EN、LANE_MODE、SOFT_RST；3) 读取STATUS/LAST_ERR检查busy和错误状态。
 期望：CSR读写正确，VERSION返回预期值，CTRL配置生效，STATUS/LAST_ERR反映正确状态。</t>
         </is>
       </c>
-      <c r="E5" s="21" t="inlineStr">
+      <c r="E5" s="6" t="inlineStr">
         <is>
           <t>CHK_003</t>
         </is>
       </c>
-      <c r="F5" s="21" t="inlineStr">
-        <is>
-          <t>TC_003</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="54" customHeight="1" s="28">
-      <c r="A6" s="21" t="inlineStr">
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>DV_TC_003</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="26" customHeight="1" s="31">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>FL_004_001</t>
         </is>
       </c>
-      <c r="B6" s="21" t="inlineStr">
+      <c r="B6" s="6" t="inlineStr">
         <is>
           <t>工作模式</t>
         </is>
       </c>
-      <c r="C6" s="21" t="inlineStr">
+      <c r="C6" s="6" t="inlineStr">
         <is>
           <t>TP_004</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="D6" s="4" t="inlineStr">
         <is>
           <t>条件：配置test_mode_i=1，通过WR_CSR设置CTRL.EN=1。
 激励：1) 发送WR_CSR命令配置lane模式；2) 发送AHB_WR32/AHB_RD32命令进行单次读写操作；3) 验证半双工请求/响应模式工作正常。
 期望：模块正确执行功能命令，协议采用半双工模式，CSR访问与AHB-Lite单次读写正常。</t>
         </is>
       </c>
-      <c r="E6" s="21" t="inlineStr">
+      <c r="E6" s="6" t="inlineStr">
         <is>
           <t>CHK_004</t>
         </is>
       </c>
-      <c r="F6" s="21" t="inlineStr">
-        <is>
-          <t>TC_004</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="54" customHeight="1" s="28">
-      <c r="A7" s="21" t="inlineStr">
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>DV_TC_004</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="28" customHeight="1" s="31">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>FL_004_002</t>
         </is>
       </c>
-      <c r="B7" s="21" t="inlineStr">
+      <c r="B7" s="6" t="inlineStr">
         <is>
           <t>工作模式</t>
         </is>
       </c>
-      <c r="C7" s="21" t="inlineStr">
+      <c r="C7" s="6" t="inlineStr">
         <is>
           <t>TP_005</t>
         </is>
       </c>
-      <c r="D7" s="7" t="inlineStr">
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>条件：模块使能状态。
 激励：1) 配置LANE_MODE=00验证1-bit模式；2) 配置LANE_MODE=01验证4-bit模式；3) 尝试配置非法LANE_MODE值(02/03)验证错误处理；4) 验证不支持Burst和AXI后端。
 期望：1-bit和4-bit模式正常工作，非法配置返回错误码，Burst和AXI功能确认不可用。</t>
         </is>
       </c>
-      <c r="E7" s="21" t="inlineStr">
-        <is>
-          <t>CHK_004</t>
-        </is>
-      </c>
-      <c r="F7" s="21" t="inlineStr">
-        <is>
-          <t>TC_004</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="54" customHeight="1" s="28">
-      <c r="A8" s="21" t="inlineStr">
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>CHK_005</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>DV_TC_005</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="30" customHeight="1" s="31">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>FL_005_001</t>
         </is>
       </c>
-      <c r="B8" s="21" t="inlineStr">
+      <c r="B8" s="6" t="inlineStr">
         <is>
           <t>数据接口</t>
         </is>
       </c>
-      <c r="C8" s="21" t="inlineStr">
+      <c r="C8" s="6" t="inlineStr">
         <is>
           <t>TP_006</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="D8" s="4" t="inlineStr">
         <is>
           <t>条件：模块使能，配置1-bit和4-bit lane模式。
 激励：1) 在1-bit模式下发送WR_CSR/AHB_WR32命令，验证pdi_i[0]/pdo_o[0]数据传输；2) 在4-bit模式下发送相同命令，验证pdi_i[3:0]/pdo_o[3:0]按高nibble优先发送；3) 验证pcs_n_i帧边界正确。
 期望：数据接口按lane模式正确传输，帧边界清晰，MSB first顺序正确。</t>
         </is>
       </c>
-      <c r="E8" s="21" t="inlineStr">
-        <is>
-          <t>CHK_005</t>
-        </is>
-      </c>
-      <c r="F8" s="21" t="inlineStr">
-        <is>
-          <t>TC_005</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="54" customHeight="1" s="28">
-      <c r="A9" s="21" t="inlineStr">
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>CHK_006</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>DV_TC_006</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="30" customHeight="1" s="31">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>FL_005_002</t>
         </is>
       </c>
-      <c r="B9" s="21" t="inlineStr">
+      <c r="B9" s="6" t="inlineStr">
         <is>
           <t>数据接口</t>
         </is>
       </c>
-      <c r="C9" s="21" t="inlineStr">
+      <c r="C9" s="6" t="inlineStr">
         <is>
           <t>TP_007</t>
         </is>
       </c>
-      <c r="D9" s="7" t="inlineStr">
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>条件：模块使能，配置不同lane模式。
 激励：1) 发送WR_CSR(0x10)命令验证请求阶段；2) 验证turnaround周期(1个clk_i)；3) 检查响应阶段pdo_oe_o输出使能；4) 验证四种命令帧格式：WR_CSR(0x10)、RD_CSR(0x11)、AHB_WR32(0x20)、AHB_RD32(0x21)。
 期望：请求/响应阶段正确分离，turnaround固定1周期，协议字段MSB first传输，四种帧格式正确处理。</t>
         </is>
       </c>
-      <c r="E9" s="21" t="inlineStr">
-        <is>
-          <t>CHK_005</t>
-        </is>
-      </c>
-      <c r="F9" s="21" t="inlineStr">
-        <is>
-          <t>TC_006</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="54" customHeight="1" s="28">
-      <c r="A10" s="21" t="inlineStr">
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>CHK_007</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>DV_TC_007</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="25" customHeight="1" s="31">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>FL_006_001</t>
         </is>
       </c>
-      <c r="B10" s="21" t="inlineStr">
+      <c r="B10" s="6" t="inlineStr">
         <is>
           <t>控制接口</t>
         </is>
       </c>
-      <c r="C10" s="21" t="inlineStr">
+      <c r="C10" s="6" t="inlineStr">
         <is>
           <t>TP_008</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="D10" s="4" t="inlineStr">
         <is>
           <t>条件：模块使能，AHB总线空闲。
 激励：1) 发送opcode=0x10执行WR_CSR命令；2) 发送opcode=0x11执行RD_CSR命令；3) 发送opcode=0x20执行AHB_WR32命令；4) 发送opcode=0x21执行AHB_RD32命令；5) 发送非法opcode(如0x00/0xFF)验证错误处理。
 期望：四种opcode正确译码并执行，非法opcode返回STS_BAD_OPCODE(0x01)，前端正确确定期望帧长。</t>
         </is>
       </c>
-      <c r="E10" s="21" t="inlineStr">
-        <is>
-          <t>CHK_006</t>
-        </is>
-      </c>
-      <c r="F10" s="21" t="inlineStr">
-        <is>
-          <t>TC_007</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="67.5" customHeight="1" s="28">
-      <c r="A11" s="21" t="inlineStr">
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>CHK_008</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t>DV_TC_008</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="29" customHeight="1" s="31">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t>FL_007_001</t>
         </is>
       </c>
-      <c r="B11" s="21" t="inlineStr">
+      <c r="B11" s="6" t="inlineStr">
         <is>
           <t>配置接口</t>
         </is>
       </c>
-      <c r="C11" s="21" t="inlineStr">
+      <c r="C11" s="6" t="inlineStr">
         <is>
           <t>TP_009</t>
         </is>
       </c>
-      <c r="D11" s="7" t="inlineStr">
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t>条件：模块使能。
 激励：1) 写CTRL.EN=1使能模块，验证功能命令可执行；2) 写CTRL.EN=0禁用模块，验证命令返回DISABLED错误；3) 配置LANE_MODE=00/01验证lane模式切换；4) 写CTRL.SOFT_RST=1触发软复位，验证协议上下文清零并恢复默认lane模式。
 期望：CTRL配置正确生效，使能/禁用状态切换正确，软复位功能正常。</t>
         </is>
       </c>
-      <c r="E11" s="21" t="inlineStr">
-        <is>
-          <t>CHK_007</t>
-        </is>
-      </c>
-      <c r="F11" s="21" t="inlineStr">
-        <is>
-          <t>TC_008</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="54" customHeight="1" s="28">
-      <c r="A12" s="21" t="inlineStr">
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>CHK_009</t>
+        </is>
+      </c>
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t>DV_TC_009</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="27" customHeight="1" s="31">
+      <c r="A12" s="6" t="inlineStr">
         <is>
           <t>FL_008_001</t>
         </is>
       </c>
-      <c r="B12" s="21" t="inlineStr">
+      <c r="B12" s="6" t="inlineStr">
         <is>
           <t>中断</t>
         </is>
       </c>
-      <c r="C12" s="21" t="inlineStr">
+      <c r="C12" s="6" t="inlineStr">
         <is>
           <t>TP_010</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="D12" s="4" t="inlineStr">
         <is>
           <t>条件：模块使能，执行各类命令。
 激励：1) 触发各类错误条件(非法opcode、帧错误、AHB错误等)；2) 通过RD_CSR读取STATUS寄存器检查sticky位；3) 读取LAST_ERR寄存器获取最近错误码；4) 验证无独立中断输出。
 期望：所有错误与完成状态通过STATUS/LAST_ERR查询获取，MVP版本无中断输出，ATE轮询方式正确获取状态。</t>
         </is>
       </c>
-      <c r="E12" s="21" t="inlineStr">
-        <is>
-          <t>CHK_008</t>
-        </is>
-      </c>
-      <c r="F12" s="21" t="inlineStr">
-        <is>
-          <t>TC_009</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="81" customHeight="1" s="28">
-      <c r="A13" s="21" t="inlineStr">
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>CHK_010</t>
+        </is>
+      </c>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>DV_TC_010</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="21" customHeight="1" s="31">
+      <c r="A13" s="6" t="inlineStr">
         <is>
           <t>FL_009_001</t>
         </is>
       </c>
-      <c r="B13" s="21" t="inlineStr">
+      <c r="B13" s="6" t="inlineStr">
         <is>
           <t>异常</t>
         </is>
       </c>
-      <c r="C13" s="21" t="inlineStr">
+      <c r="C13" s="6" t="inlineStr">
         <is>
           <t>TP_011</t>
         </is>
       </c>
-      <c r="D13" s="7" t="inlineStr">
+      <c r="D13" s="4" t="inlineStr">
         <is>
           <t>条件：模块使能，AHB总线正常。
 激励：1) 发送非法opcode(0x00/0xFF)验证BAD_OPCODE错误(0x01)；2) 访问非法CSR地址验证BAD_REG错误(0x02)；3) 发送非4Byte对齐地址验证ALIGN_ERR错误(0x03)；4) CTRL.EN=0时发送命令验证DISABLED错误(0x04)；5) test_mode_i=0时发送命令验证NOT_IN_TEST错误(0x05)；6) 提前拉高pcs_n_i验证FRAME_ERR错误(0x06)；7) 触发hresp_i=1验证AHB_ERR错误(0x07)；8) 模拟AHB超时验证TIMEOUT错误(0x08)。
 期望：各类错误正确检测，在发起AHB访问前完成前置错误收敛，返回确定性状态码，LAST_ERR更新正确。</t>
         </is>
       </c>
-      <c r="E13" s="21" t="inlineStr">
-        <is>
-          <t>CHK_009</t>
-        </is>
-      </c>
-      <c r="F13" s="21" t="inlineStr">
-        <is>
-          <t>TC_010</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="54" customHeight="1" s="28">
-      <c r="A14" s="21" t="inlineStr">
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>CHK_011</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t>DV_TC_011</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="23" customHeight="1" s="31">
+      <c r="A14" s="6" t="inlineStr">
         <is>
           <t>FL_010_001</t>
         </is>
       </c>
-      <c r="B14" s="21" t="inlineStr">
+      <c r="B14" s="6" t="inlineStr">
         <is>
           <t>低功耗</t>
         </is>
       </c>
-      <c r="C14" s="21" t="inlineStr">
+      <c r="C14" s="6" t="inlineStr">
         <is>
           <t>TP_012</t>
         </is>
       </c>
-      <c r="D14" s="7" t="inlineStr">
+      <c r="D14" s="4" t="inlineStr">
         <is>
           <t>条件：模块处于空闲态(test_mode_i=0或无有效任务)。
 激励：1) 保持pcs_n_i=1验证接收/发送移位寄存器不翻转；2) 模拟AHB等待态验证超时计数器仅在此状态工作；3) test_mode_i=0时验证AHB输出保持IDLE；4) 切换到工作态验证关键寄存器翻转。
 期望：空闲态无效翻转最小化，低功耗设计目标满足，功耗测试通过。</t>
         </is>
       </c>
-      <c r="E14" s="21" t="inlineStr">
-        <is>
-          <t>CHK_010</t>
-        </is>
-      </c>
-      <c r="F14" s="21" t="inlineStr">
-        <is>
-          <t>TC_011</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="67.5" customHeight="1" s="28">
-      <c r="A15" s="21" t="inlineStr">
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>CHK_012</t>
+        </is>
+      </c>
+      <c r="F14" s="6" t="inlineStr">
+        <is>
+          <t>DV_TC_012</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="25" customHeight="1" s="31">
+      <c r="A15" s="6" t="inlineStr">
         <is>
           <t>FL_011_001</t>
         </is>
       </c>
-      <c r="B15" s="21" t="inlineStr">
+      <c r="B15" s="6" t="inlineStr">
         <is>
           <t>性能</t>
         </is>
       </c>
-      <c r="C15" s="21" t="inlineStr">
+      <c r="C15" s="6" t="inlineStr">
         <is>
           <t>TP_013</t>
         </is>
       </c>
-      <c r="D15" s="7" t="inlineStr">
+      <c r="D15" s="4" t="inlineStr">
         <is>
           <t>条件：配置clk_i=100MHz，AHB总线响应正常。
 激励：1) 在1-bit模式下连续执行AHB_RD32/AHB_WR32命令，计算端到端延时和吞吐率；2) 在4-bit模式下执行相同测试；3) 验证原始链路线速：1-bit模式12.5MB/s，4-bit模式50MB/s；4) 验证AHB接口32bit字访问和4Byte对齐约束。
 期望：目标频率100MHz稳定工作，延时符合预期(约23~24 cycles)，吞吐率达标，AHB访问约束满足。</t>
         </is>
       </c>
-      <c r="E15" s="21" t="inlineStr">
-        <is>
-          <t>CHK_011</t>
-        </is>
-      </c>
-      <c r="F15" s="21" t="inlineStr">
-        <is>
-          <t>TC_012</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="54" customHeight="1" s="28">
-      <c r="A16" s="21" t="inlineStr">
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>CHK_013</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>DV_TC_013</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="22" customHeight="1" s="31">
+      <c r="A16" s="6" t="inlineStr">
         <is>
           <t>FL_012_001</t>
         </is>
       </c>
-      <c r="B16" s="21" t="inlineStr">
+      <c r="B16" s="6" t="inlineStr">
         <is>
           <t>DFX</t>
         </is>
       </c>
-      <c r="C16" s="21" t="inlineStr">
+      <c r="C16" s="6" t="inlineStr">
         <is>
           <t>TP_014</t>
         </is>
       </c>
-      <c r="D16" s="7" t="inlineStr">
+      <c r="D16" s="4" t="inlineStr">
         <is>
           <t>条件：仿真环境，模块使能。
 激励：1) 执行多种命令序列；2) 采集状态机状态、opcode、addr、wdata、rdata、status_code；3) 采集rx/tx计数、pcs_n_i、pdi_i、pdo_o、pdo_oe_o；4) 验证内部调试可观测点可访问。
 期望：所有调试可观测点可采集，便于联调、波形定位和故障复现。</t>
         </is>
       </c>
-      <c r="E16" s="21" t="inlineStr">
-        <is>
-          <t>CHK_012</t>
-        </is>
-      </c>
-      <c r="F16" s="21" t="inlineStr">
-        <is>
-          <t>TC_013</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="67.5" customHeight="1" s="28">
-      <c r="A17" s="21" t="inlineStr">
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>CHK_014</t>
+        </is>
+      </c>
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t>DV_TC_014</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="24" customHeight="1" s="31">
+      <c r="A17" s="6" t="inlineStr">
         <is>
           <t>FL_013_001</t>
         </is>
       </c>
-      <c r="B17" s="21" t="inlineStr">
+      <c r="B17" s="6" t="inlineStr">
         <is>
           <t>Memory map</t>
         </is>
       </c>
-      <c r="C17" s="21" t="inlineStr">
+      <c r="C17" s="6" t="inlineStr">
         <is>
           <t>TP_015</t>
         </is>
       </c>
-      <c r="D17" s="7" t="inlineStr">
+      <c r="D17" s="4" t="inlineStr">
         <is>
           <t>条件：模块使能。
 激励：1) 通过WR_CSR/RD_CSR访问模块内部CSR寄存器(VERSION/CTRL/STATUS/LAST_ERR)；2) 发送AHB_WR32/AHB_RD32命令访问SoC内部memory-mapped地址；3) 验证模块自身CSR不进入SoC AHB memory map；4) 验证AHB Master访问采用32bit地址空间和word访问粒度。
 期望：CSR通过协议命令访问正常，AHB Master访问正确，地址空间约束满足。</t>
         </is>
       </c>
-      <c r="E17" s="21" t="inlineStr">
-        <is>
-          <t>CHK_013</t>
-        </is>
-      </c>
-      <c r="F17" s="21" t="inlineStr">
-        <is>
-          <t>TC_014</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="67.5" customHeight="1" s="28">
-      <c r="A18" s="21" t="inlineStr">
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>CHK_015</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t>DV_TC_015</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="23" customHeight="1" s="31">
+      <c r="A18" s="6" t="inlineStr">
         <is>
           <t>FL_014_001</t>
         </is>
       </c>
-      <c r="B18" s="21" t="inlineStr">
+      <c r="B18" s="6" t="inlineStr">
         <is>
           <t>总线接口</t>
         </is>
       </c>
-      <c r="C18" s="21" t="inlineStr">
+      <c r="C18" s="6" t="inlineStr">
         <is>
           <t>TP_016</t>
         </is>
       </c>
-      <c r="D18" s="7" t="inlineStr">
+      <c r="D18" s="4" t="inlineStr">
         <is>
           <t>条件：模块使能，AHB总线空闲。
 激励：1) 发送AHB_WR32命令，验证haddr_o/hwrite_o/htrans_o/hsize_o/hburst_o/hwdata_o输出正确；2) 发送AHB_RD32命令，验证hrdata_i/hready_i/hresp_i输入正确处理；3) 验证htrans_o仅输出IDLE/NONSEQ；4) 验证hsize_o固定为WORD(32-bit)；5) 验证hburst_o固定为SINGLE。
 期望：AHB-Lite Master接口符合规范，单次读写事务正确，信号时序满足AHB协议要求。</t>
         </is>
       </c>
-      <c r="E18" s="21" t="inlineStr">
-        <is>
-          <t>CHK_014</t>
-        </is>
-      </c>
-      <c r="F18" s="21" t="inlineStr">
-        <is>
-          <t>TC_015</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="24" customHeight="1" s="28">
-      <c r="A19" s="21" t="n"/>
-      <c r="B19" s="21" t="n"/>
-      <c r="C19" s="21" t="n"/>
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>CHK_016</t>
+        </is>
+      </c>
+      <c r="F18" s="6" t="inlineStr">
+        <is>
+          <t>DV_TC_016</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="24" customHeight="1" s="31">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>xxx</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>DFX</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>TP_017</t>
+        </is>
+      </c>
       <c r="D19" s="4" t="n"/>
-      <c r="E19" s="21" t="n"/>
-      <c r="F19" s="21" t="n"/>
-    </row>
-    <row r="20"/>
-    <row r="21"/>
-    <row r="22"/>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>CHK_005</t>
+        </is>
+      </c>
+      <c r="F19" s="6" t="inlineStr">
+        <is>
+          <t>DV_TC_017</t>
+        </is>
+      </c>
+    </row>
     <row r="23">
-      <c r="A23" s="27" t="inlineStr">
+      <c r="A23" s="8" t="inlineStr">
         <is>
           <t>填写说明</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="54.95" customHeight="1" s="28">
-      <c r="A24" s="21" t="inlineStr">
+    <row r="24" ht="55" customHeight="1" s="31">
+      <c r="A24" s="6" t="inlineStr">
         <is>
           <t>Feature编号</t>
         </is>
       </c>
-      <c r="B24" s="29" t="inlineStr">
+      <c r="B24" s="17" t="inlineStr">
         <is>
           <t>1. 应包含’ DR-FL’ sheet中的全部feature;
 2. Feature-TP可以一对多，也可以多对一！
 3. Feature编号可以不是顺序的</t>
         </is>
       </c>
-      <c r="C24" s="22" t="n"/>
-      <c r="D24" s="22" t="n"/>
-      <c r="E24" s="22" t="n"/>
-      <c r="F24" s="23" t="n"/>
-    </row>
-    <row r="25" ht="71.09999999999999" customHeight="1" s="28">
-      <c r="A25" s="21" t="inlineStr">
+      <c r="C24" s="29" t="n"/>
+      <c r="D24" s="29" t="n"/>
+      <c r="E24" s="29" t="n"/>
+      <c r="F24" s="30" t="n"/>
+    </row>
+    <row r="25" ht="71" customHeight="1" s="31">
+      <c r="A25" s="6" t="inlineStr">
         <is>
           <t>TP类别</t>
         </is>
       </c>
-      <c r="B25" s="29" t="inlineStr">
+      <c r="B25" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">1.TestPoint类别包括但不限于：
 CLK，Reset，Register，数据接口，控制接口，配置接口，工作模式，中断，异常，低功耗，性能，DFX、设备兼容性
@@ -2041,59 +2740,59 @@
 </t>
         </is>
       </c>
-      <c r="C25" s="22" t="n"/>
-      <c r="D25" s="22" t="n"/>
-      <c r="E25" s="22" t="n"/>
-      <c r="F25" s="23" t="n"/>
-    </row>
-    <row r="26" ht="45.95" customHeight="1" s="28">
-      <c r="A26" s="21" t="inlineStr">
+      <c r="C25" s="29" t="n"/>
+      <c r="D25" s="29" t="n"/>
+      <c r="E25" s="29" t="n"/>
+      <c r="F25" s="30" t="n"/>
+    </row>
+    <row r="26" ht="46" customHeight="1" s="31">
+      <c r="A26" s="6" t="inlineStr">
         <is>
           <t>TP编号</t>
         </is>
       </c>
-      <c r="B26" s="29" t="inlineStr">
+      <c r="B26" s="17" t="inlineStr">
         <is>
           <t>1. 所有FL编号必须要有对应的TP编号。如无，要重点解释说明  
 2. 允许TP编号没有对应的FL编号，即允许TP比FL多（例如’设备兼容性’这类TP）</t>
         </is>
       </c>
-      <c r="C26" s="22" t="n"/>
-      <c r="D26" s="22" t="n"/>
-      <c r="E26" s="22" t="n"/>
-      <c r="F26" s="23" t="n"/>
-    </row>
-    <row r="27" ht="38.1" customHeight="1" s="28">
-      <c r="A27" s="21" t="inlineStr">
+      <c r="C26" s="29" t="n"/>
+      <c r="D26" s="29" t="n"/>
+      <c r="E26" s="29" t="n"/>
+      <c r="F26" s="30" t="n"/>
+    </row>
+    <row r="27" ht="38" customHeight="1" s="31">
+      <c r="A27" s="6" t="inlineStr">
         <is>
           <t>Testcase编号</t>
         </is>
       </c>
-      <c r="B27" s="31" t="inlineStr">
+      <c r="B27" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve"> 如果多个Testcase都可以cover同一个TP，写一个即可</t>
         </is>
       </c>
-      <c r="C27" s="22" t="n"/>
-      <c r="D27" s="22" t="n"/>
-      <c r="E27" s="22" t="n"/>
-      <c r="F27" s="23" t="n"/>
-    </row>
-    <row r="28" ht="41.1" customHeight="1" s="28">
-      <c r="A28" s="21" t="inlineStr">
+      <c r="C27" s="29" t="n"/>
+      <c r="D27" s="29" t="n"/>
+      <c r="E27" s="29" t="n"/>
+      <c r="F27" s="30" t="n"/>
+    </row>
+    <row r="28" ht="41" customHeight="1" s="31">
+      <c r="A28" s="6" t="inlineStr">
         <is>
           <t>Checker编号</t>
         </is>
       </c>
-      <c r="B28" s="31" t="inlineStr">
+      <c r="B28" s="18" t="inlineStr">
         <is>
           <t>可以重复</t>
         </is>
       </c>
-      <c r="C28" s="22" t="n"/>
-      <c r="D28" s="22" t="n"/>
-      <c r="E28" s="22" t="n"/>
-      <c r="F28" s="23" t="n"/>
+      <c r="C28" s="29" t="n"/>
+      <c r="D28" s="29" t="n"/>
+      <c r="E28" s="29" t="n"/>
+      <c r="F28" s="30" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -2115,473 +2814,437 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M21"/>
+  <dimension ref="A1:D20"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col width="12" customWidth="1" style="28" min="1" max="1"/>
-    <col width="25" customWidth="1" style="28" min="2" max="2"/>
-    <col width="80" customWidth="1" style="28" min="3" max="3"/>
-    <col width="15" customWidth="1" style="28" min="4" max="4"/>
+    <col width="18.825" customWidth="1" style="31" min="1" max="1"/>
+    <col width="19.3" customWidth="1" style="31" min="2" max="2"/>
+    <col width="50.3083333333333" customWidth="1" style="31" min="3" max="3"/>
+    <col width="35.1583333333333" customWidth="1" style="31" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="32" t="inlineStr">
+      <c r="A1" s="5" t="inlineStr">
         <is>
           <t>Checker List</t>
         </is>
       </c>
-      <c r="B1" s="22" t="n"/>
-      <c r="C1" s="22" t="n"/>
-      <c r="D1" s="23" t="n"/>
+      <c r="B1" s="29" t="n"/>
+      <c r="C1" s="29" t="n"/>
+      <c r="D1" s="30" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="24" t="inlineStr">
+      <c r="A2" s="5" t="inlineStr">
         <is>
           <t>CHK编号</t>
         </is>
       </c>
-      <c r="B2" s="24" t="inlineStr">
+      <c r="B2" s="5" t="inlineStr">
         <is>
           <t>CHK Name</t>
         </is>
       </c>
-      <c r="C2" s="24" t="inlineStr">
+      <c r="C2" s="5" t="inlineStr">
         <is>
           <t>CHK描述</t>
         </is>
       </c>
-      <c r="D2" s="24" t="inlineStr">
+      <c r="D2" s="5" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="21" t="inlineStr">
+    <row r="3" ht="61" customHeight="1" s="31">
+      <c r="A3" s="45" t="inlineStr">
         <is>
           <t>CHK_001</t>
         </is>
       </c>
-      <c r="B3" s="21" t="inlineStr">
+      <c r="B3" s="45" t="inlineStr">
         <is>
           <t>clk_freq_checker</t>
         </is>
       </c>
-      <c r="C3" s="36" t="inlineStr">
-        <is>
-          <t>检查clk_i时钟频率和稳定性：
-1.频率检查：连续采集clk_i上升沿和下降沿，计算实际频率/周期，判断是否处于目标频率100MHz的允许误差范围内（±1%）；
-2.稳定性检查：通过连续采样周期，对比相邻两个周期的频率偏差是否在3%内；
-3.时钟域同步：验证协议采样、状态机控制和AHB-Lite主接口均在clk_i上升沿同步工作。</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>覆盖TP_001</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="21" t="inlineStr">
+      <c r="C3" s="46" t="inlineStr">
+        <is>
+          <t>1.检查频率值是否正确：连续采集clk_i时钟上升沿和下降沿并计算实际频率/周期，判断是否处于目标频率100MHz的允许误差范围内（±1%，即99MHz~101MHz）；
+2.检查时钟稳定性：通过连续采样周期，对比相邻两个周期的频率偏差是否在3%内；
+3.检查协议采样、状态机控制和AHB-Lite主接口是否在同域工作，无跨时钟域问题。</t>
+        </is>
+      </c>
+      <c r="D3" s="45" t="inlineStr"/>
+    </row>
+    <row r="4" ht="155" customHeight="1" s="31">
+      <c r="A4" s="45" t="inlineStr">
         <is>
           <t>CHK_002</t>
         </is>
       </c>
-      <c r="B4" s="18" t="inlineStr">
-        <is>
-          <t>reset_checker</t>
-        </is>
-      </c>
-      <c r="C4" s="37" t="inlineStr">
-        <is>
-          <t>检查rst_ni复位行为正确性：
-1.复位有效检查：rst_ni为低时，状态机应处于IDLE状态；
-2.复位释放检查：rst_ni释放后，验证内部同步释放机制；
-3.默认值检查：复位后CTRL.EN=0，CTRL.LANE_MODE=00(1-bit模式)；
-4.状态清零检查：复位后STATUS寄存器和LAST_ERR寄存器清零，协议上下文和错误状态已清空。</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>覆盖TP_002</t>
-        </is>
-      </c>
+      <c r="B4" s="45" t="inlineStr">
+        <is>
+          <t>reset_state_checker</t>
+        </is>
+      </c>
+      <c r="C4" s="46" t="inlineStr">
+        <is>
+          <t>检查rst_ni复位后的模块状态：
+1.检查状态机是否回到IDLE状态；
+2.检查CTRL.EN=0（模块未使能）；
+3.检查CTRL.LANE_MODE=00（1-bit模式）；
+4.检查STATUS寄存器值为0x00（无busy、无错误）；
+5.检查LAST_ERR寄存器值为0x00；
+6.检查协议上下文和响应上下文已清空。</t>
+        </is>
+      </c>
+      <c r="D4" s="45" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="21" t="inlineStr">
+      <c r="A5" s="45" t="inlineStr">
         <is>
           <t>CHK_003</t>
         </is>
       </c>
-      <c r="B5" s="21" t="inlineStr">
-        <is>
-          <t>csr_reg_checker</t>
-        </is>
-      </c>
-      <c r="C5" s="36" t="inlineStr">
-        <is>
-          <t>检查CSR寄存器读写正确性：
-1.VERSION寄存器：读取值应返回预期版本号；
-2.CTRL寄存器：EN、LANE_MODE、SOFT_RST字段读写正确，写入配置后读取值与写入一致；
-3.STATUS寄存器：busy位和sticky位反映正确状态；
-4.LAST_ERR寄存器：正确记录最近发生的错误码。</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>覆盖TP_003</t>
-        </is>
-      </c>
+      <c r="B5" s="45" t="inlineStr">
+        <is>
+          <t>csr_access_checker</t>
+        </is>
+      </c>
+      <c r="C5" s="45" t="inlineStr">
+        <is>
+          <t>检查CSR寄存器访问正确性：
+1.检查VERSION寄存器（地址0x00）读取返回预期版本值；
+2.检查CTRL寄存器（地址0x04）读写正确：EN[0]、LANE_MODE[2:1]、SOFT_RST[3]字段可配置；
+3.检查STATUS寄存器（地址0x08）只读属性：BUSY[0]、RESP_VALID[1]、CMD_ERR[2]、BUS_ERR[3]、FRAME_ERR[4]、IN_TEST_MODE[5]、OUT_EN[6]位反映正确状态；
+4.检查LAST_ERR寄存器（地址0x0C）只读属性：记录最近失败错误码；
+5.检查非法CSR地址访问返回STS_BAD_REG(0x02)。</t>
+        </is>
+      </c>
+      <c r="D5" s="45" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="45" t="inlineStr">
         <is>
           <t>CHK_004</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>work_mode_checker</t>
-        </is>
-      </c>
-      <c r="C6" s="38" t="inlineStr">
-        <is>
-          <t>检查工作模式和lane模式配置正确性：
-1.使能检查：test_mode_i=1且CTRL.EN=1时，模块允许执行功能命令；
-2.lane模式检查：LANE_MODE=00时使用1-bit模式(pdi_i[0]/pdo_o[0])，LANE_MODE=01时使用4-bit模式(pdi_i[3:0]/pdo_o[3:0])；
-3.半双工检查：请求阶段由主机驱动pdi_i，响应阶段由模块驱动pdo_o，pdo_oe_o正确指示方向切换；
-4.不支持功能检查：验证Burst和AXI后端功能确认不可用。</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>覆盖TP_004, TP_005</t>
-        </is>
-      </c>
+      <c r="B6" s="45" t="inlineStr">
+        <is>
+          <t>test_mode_checker</t>
+        </is>
+      </c>
+      <c r="C6" s="45" t="inlineStr">
+        <is>
+          <t>检查测试模式工作正确性：
+1.检查test_mode_i=1且CTRL.EN=1时模块允许执行功能命令；
+2.检查test_mode_i=0时命令返回STS_NOT_IN_TEST(0x05)；
+3.检查CTRL.EN=0时命令返回STS_DISABLED(0x04)；
+4.检查半双工请求/响应模式：请求阶段pdi_i输入，响应阶段pdo_o输出；
+5.检查turnaround周期pdo_oe_o=0（高阻态）。</t>
+        </is>
+      </c>
+      <c r="D6" s="45" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="45" t="inlineStr">
         <is>
           <t>CHK_005</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="45" t="inlineStr">
+        <is>
+          <t>lane_mode_checker</t>
+        </is>
+      </c>
+      <c r="C7" s="45" t="inlineStr">
+        <is>
+          <t>检查lane模式配置正确性：
+1.检查LANE_MODE=00时，仅pdi_i[0]/pdo_o[0]有效，其他位忽略；
+2.检查LANE_MODE=01时，pdi_i[3:0]/pdo_o[3:0]按高nibble优先发送；
+3.检查LANE_MODE=10/11为非法值，返回错误或忽略；
+4.检查事务执行期间lane mode不可动态切换；
+5.检查SOFT_RST=1后LANE_MODE恢复默认值00（1-bit）。</t>
+        </is>
+      </c>
+      <c r="D7" s="45" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="45" t="inlineStr">
+        <is>
+          <t>CHK_006</t>
+        </is>
+      </c>
+      <c r="B8" s="45" t="inlineStr">
         <is>
           <t>data_interface_checker</t>
         </is>
       </c>
-      <c r="C7" s="38" t="inlineStr">
-        <is>
-          <t>检查数据接口时序和格式正确性：
-1.帧边界检查：pcs_n_i=1表示空闲，pcs_n_i拉低开启事务，pcs_n_i拉高结束事务；
-2.数据顺序检查：协议字段按MSB first传输；
-3.lane模式检查：1-bit模式使用bit0，4-bit模式按高nibble优先发送；
-4.turnaround检查：请求阶段与响应阶段之间固定插入1个clk_i周期的turnaround；
-5.方向控制检查：响应期间pdo_oe_o=1，非响应期间pdo_oe_o=0。</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>覆盖TP_006, TP_007</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>CHK_006</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>opcode_checker</t>
-        </is>
-      </c>
-      <c r="C8" s="38" t="inlineStr">
+      <c r="C8" s="45" t="inlineStr">
+        <is>
+          <t>检查数据接口时序和格式：
+1.检查pcs_n_i帧边界：pcs_n_i=1表示空闲，pcs_n_i=0表示事务开始；
+2.检查MSB first传输顺序：高位先发；
+3.检查1-bit模式：pdi_i[0]/pdo_o[0]逐位传输；
+4.检查4-bit模式：pdi_i[3:0]/pdo_o[3:0]按nibble并行传输；
+5.检查pdo_oe_o输出使能：请求阶段为0，响应阶段为1。</t>
+        </is>
+      </c>
+      <c r="D8" s="45" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="45" t="inlineStr">
+        <is>
+          <t>CHK_007</t>
+        </is>
+      </c>
+      <c r="B9" s="45" t="inlineStr">
+        <is>
+          <t>protocol_timing_checker</t>
+        </is>
+      </c>
+      <c r="C9" s="45" t="inlineStr">
+        <is>
+          <t>检查协议时序正确性：
+1.检查turnaround固定1个clk_i周期；
+2.检查请求阶段与响应阶段之间pdo_oe_o正确切换；
+3.检查四种命令帧格式正确解析：
+   - WR_CSR(0x10)：8bit opcode + 8bit addr + 32bit wdata
+   - RD_CSR(0x11)：8bit opcode + 8bit addr
+   - AHB_WR32(0x20)：8bit opcode + 32bit addr + 32bit wdata
+   - AHB_RD32(0x21)：8bit opcode + 32bit addr
+4.检查帧长度与opcode匹配，不匹配返回STS_FRAME_ERR(0x06)。</t>
+        </is>
+      </c>
+      <c r="D9" s="45" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="45" t="inlineStr">
+        <is>
+          <t>CHK_008</t>
+        </is>
+      </c>
+      <c r="B10" s="45" t="inlineStr">
+        <is>
+          <t>opcode_decode_checker</t>
+        </is>
+      </c>
+      <c r="C10" s="45" t="inlineStr">
         <is>
           <t>检查opcode译码正确性：
-1.合法opcode检查：0x10译码为WR_CSR，0x11译码为RD_CSR，0x20译码为AHB_WR32，0x21译码为AHB_RD32；
-2.帧长确定检查：前端收满8bit opcode后正确确定期望帧长；
-3.非法opcode检查：非法opcode(如0x00/0xFF)应返回STS_BAD_OPCODE(0x01)。</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>覆盖TP_008</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>CHK_007</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
+1.检查opcode=0x10正确译码为WR_CSR命令；
+2.检查opcode=0x11正确译码为RD_CSR命令；
+3.检查opcode=0x20正确译码为AHB_WR32命令；
+4.检查opcode=0x21正确译码为AHB_RD32命令；
+5.检查非法opcode(非0x10/0x11/0x20/0x21)返回STS_BAD_OPCODE(0x01)；
+6.检查前端收满8bit opcode后正确确定期望帧长。</t>
+        </is>
+      </c>
+      <c r="D10" s="45" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="45" t="inlineStr">
+        <is>
+          <t>CHK_009</t>
+        </is>
+      </c>
+      <c r="B11" s="45" t="inlineStr">
         <is>
           <t>ctrl_config_checker</t>
         </is>
       </c>
-      <c r="C9" s="38" t="inlineStr">
-        <is>
-          <t>检查CTRL寄存器配置生效正确性：
-1.EN字段检查：CTRL.EN=1使能模块功能，CTRL.EN=0禁用模块；
-2.LANE_MODE字段检查：仅允许00=1-bit、01=4-bit，其他值应返回错误；
-3.SOFT_RST字段检查：SOFT_RST写1触发协议上下文清零并恢复默认lane模式(1-bit)；
-4.配置生效时序检查：配置在下一个事务生效。</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>覆盖TP_009</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="24" customHeight="1" s="28">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>CHK_008</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
+      <c r="C11" s="45" t="inlineStr">
+        <is>
+          <t>检查CTRL寄存器配置正确性：
+1.检查CTRL.EN写1后模块使能，可执行功能命令；
+2.检查CTRL.EN写0后模块禁用，命令返回STS_DISABLED(0x04)；
+3.检查CTRL.LANE_MODE=00/01配置生效；
+4.检查CTRL.SOFT_RST写1后触发软复位：协议上下文清零、LANE_MODE恢复00；
+5.检查软复位后STATUS.CMD_ERR、STATUS.BUS_ERR、STATUS.FRAME_ERR清零。</t>
+        </is>
+      </c>
+      <c r="D11" s="45" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="45" t="inlineStr">
+        <is>
+          <t>CHK_010</t>
+        </is>
+      </c>
+      <c r="B12" s="45" t="inlineStr">
         <is>
           <t>status_polling_checker</t>
         </is>
       </c>
-      <c r="C10" s="38" t="inlineStr">
-        <is>
-          <t>检查状态查询机制正确性：
-1.STATUS寄存器检查：busy位反映模块执行状态，sticky位记录历史错误；
-2.LAST_ERR寄存器检查：正确记录最近错误码(0x00~0x08)；
-3.无中断检查：MVP版本无独立中断输出，所有状态通过轮询获取。</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>覆盖TP_010</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="69.95" customHeight="1" s="28">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>CHK_009</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>exception_checker</t>
-        </is>
-      </c>
-      <c r="C11" s="38" t="inlineStr">
-        <is>
-          <t>检查异常检测和状态码返回正确性：
-1.BAD_OPCODE(0x01)：非法opcode检测；
-2.BAD_REG(0x02)：非法CSR地址检测；
-3.ALIGN_ERR(0x03)：非4Byte对齐地址检测；
-4.DISABLED(0x04)：CTRL.EN=0时发送命令检测；
-5.NOT_IN_TEST(0x05)：test_mode_i=0时发送命令检测；
-6.FRAME_ERR(0x06)：pcs_n_i提前拉高帧错误检测；
-7.AHB_ERR(0x07)：hresp_i=1错误检测；
-8.TIMEOUT(0x08)：AHB超时检测；
-9.错误收敛检查：在发起AHB访问前完成前置错误收敛。</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>覆盖TP_011</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>CHK_010</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
+      <c r="C12" s="45" t="inlineStr">
+        <is>
+          <t>检查状态查询机制：
+1.检查STATUS.BUSY=1表示当前有事务执行；
+2.检查STATUS.RESP_VALID=1表示最近响应有效；
+3.检查STATUS.CMD_ERR=1表示命令错误（sticky位）；
+4.检查STATUS.BUS_ERR=1表示总线错误（sticky位）；
+5.检查STATUS.FRAME_ERR=1表示帧错误（sticky位）；
+6.检查LAST_ERR记录最近失败错误码（0x01~0x08）；
+7.检查无独立中断输出，状态仅通过轮询获取。</t>
+        </is>
+      </c>
+      <c r="D12" s="45" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="47" t="inlineStr">
+        <is>
+          <t>CHK_011</t>
+        </is>
+      </c>
+      <c r="B13" s="47" t="inlineStr">
+        <is>
+          <t>error_handling_checker</t>
+        </is>
+      </c>
+      <c r="C13" s="47" t="inlineStr">
+        <is>
+          <t>检查异常处理正确性：
+1.检查BAD_OPCODE(0x01)：opcode非0x10/0x11/0x20/0x21时返回；
+2.检查BAD_REG(0x02)：CSR地址非0x00/0x04/0x08/0x0C时返回；
+3.检查ALIGN_ERR(0x03)：AHB地址非4Byte对齐时返回；
+4.检查DISABLED(0x04)：CTRL.EN=0时返回；
+5.检查NOT_IN_TEST(0x05)：test_mode_i=0时返回；
+6.检查FRAME_ERR(0x06)：pcs_n_i提前拉高或帧长度不匹配时返回；
+7.检查AHB_ERR(0x07)：hresp_i=1时返回；
+8.检查TIMEOUT(0x08)：AHB等待超过BUS_TIMEOUT_CYCLES(默认1024)时返回；
+9.检查前置错误在发起AHB访问前完成收敛，不得发起无效总线访问。</t>
+        </is>
+      </c>
+      <c r="D13" s="47" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="47" t="inlineStr">
+        <is>
+          <t>CHK_012</t>
+        </is>
+      </c>
+      <c r="B14" s="47" t="inlineStr">
         <is>
           <t>low_power_checker</t>
         </is>
       </c>
-      <c r="C12" s="38" t="inlineStr">
-        <is>
-          <t>检查低功耗设计正确性：
-1.空闲态检查：pcs_n_i=1时，接收移位寄存器不更新；
-2.非发送态检查：非发送阶段，发送移位寄存器不翻转；
-3.超时计数器检查：timeout counter仅在AHB等待态工作；
-4.测试模式检查：test_mode_i=0时，AHB输出保持IDLE值。</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>覆盖TP_012</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>CHK_011</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
+      <c r="C14" s="47" t="inlineStr">
+        <is>
+          <t>检查低功耗设计：
+1.检查空闲态（pcs_n_i=1）接收移位寄存器不更新；
+2.检查非发送阶段发送移位寄存器不翻转；
+3.检查timeout counter仅在AHB等待态工作；
+4.检查test_mode_i=0时AHB输出保持IDLE（htrans_o=0）；
+5.检查仅RX/TX/WAIT_AHB状态关键寄存器翻转。</t>
+        </is>
+      </c>
+      <c r="D14" s="47" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="47" t="inlineStr">
+        <is>
+          <t>CHK_013</t>
+        </is>
+      </c>
+      <c r="B15" s="47" t="inlineStr">
         <is>
           <t>performance_checker</t>
         </is>
       </c>
-      <c r="C13" s="38" t="inlineStr">
-        <is>
-          <t>检查性能指标达标：
-1.频率检查：clk_i=100MHz稳定工作；
-2.延时检查：4-bit模式下AHB_RD32最小端到端延时约23~24 cycles；
-3.吞吐率检查：1-bit模式线速12.5MB/s，4-bit模式线速50MB/s；
-4.AHB约束检查：AHB接口32bit字访问，地址4Byte对齐。</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>覆盖TP_013</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>CHK_012</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>dfx_observer_checker</t>
-        </is>
-      </c>
-      <c r="C14" s="38" t="inlineStr">
-        <is>
-          <t>检查DFX可观测点可访问：
-1.状态机状态可观测；
-2.opcode、addr、wdata、rdata、status_code可观测；
-3.rx/tx计数可观测；
-4.pcs_n_i、pdi_i、pdo_o、pdo_oe_o信号可观测。</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>覆盖TP_014</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>CHK_013</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
+      <c r="C15" s="47" t="inlineStr">
+        <is>
+          <t>检查性能指标：
+1.检查clk_i=100MHz稳定工作；
+2.检查端到端延时：4-bit模式AHB_RD32约23~24 cycles，AHB_WR32约23 cycles；
+3.检查吞吐率：1-bit模式约12.5MB/s，4-bit模式约50MB/s；
+4.检查AHB接口32bit字访问约束：hsize_o固定为WORD(010)；
+5.检查AHB地址4Byte对齐：addr[1:0]=00。</t>
+        </is>
+      </c>
+      <c r="D15" s="47" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="48" t="inlineStr">
+        <is>
+          <t>CHK_014</t>
+        </is>
+      </c>
+      <c r="B16" s="47" t="inlineStr">
+        <is>
+          <t>dfx_observability_checker</t>
+        </is>
+      </c>
+      <c r="C16" s="47" t="inlineStr">
+        <is>
+          <t>检查DFX可观测性：
+1.检查状态机状态可观测；
+2.检查opcode、addr、wdata、rdata、status_code可采集；
+3.检查rx/tx计数可观测；
+4.检查pcs_n_i、pdi_i、pdo_o、pdo_oe_o信号可采集；
+5.检查htrans_o、hready_i、hresp_i可观测。</t>
+        </is>
+      </c>
+      <c r="D16" s="47" t="inlineStr"/>
+    </row>
+    <row r="17" ht="24" customHeight="1" s="31">
+      <c r="A17" s="45" t="inlineStr">
+        <is>
+          <t>CHK_015</t>
+        </is>
+      </c>
+      <c r="B17" s="46" t="inlineStr">
         <is>
           <t>memory_map_checker</t>
         </is>
       </c>
-      <c r="C15" s="38" t="inlineStr">
+      <c r="C17" s="47" t="inlineStr">
         <is>
           <t>检查memory map正确性：
-1.CSR访问检查：模块内部CSR(VERSION/CTRL/STATUS/LAST_ERR)通过WR_CSR/RD_CSR协议命令访问；
-2.CSR隔离检查：模块自身CSR不进入SoC AHB memory map；
-3.AHB Master检查：对外AHB-Lite Master访问采用32bit地址空间和word访问粒度。</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>覆盖TP_015</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>CHK_014</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
+1.检查模块CSR（VERSION/CTRL/STATUS/LAST_ERR）仅通过协议命令访问，不进入SoC AHB memory map；
+2.检查AHB Master访问使用32bit地址空间；
+3.检查AHB Master访问粒度为word（32bit）；
+4.检查AHB地址范围由SoC顶层约束。</t>
+        </is>
+      </c>
+      <c r="D17" s="47" t="inlineStr"/>
+    </row>
+    <row r="18" ht="70" customHeight="1" s="31">
+      <c r="A18" s="45" t="inlineStr">
+        <is>
+          <t>CHK_016</t>
+        </is>
+      </c>
+      <c r="B18" s="46" t="inlineStr">
         <is>
           <t>ahb_interface_checker</t>
         </is>
       </c>
-      <c r="C16" s="38" t="inlineStr">
-        <is>
-          <t>检查AHB-Lite Master接口正确性：
-1.htrans_o检查：仅输出IDLE(2'b00)和NONSEQ(2'b10)；
-2.hsize_o检查：固定为WORD(3'b010)；
-3.hburst_o检查：固定为SINGLE(3'b000)；
-4.hwrite_o检查：写命令为高，读命令为低；
-5.haddr_o检查：地址4Byte对齐；
-6.hwdata_o/hrdata_i检查：32bit数据正确传输；
-7.hready_i/hresp_i检查：正确处理响应信号。</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>覆盖TP_016</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="27" t="inlineStr">
-        <is>
-          <t>填写要求</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="12" t="inlineStr">
-        <is>
-          <t>CHK Name</t>
-        </is>
-      </c>
-      <c r="B18" s="39" t="inlineStr">
-        <is>
-          <t>如果是SVA checker，需填写SVA property名字</t>
-        </is>
-      </c>
-      <c r="C18" s="22" t="n"/>
-      <c r="D18" s="23" t="n"/>
+      <c r="C18" s="47" t="inlineStr">
+        <is>
+          <t>检查AHB-Lite Master接口符合规范：
+1.检查haddr_o[31:0]输出正确的32bit地址；
+2.检查hwrite_o：写命令为1，读命令为0；
+3.检查htrans_o仅输出IDLE(00)或NONSEQ(10)；
+4.检查hsize_o固定为WORD(010)，表示32bit传输；
+5.检查hburst_o固定为SINGLE(000)，表示单次传输；
+6.检查hwdata_o[31:0]在写数据相输出正确数据；
+7.检查hrdata_i[31:0]正确接收读返回数据；
+8.检查hready_i=1时数据有效，hready_i=0时等待；
+9.检查hresp_i=1时返回STS_AHB_ERR(0x07)。</t>
+        </is>
+      </c>
+      <c r="D18" s="47" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="12" t="inlineStr">
-        <is>
-          <t>CHK描述</t>
-        </is>
-      </c>
-      <c r="B19" s="40" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1、需要定性+定量描述，需具体到check的信号、取值 
-2、和DV SPEC中Checker方案描述的区别 — RTM中描述check的内容，DV SPEC中描述checker的实现方案(例如是通过SVA实现还是scoreboard实时数据比对，还是文件对比)
-</t>
-        </is>
-      </c>
-      <c r="C19" s="22" t="n"/>
-      <c r="D19" s="23" t="n"/>
+      <c r="A19" s="6" t="n"/>
+      <c r="B19" s="6" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="12" t="n"/>
-      <c r="B20" s="12" t="n"/>
-      <c r="C20" s="22" t="n"/>
-      <c r="D20" s="23" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="12" t="n"/>
-      <c r="B21" s="12" t="n"/>
-      <c r="C21" s="22" t="n"/>
-      <c r="D21" s="23" t="n"/>
+      <c r="A20" s="6" t="n"/>
+      <c r="B20" s="6" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="1">
     <mergeCell ref="A1:D1"/>
-    <mergeCell ref="I17"/>
-    <mergeCell ref="J17"/>
-    <mergeCell ref="K17"/>
-    <mergeCell ref="M17"/>
-    <mergeCell ref="L17"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2593,604 +3256,595 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:D18"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col width="12" customWidth="1" style="28" min="1" max="1"/>
-    <col width="25" customWidth="1" style="28" min="2" max="2"/>
-    <col width="80" customWidth="1" style="28" min="3" max="3"/>
-    <col width="15" customWidth="1" style="28" min="4" max="4"/>
+    <col width="13.75" customWidth="1" style="31" min="1" max="1"/>
+    <col width="20.0583333333333" customWidth="1" style="31" min="2" max="2"/>
+    <col width="53.5" customWidth="1" style="31" min="3" max="3"/>
+    <col width="14.275" customWidth="1" style="31" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="32" t="inlineStr">
+      <c r="A1" s="5" t="inlineStr">
         <is>
           <t>Test Case List</t>
         </is>
       </c>
-      <c r="B1" s="22" t="n"/>
-      <c r="C1" s="22" t="n"/>
-      <c r="D1" s="23" t="n"/>
+      <c r="B1" s="29" t="n"/>
+      <c r="C1" s="29" t="n"/>
+      <c r="D1" s="30" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="24" t="inlineStr">
+      <c r="A2" s="5" t="inlineStr">
         <is>
           <t>TC编号</t>
         </is>
       </c>
-      <c r="B2" s="24" t="inlineStr">
+      <c r="B2" s="5" t="inlineStr">
         <is>
           <t>TC Name</t>
         </is>
       </c>
-      <c r="C2" s="24" t="inlineStr">
+      <c r="C2" s="5" t="inlineStr">
         <is>
           <t>TC 描述</t>
         </is>
       </c>
-      <c r="D2" s="24" t="inlineStr">
+      <c r="D2" s="5" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>TC_001</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>clk_domain_sync_test</t>
-        </is>
-      </c>
-      <c r="C3" s="41" t="inlineStr">
+    <row r="3" ht="98" customHeight="1" s="31">
+      <c r="A3" s="46" t="inlineStr">
+        <is>
+          <t>DV_TC_001</t>
+        </is>
+      </c>
+      <c r="B3" s="46" t="inlineStr">
+        <is>
+          <t>aplc_clk_freq_test</t>
+        </is>
+      </c>
+      <c r="C3" s="49" t="inlineStr">
         <is>
           <t>配置条件：
 1.配置clk_i时钟频率为100MHz；
-2.配置test_mode_i=1，通过WR_CSR(0x10)设置CTRL.EN=1；
-3.分别配置LANE_MODE=00(1-bit)和LANE_MODE=01(4-bit)。
+2.配置test_mode_i=1，通过WR_CSR(0x10)写CTRL.EN=1使能模块；
+3.配置LANE_MODE=00（1-bit模式）和01（4-bit模式）。
 输入激励：
-1.在1-bit模式下，连续发送AHB_RD32(0x21)和AHB_WR32(0x20)命令各100次；
-2.在4-bit模式下，重复上述测试；
-3.随机插入idle周期，验证时钟稳定性。
+1.连续发送AHB_RD32(0x21)命令，读取SoC内部有效地址；
+2.连续发送AHB_WR32(0x20)命令，写入SoC内部有效地址；
+3.覆盖1-bit和4-bit两种lane模式。
 期望结果：
 1.所有命令在100MHz频率下正确执行；
 2.协议采样、状态机控制和AHB-Lite主接口同域工作正常；
-3.无时序违例，无数据丢失。
+3.无时序违例，状态码返回0x00（成功）。
 coverage check点：
 直接用例覆盖，不收功能覆盖率。</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>覆盖TP_001</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>TC_002</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>reset_behavior_test</t>
-        </is>
-      </c>
-      <c r="C4" s="41" t="inlineStr">
+      <c r="D3" s="45" t="inlineStr"/>
+    </row>
+    <row r="4" ht="192" customHeight="1" s="31">
+      <c r="A4" s="46" t="inlineStr">
+        <is>
+          <t>DV_TC_002</t>
+        </is>
+      </c>
+      <c r="B4" s="46" t="inlineStr">
+        <is>
+          <t>aplc_reset_test</t>
+        </is>
+      </c>
+      <c r="C4" s="49" t="inlineStr">
         <is>
           <t>配置条件：
 1.初始状态rst_ni为低，模块处于复位状态；
-2.时钟clk_i稳定运行。
+2.配置clk_i=100MHz。
 输入激励：
-1.释放rst_ni，等待同步释放完成；
+1.释放rst_ni，验证复位后状态机回到IDLE；
 2.通过RD_CSR(0x11)读取CTRL寄存器，验证EN=0、LANE_MODE=00；
-3.通过RD_CSR读取STATUS和LAST_ERR寄存器，验证清零；
-4.验证状态机处于IDLE状态；
-5.反复复位释放10次，验证复位行为一致性。
+3.通过RD_CSR(0x11)读取STATUS寄存器，验证值为0x00；
+4.通过RD_CSR(0x11)读取LAST_ERR寄存器，验证值为0x00。
 期望结果：
-1.复位后状态机处于IDLE；
-2.CTRL.EN=0，CTRL.LANE_MODE=00(1-bit)；
-3.STATUS=0x00，LAST_ERR=0x00；
-4.协议上下文和错误状态已清空，无残留状态。
+1.复位后状态机处于IDLE状态；
+2.CTRL.EN=0（模块未使能）；
+3.CTRL.LANE_MODE=00（1-bit模式）；
+4.STATUS=0x00，LAST_ERR=0x00，无残留状态。
 coverage check点：
 直接用例覆盖，不收功能覆盖率。</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>覆盖TP_002</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>TC_003</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>csr_access_test</t>
-        </is>
-      </c>
-      <c r="C5" s="41" t="inlineStr">
+      <c r="D4" s="45" t="inlineStr"/>
+    </row>
+    <row r="5" ht="55" customHeight="1" s="31">
+      <c r="A5" s="46" t="inlineStr">
+        <is>
+          <t>DV_TC_003</t>
+        </is>
+      </c>
+      <c r="B5" s="46" t="inlineStr">
+        <is>
+          <t>aplc_csr_access_test</t>
+        </is>
+      </c>
+      <c r="C5" s="49" t="inlineStr">
         <is>
           <t>配置条件：
-1.配置test_mode_i=1；
-2.通过WR_CSR(0x10)设置CTRL.EN=1使能模块。
+1.配置test_mode_i=1，通过WR_CSR(0x10)写CTRL.EN=1使能模块；
+2.配置LANE_MODE=01（4-bit模式）。
 输入激励：
-1.通过RD_CSR(0x11)读取VERSION寄存器，验证版本号；
-2.通过WR_CSR写入CTRL.EN=1，LANE_MODE=01，验证配置生效；
-3.通过RD_CSR读取CTRL寄存器，验证写入正确；
-4.写入CTRL.SOFT_RST=1触发软复位，验证恢复默认值；
-5.随机读写STATUS和LAST_ERR寄存器，验证sticky位行为。
+1.发送RD_CSR(0x11)命令读取VERSION寄存器（地址0x00），验证版本号；
+2.发送WR_CSR(0x10)命令写CTRL寄存器（地址0x04），配置EN=1、LANE_MODE=01、SOFT_RST=0；
+3.发送RD_CSR(0x11)命令读取CTRL寄存器，验证写入正确；
+4.发送RD_CSR(0x11)命令读取STATUS寄存器（地址0x08），检查BUSY、RESP_VALID等位；
+5.发送RD_CSR(0x11)命令读取LAST_ERR寄存器（地址0x0C）；
+6.发送RD_CSR(0x11)命令访问非法CSR地址（如0x10），验证返回STS_BAD_REG(0x02)。
 期望结果：
-1.VERSION寄存器返回预期版本号；
-2.CTRL配置正确写入和读取；
-3.SOFT_RST触发后恢复默认lane模式；
-4.STATUS/LAST_ERR反映正确状态。
+1.VERSION寄存器返回预期版本值；
+2.CTRL寄存器读写正确，配置生效；
+3.STATUS寄存器反映正确状态；
+4.LAST_ERR寄存器记录错误码；
+5.非法CSR地址返回STS_BAD_REG(0x02)。
 coverage check点：
 直接用例覆盖，不收功能覆盖率。</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>覆盖TP_003</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>TC_004</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>work_mode_test</t>
-        </is>
-      </c>
-      <c r="C6" s="41" t="inlineStr">
+      <c r="D5" s="45" t="inlineStr"/>
+    </row>
+    <row r="6" ht="26" customHeight="1" s="31">
+      <c r="A6" s="46" t="inlineStr">
+        <is>
+          <t>DV_TC_004</t>
+        </is>
+      </c>
+      <c r="B6" s="46" t="inlineStr">
+        <is>
+          <t>aplc_test_mode_test</t>
+        </is>
+      </c>
+      <c r="C6" s="45" t="inlineStr">
         <is>
           <t>配置条件：
-1.配置test_mode_i=1，通过WR_CSR(0x10)设置CTRL.EN=1；
-2.分别配置LANE_MODE=00(1-bit)和LANE_MODE=01(4-bit)。
+1.配置clk_i=100MHz，test_mode_i=1；
+2.通过WR_CSR(0x10)写CTRL.EN=1使能模块。
 输入激励：
-1.在test_mode_i=1时，发送WR_CSR配置lane模式，发送AHB_WR32/AHB_RD32命令；
-2.在test_mode_i=0时，发送功能命令，验证返回NOT_IN_TEST错误(0x05)；
-3.在CTRL.EN=0时，发送功能命令，验证返回DISABLED错误(0x04)；
-4.尝试配置非法LANE_MODE值(02/03)，验证错误处理；
-5.验证半双工请求/响应模式：请求阶段pdo_oe_o=0，响应阶段pdo_oe_o=1。
+1.发送WR_CSR(0x10)命令配置LANE_MODE=01（4-bit模式）；
+2.发送AHB_WR32(0x20)命令进行单次写操作；
+3.发送AHB_RD32(0x21)命令进行单次读操作；
+4.验证半双工请求/响应模式工作正常；
+5.验证turnaround周期pdo_oe_o=0。
 期望结果：
-1.test_mode_i=1且CTRL.EN=1时，命令正确执行；
-2.test_mode_i=0时，返回STS_NOT_IN_TEST(0x05)；
-3.CTRL.EN=0时，返回STS_DISABLED(0x04)；
-4.非法LANE_MODE值返回错误；
+1.模块正确执行WR_CSR、AHB_WR32、AHB_RD32功能命令；
+2.协议采用半双工模式：请求阶段pdi_i输入，响应阶段pdo_o输出；
+3.turnaround固定1周期，pdo_oe_o正确切换；
+4.状态码返回0x00（成功）。
+coverage check点：
+直接用例覆盖，不收功能覆盖率。</t>
+        </is>
+      </c>
+      <c r="D6" s="45" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="45" t="inlineStr">
+        <is>
+          <t>DV_TC_005</t>
+        </is>
+      </c>
+      <c r="B7" s="45" t="inlineStr">
+        <is>
+          <t>aplc_lane_mode_test</t>
+        </is>
+      </c>
+      <c r="C7" s="45" t="inlineStr">
+        <is>
+          <t>配置条件：
+1.配置test_mode_i=1，CTRL.EN=1使能模块；
+2.依次配置不同LANE_MODE。
+输入激励：
+1.配置CTRL.LANE_MODE=00（1-bit模式），发送AHB_RD32命令，验证pdi_i[0]/pdo_o[0]逐位传输；
+2.配置CTRL.LANE_MODE=01（4-bit模式），发送AHB_RD32命令，验证pdi_i[3:0]/pdo_o[3:0]并行传输，高nibble优先；
+3.尝试配置LANE_MODE=10/11，验证返回错误或忽略；
+4.验证事务执行期间lane mode不可动态切换；
+5.配置CTRL.SOFT_RST=1触发软复位，验证LANE_MODE恢复00。
+期望结果：
+1.1-bit模式使用bit0传输，其他位忽略；
+2.4-bit模式使用pdi_i[3:0]/pdo_o[3:0]并行传输；
+3.LANE_MODE=10/11为非法值；
+4.软复位后LANE_MODE恢复默认值00；
 5.Burst和AXI功能确认不可用。
 coverage check点：
 直接用例覆盖，不收功能覆盖率。</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>覆盖TP_004, TP_005</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="16" t="inlineStr">
-        <is>
-          <t>TC_005</t>
-        </is>
-      </c>
-      <c r="B7" s="16" t="inlineStr">
-        <is>
-          <t>data_interface_test</t>
-        </is>
-      </c>
-      <c r="C7" s="42" t="inlineStr">
+      <c r="D7" s="45" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="45" t="inlineStr">
+        <is>
+          <t>DV_TC_006</t>
+        </is>
+      </c>
+      <c r="B8" s="45" t="inlineStr">
+        <is>
+          <t>aplc_data_interface_test</t>
+        </is>
+      </c>
+      <c r="C8" s="45" t="inlineStr">
         <is>
           <t>配置条件：
-1.配置test_mode_i=1，CTRL.EN=1；
-2.分别配置LANE_MODE=00(1-bit)和LANE_MODE=01(4-bit)。
+1.配置test_mode_i=1，CTRL.EN=1使能模块；
+2.配置LANE_MODE=00（1-bit）和01（4-bit）两种模式。
 输入激励：
 1.在1-bit模式下发送WR_CSR(0x10)命令，验证pdi_i[0]/pdo_o[0]数据传输；
-2.在4-bit模式下发送相同命令，验证pdi_i[3:0]/pdo_o[3:0]按高nibble优先发送；
-3.验证pcs_n_i帧边界：拉低开启事务，拉高结束事务；
-4.验证MSB first传输顺序。
+2.在1-bit模式下发送AHB_WR32(0x20)命令，验证帧边界和数据顺序；
+3.在4-bit模式下发送相同命令，验证pdi_i[3:0]/pdo_o[3:0]按高nibble优先发送；
+4.验证pcs_n_i帧边界：pcs_n_i=0开启事务，pcs_n_i=1结束事务；
+5.验证MSB first传输顺序。
 期望结果：
-1.1-bit模式正确使用bit0传输；
-2.4-bit模式按高nibble优先发送；
-3.pcs_n_i正确标记帧边界；
-4.数据按MSB first顺序传输。
+1.1-bit模式仅bit0有效，其他位忽略；
+2.4-bit模式按nibble并行传输；
+3.pcs_n_i帧边界清晰正确；
+4.MSB first顺序正确；
+5.pdo_oe_o在响应阶段为1。
 coverage check点：
 直接用例覆盖，不收功能覆盖率。</t>
         </is>
       </c>
-      <c r="D7" s="14" t="inlineStr">
-        <is>
-          <t>覆盖TP_006</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>TC_006</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>protocol_timing_test</t>
-        </is>
-      </c>
-      <c r="C8" s="38" t="inlineStr">
+      <c r="D8" s="45" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="45" t="inlineStr">
+        <is>
+          <t>DV_TC_007</t>
+        </is>
+      </c>
+      <c r="B9" s="45" t="inlineStr">
+        <is>
+          <t>aplc_protocol_timing_test</t>
+        </is>
+      </c>
+      <c r="C9" s="45" t="inlineStr">
         <is>
           <t>配置条件：
-1.配置test_mode_i=1，CTRL.EN=1；
-2.配置LANE_MODE=01(4-bit模式)。
+1.配置test_mode_i=1，CTRL.EN=1使能模块；
+2.配置LANE_MODE=01（4-bit模式）。
 输入激励：
-1.发送WR_CSR(0x10)命令，记录请求阶段结束时刻；
-2.验证turnaround周期为1个clk_i周期；
-3.检查pdo_oe_o在turnaround后置1；
-4.依次发送四种命令：WR_CSR(0x10)、RD_CSR(0x11)、AHB_WR32(0x20)、AHB_RD32(0x21)；
-5.测量每种命令的端到端延时。
+1.发送WR_CSR(0x10)命令验证请求阶段；
+2.验证turnaround周期为固定1个clk_i周期；
+3.检查响应阶段pdo_oe_o=1输出使能；
+4.验证四种命令帧格式：
+   - WR_CSR(0x10)：8bit opcode + 8bit addr + 32bit wdata = 48bit = 12拍（4-bit模式）
+   - RD_CSR(0x11)：8bit opcode + 8bit addr = 16bit = 4拍（4-bit模式）
+   - AHB_WR32(0x20)：8bit opcode + 32bit addr + 32bit wdata = 72bit = 18拍（4-bit模式）
+   - AHB_RD32(0x21)：8bit opcode + 32bit addr = 40bit = 10拍（4-bit模式）；
+5.提前拉高pcs_n_i验证FRAME_ERR检测。
 期望结果：
-1.请求阶段与响应阶段正确分离；
+1.请求/响应阶段正确分离；
 2.turnaround固定1周期；
-3.pdo_oe_o在响应阶段置1；
-4.协议字段MSB first传输；
-5.四种帧格式正确处理。
+3.协议字段MSB first传输；
+4.四种帧格式正确处理；
+5.帧长度不匹配返回STS_FRAME_ERR(0x06)。
 coverage check点：
 直接用例覆盖，不收功能覆盖率。</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>覆盖TP_007</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>TC_007</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>opcode_test</t>
-        </is>
-      </c>
-      <c r="C9" s="38" t="inlineStr">
+      <c r="D9" s="45" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="45" t="inlineStr">
+        <is>
+          <t>DV_TC_008</t>
+        </is>
+      </c>
+      <c r="B10" s="45" t="inlineStr">
+        <is>
+          <t>aplc_opcode_test</t>
+        </is>
+      </c>
+      <c r="C10" s="45" t="inlineStr">
         <is>
           <t>配置条件：
-1.配置test_mode_i=1，CTRL.EN=1；
-2.AHB总线空闲。
+1.配置test_mode_i=1，CTRL.EN=1使能模块；
+2.配置AHB总线空闲正常。
 输入激励：
-1.发送opcode=0x10(WR_CSR)，验证CSR写功能；
-2.发送opcode=0x11(RD_CSR)，验证CSR读功能；
-3.发送opcode=0x20(AHB_WR32)，验证AHB单次写功能；
-4.发送opcode=0x21(AHB_RD32)，验证AHB单次读功能；
-5.发送非法opcode(0x00/0xFF/0x30/0x0F等)，验证错误返回；
-6.随机生成100个非法opcode，验证全部返回STS_BAD_OPCODE(0x01)。
+1.发送opcode=0x10执行WR_CSR命令，验证正确译码；
+2.发送opcode=0x11执行RD_CSR命令，验证正确译码；
+3.发送opcode=0x20执行AHB_WR32命令，验证正确译码；
+4.发送opcode=0x21执行AHB_RD32命令，验证正确译码；
+5.发送非法opcode（如0x00、0xFF、0x30等非0x10/0x11/0x20/0x21值）；
+6.验证前端收满8bit opcode后正确确定期望帧长。
 期望结果：
-1.四种合法opcode正确译码并执行；
+1.四种opcode正确译码并执行对应功能；
 2.非法opcode返回STS_BAD_OPCODE(0x01)；
-3.前端收满8bit后正确确定期望帧长。
+3.LAST_ERR更新为0x01；
+4.STATUS.CMD_ERR=1；
+5.前端正确确定期望帧长。
 coverage check点：
 直接用例覆盖，不收功能覆盖率。</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>覆盖TP_008</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>TC_008</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>ctrl_config_test</t>
-        </is>
-      </c>
-      <c r="C10" s="38" t="inlineStr">
+      <c r="D10" s="45" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="45" t="inlineStr">
+        <is>
+          <t>DV_TC_009</t>
+        </is>
+      </c>
+      <c r="B11" s="45" t="inlineStr">
+        <is>
+          <t>aplc_ctrl_config_test</t>
+        </is>
+      </c>
+      <c r="C11" s="45" t="inlineStr">
         <is>
           <t>配置条件：
 1.配置test_mode_i=1；
-2.模块初始状态禁用(CTRL.EN=0)。
+2.初始CTRL.EN=0。
 输入激励：
-1.写CTRL.EN=1使能模块，发送功能命令验证可执行；
-2.写CTRL.EN=0禁用模块，发送命令验证返回DISABLED(0x04)；
-3.配置LANE_MODE=00验证1-bit模式工作；
-4.配置LANE_MODE=01验证4-bit模式工作；
-5.尝试配置LANE_MODE=10/11，验证非法配置处理；
-6.写CTRL.SOFT_RST=1触发软复位，验证协议上下文清零；
-7.软复位后验证恢复默认lane模式(1-bit)。
+1.写CTRL.EN=1使能模块，发送AHB_RD32命令验证功能命令可执行；
+2.写CTRL.EN=0禁用模块，发送命令验证返回STS_DISABLED(0x04)；
+3.写CTRL.LANE_MODE=00验证1-bit模式生效；
+4.写CTRL.LANE_MODE=01验证4-bit模式生效；
+5.写CTRL.SOFT_RST=1触发软复位，验证协议上下文清零、LANE_MODE恢复00；
+6.验证软复位后STATUS寄存器错误位清零。
 期望结果：
-1.EN使能/禁用状态切换正确；
-2.LANE_MODE=00/01配置生效；
-3.非法LANE_MODE返回错误；
-4.SOFT_RST触发协议上下文清零；
-5.恢复默认1-bit模式。
+1.CTRL.EN使能/禁用状态切换正确；
+2.CTRL.LANE_MODE配置生效；
+3.软复位功能正常；
+4.协议上下文清零；
+5.LANE_MODE恢复默认值00。
 coverage check点：
 直接用例覆盖，不收功能覆盖率。</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>覆盖TP_009</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>TC_009</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>status_polling_test</t>
-        </is>
-      </c>
-      <c r="C11" s="38" t="inlineStr">
+      <c r="D11" s="45" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="45" t="inlineStr">
+        <is>
+          <t>DV_TC_010</t>
+        </is>
+      </c>
+      <c r="B12" s="45" t="inlineStr">
+        <is>
+          <t>aplc_status_polling_test</t>
+        </is>
+      </c>
+      <c r="C12" s="45" t="inlineStr">
         <is>
           <t>配置条件：
-1.配置test_mode_i=1，CTRL.EN=1；
-2.准备触发各类错误条件。
+1.配置test_mode_i=1，CTRL.EN=1使能模块；
+2.配置各类错误触发条件。
 输入激励：
-1.触发非法opcode错误，通过RD_CSR读取STATUS寄存器sticky位；
-2.读取LAST_ERR寄存器验证错误码更新；
-3.依次触发各类错误(BAD_REG/ALIGN_ERR/DISABLED/NOT_IN_TEST/FRAME_ERR/AHB_ERR/TIMEOUT)；
-4.验证无独立中断输出信号；
-5.模拟ATE轮询方式获取状态。
+1.触发非法opcode错误，通过RD_CSR读取STATUS寄存器，验证CMD_ERR=1；
+2.触发AHB错误（hresp_i=1），通过RD_CSR读取STATUS寄存器，验证BUS_ERR=1；
+3.触发帧错误，通过RD_CSR读取STATUS寄存器，验证FRAME_ERR=1；
+4.执行命令期间读取STATUS.BUSY=1；
+5.命令完成后读取STATUS.RESP_VALID=1；
+6.读取LAST_ERR寄存器获取最近错误码；
+7.验证无独立中断输出引脚。
 期望结果：
-1.STATUS寄存器sticky位正确记录历史错误；
-2.LAST_ERR正确记录最近错误码；
+1.STATUS寄存器各sticky位正确置位；
+2.LAST_ERR记录最近失败错误码；
 3.MVP版本无中断输出；
-4.轮询方式正确获取状态。
+4.ATE轮询方式正确获取状态。
 coverage check点：
 直接用例覆盖，不收功能覆盖率。</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>覆盖TP_010</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>TC_010</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>exception_test</t>
-        </is>
-      </c>
-      <c r="C12" s="38" t="inlineStr">
+      <c r="D12" s="45" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="47" t="inlineStr">
+        <is>
+          <t>DV_TC_011</t>
+        </is>
+      </c>
+      <c r="B13" s="47" t="inlineStr">
+        <is>
+          <t>aplc_error_handling_test</t>
+        </is>
+      </c>
+      <c r="C13" s="47" t="inlineStr">
         <is>
           <t>配置条件：
-1.配置test_mode_i=1，CTRL.EN=1；
-2.AHB总线正常响应。
+1.配置test_mode_i=1，CTRL.EN=1使能模块；
+2.配置AHB总线正常响应。
 输入激励：
-1.发送非法opcode(0x00/0xFF)验证BAD_OPCODE(0x01)；
-2.访问非法CSR地址(如0xFC)验证BAD_REG(0x02)；
-3.发送非4Byte对齐地址(如0x01)验证ALIGN_ERR(0x03)；
-4.设置CTRL.EN=0后发送命令验证DISABLED(0x04)；
-5.设置test_mode_i=0后发送命令验证NOT_IN_TEST(0x05)；
-6.在请求阶段提前拉高pcs_n_i验证FRAME_ERR(0x06)；
-7.配置hresp_i=1模拟AHB错误验证AHB_ERR(0x07)；
-8.模拟hready_i长时间为0验证TIMEOUT(0x08)；
-9.验证所有错误在发起AHB访问前完成收敛。
+1.发送非法opcode（0x00/0xFF）验证返回STS_BAD_OPCODE(0x01)；
+2.访问非法CSR地址（0x10等）验证返回STS_BAD_REG(0x02)；
+3.发送非4Byte对齐地址（如0x00000001）执行AHB命令，验证返回STS_ALIGN_ERR(0x03)；
+4.配置CTRL.EN=0，发送命令验证返回STS_DISABLED(0x04)；
+5.配置test_mode_i=0，发送命令验证返回STS_NOT_IN_TEST(0x05)；
+6.发送命令期间提前拉高pcs_n_i，验证返回STS_FRAME_ERR(0x06)；
+7.触发hresp_i=1，验证返回STS_AHB_ERR(0x07)；
+8.模拟AHB超时（hready_i=0持续超过1024周期），验证返回STS_TIMEOUT(0x08)；
+9.验证前置错误在发起AHB访问前完成收敛。
 期望结果：
 1.各类错误正确检测并返回对应状态码；
 2.LAST_ERR更新正确；
-3.错误在AHB访问前收敛，不发起错误AHB访问。
+3.STATUS对应错误位置位；
+4.不发起无效总线访问。
 coverage check点：
 直接用例覆盖，不收功能覆盖率。</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>覆盖TP_011</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>TC_011</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>low_power_test</t>
-        </is>
-      </c>
-      <c r="C13" s="38" t="inlineStr">
+      <c r="D13" s="47" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="47" t="inlineStr">
+        <is>
+          <t>DV_TC_012</t>
+        </is>
+      </c>
+      <c r="B14" s="47" t="inlineStr">
+        <is>
+          <t>aplc_low_power_test</t>
+        </is>
+      </c>
+      <c r="C14" s="47" t="inlineStr">
         <is>
           <t>配置条件：
-1.模块初始处于空闲态(test_mode_i=0或pcs_n_i=1)。
+1.模块处于空闲态（pcs_n_i=1或test_mode_i=0或无有效任务）；
+2.配置clk_i=100MHz。
 输入激励：
-1.保持pcs_n_i=1，观察接收移位寄存器是否翻转；
-2.模拟AHB等待态，观察超时计数器是否工作；
-3.设置test_mode_i=0，验证AHB输出保持IDLE；
-4.切换到工作态，验证关键寄存器翻转；
-5.测量空闲态和工作态的翻转活动差异。
+1.保持pcs_n_i=1，监控接收移位寄存器是否翻转；
+2.保持非发送状态，监控发送移位寄存器是否翻转；
+3.模拟AHB等待态（hready_i=0），验证timeout counter工作；
+4.配置test_mode_i=0，验证AHB输出保持IDLE（htrans_o=0）；
+5.切换到工作态，监控关键寄存器翻转情况。
 期望结果：
-1.pcs_n_i=1时接收移位寄存器不翻转；
-2.超时计数器仅在AHB等待态工作；
-3.test_mode_i=0时AHB输出IDLE；
-4.空闲态翻转最小化，低功耗目标满足。
+1.空闲态接收/发送移位寄存器不翻转；
+2.timeout counter仅在AHB等待态工作；
+3.test_mode_i=0时AHB输出保持IDLE；
+4.仅RX/TX/WAIT_AHB状态关键寄存器翻转。
 coverage check点：
 直接用例覆盖，不收功能覆盖率。</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>覆盖TP_012</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>TC_012</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>performance_test</t>
-        </is>
-      </c>
-      <c r="C14" s="38" t="inlineStr">
+      <c r="D14" s="47" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="47" t="inlineStr">
+        <is>
+          <t>DV_TC_013</t>
+        </is>
+      </c>
+      <c r="B15" s="47" t="inlineStr">
+        <is>
+          <t>aplc_performance_test</t>
+        </is>
+      </c>
+      <c r="C15" s="47" t="inlineStr">
         <is>
           <t>配置条件：
 1.配置clk_i=100MHz；
-2.AHB总线hready_i=1正常响应。
+2.配置test_mode_i=1，CTRL.EN=1使能模块；
+3.配置AHB总线响应正常（hready_i=1）。
 输入激励：
-1.在1-bit模式下连续执行AHB_RD32/AHB_WR32命令各100次，计算端到端延时；
-2.在4-bit模式下执行相同测试，测量延时；
-3.计算吞吐率：1-bit模式和4-bit模式；
-4.发送非4Byte对齐地址，验证AHB访问约束；
-5.测量状态机各阶段延时分布。
+1.在1-bit模式下连续执行AHB_RD32/AHB_WR32命令，计算端到端延时和吞吐率；
+2.在4-bit模式下执行相同测试；
+3.验证链路线速：1-bit模式约12.5MB/s，4-bit模式约50MB/s；
+4.验证AHB接口32bit字访问（hsize_o=010）；
+5.验证AHB地址4Byte对齐（addr[1:0]=00）。
 期望结果：
-1.100MHz稳定工作；
-2.4-bit模式AHB_RD32最小延时约23~24 cycles；
-3.1-bit模式线速≈12.5MB/s，4-bit模式≈50MB/s；
-4.AHB访问32bit字粒度，4Byte对齐约束满足。
+1.目标频率100MHz稳定工作；
+2.端到端延时：4-bit模式AHB_RD32约23~24 cycles，AHB_WR32约23 cycles；
+3.吞吐率达标；
+4.AHB访问约束满足。
 coverage check点：
 直接用例覆盖，不收功能覆盖率。</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>覆盖TP_013</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>TC_013</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>dfx_test</t>
-        </is>
-      </c>
-      <c r="C15" s="38" t="inlineStr">
+      <c r="D15" s="47" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="47" t="inlineStr">
+        <is>
+          <t>DV_TC_014</t>
+        </is>
+      </c>
+      <c r="B16" s="47" t="inlineStr">
+        <is>
+          <t>aplc_dfx_test</t>
+        </is>
+      </c>
+      <c r="C16" s="47" t="inlineStr">
         <is>
           <t>配置条件：
-1.仿真环境，配置test_mode_i=1，CTRL.EN=1。
+1.仿真环境，test_mode_i=1，CTRL.EN=1使能模块。
 输入激励：
-1.执行多种命令序列(包含所有四种opcode)；
-2.采集状态机状态信号；
-3.采集opcode、addr、wdata、rdata、status_code；
-4.采集rx/tx计数；
-5.采集pcs_n_i、pdi_i、pdo_o、pdo_oe_o；
-6.触发各类错误，观察调试可观测点。
+1.执行多种命令序列（WR_CSR、RD_CSR、AHB_WR32、AHB_RD32）；
+2.采集状态机状态、opcode、addr、wdata、rdata、status_code；
+3.采集rx/tx计数；
+4.采集pcs_n_i、pdi_i、pdo_o、pdo_oe_o信号；
+5.采集htrans_o、hready_i、hresp_i信号。
 期望结果：
-1.状态机状态可观测；
-2.所有内部调试信号可采集；
-3.便于联调、波形定位和故障复现。
+1.所有调试可观测点可采集；
+2.便于联调、波形定位和故障复现；
+3.流量统计可观测。
 coverage check点：
 直接用例覆盖，不收功能覆盖率。</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>覆盖TP_014</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>TC_014</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>memory_map_test</t>
-        </is>
-      </c>
-      <c r="C16" s="38" t="inlineStr">
+      <c r="D16" s="47" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="47" t="inlineStr">
+        <is>
+          <t>DV_TC_015</t>
+        </is>
+      </c>
+      <c r="B17" s="47" t="inlineStr">
+        <is>
+          <t>aplc_memory_map_test</t>
+        </is>
+      </c>
+      <c r="C17" s="47" t="inlineStr">
         <is>
           <t>配置条件：
-1.配置test_mode_i=1，CTRL.EN=1。
+1.配置test_mode_i=1，CTRL.EN=1使能模块。
 输入激励：
-1.通过WR_CSR/RD_CSR访问VERSION寄存器，验证CSR路径；
-2.通过WR_CSR/RD_CSR访问CTRL、STATUS、LAST_ERR寄存器；
-3.发送AHB_WR32/AHB_RD32命令访问SoC内部memory-mapped地址；
-4.验证模块自身CSR不通过AHB地址空间访问；
-5.验证AHB Master使用32bit地址空间和word访问粒度。
+1.通过WR_CSR/RD_CSR访问模块内部CSR寄存器（VERSION地址0x00、CTRL地址0x04、STATUS地址0x08、LAST_ERR地址0x0C）；
+2.发送AHB_WR32/AHB_RD32命令访问SoC内部memory-mapped地址；
+3.验证模块自身CSR不进入SoC AHB memory map；
+4.验证AHB Master访问使用32bit地址空间；
+5.验证AHB Master访问粒度为word（32bit）。
 期望结果：
-1.CSR通过协议命令正确访问；
-2.模块CSR不进入SoC AHB memory map；
-3.AHB Master访问正确，地址空间约束满足。
+1.CSR通过协议命令访问正常；
+2.AHB Master访问正确；
+3.CSR不暴露在AHB memory map中；
+4.地址空间约束满足。
 coverage check点：
 直接用例覆盖，不收功能覆盖率。</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>覆盖TP_015</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>TC_015</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>ahb_interface_test</t>
-        </is>
-      </c>
-      <c r="C17" s="38" t="inlineStr">
+      <c r="D17" s="47" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="47" t="inlineStr">
+        <is>
+          <t>DV_TC_016</t>
+        </is>
+      </c>
+      <c r="B18" s="47" t="inlineStr">
+        <is>
+          <t>aplc_ahb_interface_test</t>
+        </is>
+      </c>
+      <c r="C18" s="47" t="inlineStr">
         <is>
           <t>配置条件：
-1.配置test_mode_i=1，CTRL.EN=1；
-2.AHB总线hready_i=1，hresp_i=0正常响应。
+1.配置test_mode_i=1，CTRL.EN=1使能模块；
+2.配置AHB总线空闲正常。
 输入激励：
-1.发送AHB_WR32(0x20)命令，验证haddr_o/hwrite_o/htrans_o/hsize_o/hburst_o/hwdata_o输出；
-2.发送AHB_RD32(0x21)命令，验证hrdata_i输入正确接收；
-3.验证htrans_o仅输出IDLE(2'b00)和NONSEQ(2'b10)；
-4.验证hsize_o固定为WORD(3'b010)；
-5.验证hburst_o固定为SINGLE(3'b000)；
-6.模拟hready_i=0等待态，验证模块行为；
-7.模拟hresp_i=1错误响应，验证错误处理。
+1.发送AHB_WR32(0x20)命令，验证haddr_o[31:0]输出正确的32bit地址；
+2.验证hwrite_o=1（写操作）；
+3.验证htrans_o=NONSEQ(10)；
+4.验证hsize_o=WORD(010)表示32bit传输；
+5.验证hburst_o=SINGLE(000)表示单次传输；
+6.验证hwdata_o[31:0]输出正确写数据；
+7.发送AHB_RD32(0x21)命令，验证hwrite_o=0（读操作）；
+8.验证hrdata_i[31:0]正确接收读返回数据；
+9.模拟hready_i=0等待，验证模块正确等待；
+10.模拟hresp_i=1，验证返回STS_AHB_ERR(0x07)。
 期望结果：
-1.AHB信号输出符合AHB-Lite协议规范；
-2.htrans_o仅IDLE/NONSEQ；
-3.hsize_o=WORD，hburst_o=SINGLE；
-4.hready_i等待和hresp_i错误正确处理。
+1.AHB-Lite Master接口符合规范；
+2.单次读写事务正确；
+3.htrans_o仅输出IDLE/NONSEQ；
+4.hsize_o固定为WORD；
+5.hburst_o固定为SINGLE；
+6.错误响应正确处理。
 coverage check点：
 直接用例覆盖，不收功能覆盖率。</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>覆盖TP_016</t>
-        </is>
-      </c>
+      <c r="D18" s="47" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
